--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>27021.686746988</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>162130.120481928</v>
+        <v>162000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -944,10 +944,10 @@
         <v>26</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3087824351</v>
+        <v>1811.3087912088</v>
       </c>
       <c r="O13" t="n">
-        <v>47094.0283433126</v>
+        <v>47094.0285714288</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -3666,10 +3666,10 @@
         <v>7</v>
       </c>
       <c r="N78" t="n">
-        <v>16486.408</v>
+        <v>16486.40779661</v>
       </c>
       <c r="O78" t="n">
-        <v>115404.856</v>
+        <v>115404.85457627</v>
       </c>
       <c r="P78" t="n">
         <v>30500</v>
@@ -3708,10 +3708,10 @@
         <v>13</v>
       </c>
       <c r="N79" t="n">
-        <v>15711.964602273</v>
+        <v>15711.964444444</v>
       </c>
       <c r="O79" t="n">
-        <v>204255.539829549</v>
+        <v>204255.537777772</v>
       </c>
       <c r="P79" t="n">
         <v>28500</v>
@@ -4659,10 +4659,10 @@
         <v>3</v>
       </c>
       <c r="N101" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17847826</v>
       </c>
       <c r="O101" t="n">
-        <v>1033797.53553192</v>
+        <v>1033797.53543478</v>
       </c>
       <c r="P101" t="n">
         <v>532900</v>
@@ -8040,10 +8040,10 @@
         <v>316</v>
       </c>
       <c r="N179" t="n">
-        <v>1098.0630728186</v>
+        <v>1098.0632479443</v>
       </c>
       <c r="O179" t="n">
-        <v>346987.9310106776</v>
+        <v>346987.9863503988</v>
       </c>
       <c r="P179" t="n">
         <v>1500</v>
@@ -9055,10 +9055,10 @@
         <v>82</v>
       </c>
       <c r="N202" t="n">
-        <v>2582.2551438323</v>
+        <v>2582.2551367187</v>
       </c>
       <c r="O202" t="n">
-        <v>211744.9217942486</v>
+        <v>211744.9212109334</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9147,10 +9147,10 @@
         <v>44</v>
       </c>
       <c r="N204" t="n">
-        <v>10603.665283541</v>
+        <v>10600</v>
       </c>
       <c r="O204" t="n">
-        <v>466561.272475804</v>
+        <v>466400</v>
       </c>
       <c r="P204" t="n">
         <v>17200</v>
@@ -9193,10 +9193,10 @@
         <v>38</v>
       </c>
       <c r="N205" t="n">
-        <v>5216.8959810174</v>
+        <v>5216.895979825</v>
       </c>
       <c r="O205" t="n">
-        <v>198242.0472786612</v>
+        <v>198242.04723335</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -9239,10 +9239,10 @@
         <v>6</v>
       </c>
       <c r="N206" t="n">
-        <v>2033.5022</v>
+        <v>2033.5002040816</v>
       </c>
       <c r="O206" t="n">
-        <v>12201.0132</v>
+        <v>12201.0012244896</v>
       </c>
       <c r="P206" t="n">
         <v>4100</v>
@@ -9511,10 +9511,10 @@
         <v>351</v>
       </c>
       <c r="N212" t="n">
-        <v>3158.8608348592</v>
+        <v>3158.8608362663</v>
       </c>
       <c r="O212" t="n">
-        <v>1108760.153035579</v>
+        <v>1108760.153529471</v>
       </c>
       <c r="P212" t="n">
         <v>5600</v>
@@ -9603,10 +9603,10 @@
         <v>116</v>
       </c>
       <c r="N214" t="n">
-        <v>3841.6250103093</v>
+        <v>3841.6250258532</v>
       </c>
       <c r="O214" t="n">
-        <v>445628.5011958788</v>
+        <v>445628.5029989712</v>
       </c>
       <c r="P214" t="n">
         <v>6900</v>
@@ -9923,10 +9923,10 @@
         <v>169</v>
       </c>
       <c r="N221" t="n">
-        <v>2694.823125</v>
+        <v>2694.8231119545</v>
       </c>
       <c r="O221" t="n">
-        <v>455425.108125</v>
+        <v>455425.1059203105</v>
       </c>
       <c r="P221" t="n">
         <v>4900</v>
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -10107,19 +10107,19 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="N225" t="n">
         <v>8796</v>
       </c>
       <c r="O225" t="n">
-        <v>413412</v>
+        <v>483780</v>
       </c>
       <c r="P225" t="n">
         <v>14900</v>
       </c>
       <c r="Q225" t="n">
-        <v>700300</v>
+        <v>819500</v>
       </c>
     </row>
     <row r="226">
@@ -11290,10 +11290,10 @@
         <v>32</v>
       </c>
       <c r="N251" t="n">
-        <v>3596.7580209059</v>
+        <v>3594.2532489451</v>
       </c>
       <c r="O251" t="n">
-        <v>115096.2566689888</v>
+        <v>115016.1039662432</v>
       </c>
       <c r="P251" t="n">
         <v>6500</v>
@@ -12230,10 +12230,10 @@
         <v>6</v>
       </c>
       <c r="N272" t="n">
-        <v>12422.462931554</v>
+        <v>12422.462939145</v>
       </c>
       <c r="O272" t="n">
-        <v>74534.777589324</v>
+        <v>74534.77763487</v>
       </c>
       <c r="P272" t="n">
         <v>19900</v>
@@ -12600,10 +12600,10 @@
         <v>6</v>
       </c>
       <c r="N280" t="n">
-        <v>4242.5422439024</v>
+        <v>4242.5422660099</v>
       </c>
       <c r="O280" t="n">
-        <v>25455.2534634144</v>
+        <v>25455.2535960594</v>
       </c>
       <c r="P280" t="n">
         <v>5900</v>
@@ -12690,10 +12690,10 @@
         <v>5</v>
       </c>
       <c r="N282" t="n">
-        <v>3041.6600138793</v>
+        <v>3041.6600139179</v>
       </c>
       <c r="O282" t="n">
-        <v>15208.3000693965</v>
+        <v>15208.3000695895</v>
       </c>
       <c r="P282" t="n">
         <v>5500</v>
@@ -12818,10 +12818,10 @@
         <v>11</v>
       </c>
       <c r="N285" t="n">
-        <v>4371.766707533</v>
+        <v>4371.1712622683</v>
       </c>
       <c r="O285" t="n">
-        <v>48089.433782863</v>
+        <v>48082.8838849513</v>
       </c>
       <c r="P285" t="n">
         <v>8900</v>
@@ -12896,7 +12896,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -12905,19 +12905,19 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N287" t="n">
         <v>6441.03</v>
       </c>
       <c r="O287" t="n">
-        <v>386461.8</v>
+        <v>483077.25</v>
       </c>
       <c r="P287" t="n">
         <v>10500</v>
       </c>
       <c r="Q287" t="n">
-        <v>630000</v>
+        <v>787500</v>
       </c>
     </row>
     <row r="288">
@@ -12954,10 +12954,10 @@
         <v>244</v>
       </c>
       <c r="N288" t="n">
-        <v>1592.5655172414</v>
+        <v>1592.5654664342</v>
       </c>
       <c r="O288" t="n">
-        <v>388585.9862069016</v>
+        <v>388585.9738099448</v>
       </c>
       <c r="P288" t="n">
         <v>3900</v>
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -13079,19 +13079,19 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N291" t="n">
         <v>5331.69</v>
       </c>
       <c r="O291" t="n">
-        <v>181277.46</v>
+        <v>223930.98</v>
       </c>
       <c r="P291" t="n">
         <v>7900</v>
       </c>
       <c r="Q291" t="n">
-        <v>268600</v>
+        <v>331800</v>
       </c>
     </row>
     <row r="292">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13125,19 +13125,19 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="N292" t="n">
         <v>4717</v>
       </c>
       <c r="O292" t="n">
-        <v>89623</v>
+        <v>429247</v>
       </c>
       <c r="P292" t="n">
         <v>7900</v>
       </c>
       <c r="Q292" t="n">
-        <v>150100</v>
+        <v>718900</v>
       </c>
     </row>
     <row r="293">
@@ -14914,10 +14914,10 @@
         <v>104</v>
       </c>
       <c r="N331" t="n">
-        <v>1151.3923553227</v>
+        <v>1151.3923688623</v>
       </c>
       <c r="O331" t="n">
-        <v>119744.8049535608</v>
+        <v>119744.8063616792</v>
       </c>
       <c r="P331" t="n">
         <v>1500</v>
@@ -15142,10 +15142,10 @@
         <v>220</v>
       </c>
       <c r="N336" t="n">
-        <v>1630.9242252747</v>
+        <v>1630.9242345815</v>
       </c>
       <c r="O336" t="n">
-        <v>358803.329560434</v>
+        <v>358803.33160793</v>
       </c>
       <c r="P336" t="n">
         <v>2500</v>
@@ -15234,10 +15234,10 @@
         <v>32</v>
       </c>
       <c r="N338" t="n">
-        <v>1690.5858435754</v>
+        <v>1690.5851822323</v>
       </c>
       <c r="O338" t="n">
-        <v>54098.7469944128</v>
+        <v>54098.7258314336</v>
       </c>
       <c r="P338" t="n">
         <v>2900</v>
@@ -15280,10 +15280,10 @@
         <v>675</v>
       </c>
       <c r="N339" t="n">
-        <v>1550.1943922358</v>
+        <v>1550.19440684</v>
       </c>
       <c r="O339" t="n">
-        <v>1046381.214759165</v>
+        <v>1046381.224617</v>
       </c>
       <c r="P339" t="n">
         <v>2500</v>
@@ -15326,10 +15326,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>1579.3858102767</v>
+        <v>1579.3856972112</v>
       </c>
       <c r="O340" t="n">
-        <v>1579.3858102767</v>
+        <v>1579.3856972112</v>
       </c>
       <c r="P340" t="n">
         <v>2900</v>
@@ -15372,10 +15372,10 @@
         <v>384</v>
       </c>
       <c r="N341" t="n">
-        <v>2403.5166025127</v>
+        <v>2403.516914488</v>
       </c>
       <c r="O341" t="n">
-        <v>922950.3753648768</v>
+        <v>922950.495163392</v>
       </c>
       <c r="P341" t="n">
         <v>3500</v>
@@ -15418,10 +15418,10 @@
         <v>5</v>
       </c>
       <c r="N342" t="n">
-        <v>2521.3983636364</v>
+        <v>2521.3785714286</v>
       </c>
       <c r="O342" t="n">
-        <v>12606.991818182</v>
+        <v>12606.892857143</v>
       </c>
       <c r="P342" t="n">
         <v>3900</v>
@@ -19483,10 +19483,10 @@
         <v>16</v>
       </c>
       <c r="N435" t="n">
-        <v>4285.1961426844</v>
+        <v>4285.1961725395</v>
       </c>
       <c r="O435" t="n">
-        <v>68563.1382829504</v>
+        <v>68563.13876063201</v>
       </c>
       <c r="P435" t="n">
         <v>6900</v>
@@ -19911,10 +19911,10 @@
         <v>11</v>
       </c>
       <c r="N445" t="n">
-        <v>4814.2679275122</v>
+        <v>4814.2679274047</v>
       </c>
       <c r="O445" t="n">
-        <v>52956.9472026342</v>
+        <v>52956.94720145169</v>
       </c>
       <c r="P445" t="n">
         <v>9900</v>
@@ -20822,10 +20822,10 @@
         <v>10</v>
       </c>
       <c r="N466" t="n">
-        <v>8332.779613402099</v>
+        <v>8332.779612403099</v>
       </c>
       <c r="O466" t="n">
-        <v>83327.79613402099</v>
+        <v>83327.796124031</v>
       </c>
       <c r="P466" t="n">
         <v>14900</v>
@@ -20955,10 +20955,10 @@
         <v>84</v>
       </c>
       <c r="N469" t="n">
-        <v>1561.003634439</v>
+        <v>1561.0036827195</v>
       </c>
       <c r="O469" t="n">
-        <v>131124.305292876</v>
+        <v>131124.309348438</v>
       </c>
       <c r="P469" t="n">
         <v>2900</v>
@@ -24240,10 +24240,10 @@
         <v>34</v>
       </c>
       <c r="N542" t="n">
-        <v>1664.3420823245</v>
+        <v>1664.3416707617</v>
       </c>
       <c r="O542" t="n">
-        <v>56587.630799033</v>
+        <v>56587.6168058978</v>
       </c>
       <c r="P542" t="n">
         <v>2900</v>
@@ -25034,10 +25034,10 @@
         <v>44</v>
       </c>
       <c r="N559" t="n">
-        <v>1778.4727855775</v>
+        <v>1778.47280077</v>
       </c>
       <c r="O559" t="n">
-        <v>78252.80256541001</v>
+        <v>78252.80323388</v>
       </c>
       <c r="P559" t="n">
         <v>4900</v>
@@ -25344,7 +25344,7 @@
         </is>
       </c>
       <c r="J566" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K566" t="n">
         <v>0</v>
@@ -25353,19 +25353,19 @@
         <v>0</v>
       </c>
       <c r="M566" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N566" t="n">
         <v>16058</v>
       </c>
       <c r="O566" t="n">
-        <v>160580</v>
+        <v>208754</v>
       </c>
       <c r="P566" t="n">
         <v>25900</v>
       </c>
       <c r="Q566" t="n">
-        <v>259000</v>
+        <v>336700</v>
       </c>
     </row>
     <row r="567">
@@ -26270,7 +26270,7 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
@@ -26279,19 +26279,19 @@
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="N586" t="n">
         <v>520</v>
       </c>
       <c r="O586" t="n">
-        <v>46800</v>
+        <v>53040</v>
       </c>
       <c r="P586" t="n">
         <v>850</v>
       </c>
       <c r="Q586" t="n">
-        <v>76500</v>
+        <v>86700</v>
       </c>
     </row>
     <row r="587">
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="J599" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="K599" t="n">
         <v>0</v>
@@ -26889,19 +26889,19 @@
         <v>0</v>
       </c>
       <c r="M599" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="N599" t="n">
         <v>13687</v>
       </c>
       <c r="O599" t="n">
-        <v>314801</v>
+        <v>520106</v>
       </c>
       <c r="P599" t="n">
         <v>21900</v>
       </c>
       <c r="Q599" t="n">
-        <v>503700</v>
+        <v>832200</v>
       </c>
     </row>
     <row r="600">
@@ -28969,10 +28969,10 @@
         <v>27</v>
       </c>
       <c r="N644" t="n">
-        <v>4907.8225298805</v>
+        <v>4907.82254</v>
       </c>
       <c r="O644" t="n">
-        <v>132511.2083067735</v>
+        <v>132511.20858</v>
       </c>
       <c r="P644" t="n">
         <v>8200</v>
@@ -29245,10 +29245,10 @@
         <v>85</v>
       </c>
       <c r="N650" t="n">
-        <v>3903.7388113695</v>
+        <v>3903.7388764045</v>
       </c>
       <c r="O650" t="n">
-        <v>331817.7989664075</v>
+        <v>331817.8044943825</v>
       </c>
       <c r="P650" t="n">
         <v>7500</v>
@@ -31316,10 +31316,10 @@
         <v>18</v>
       </c>
       <c r="N695" t="n">
-        <v>4268.7100574713</v>
+        <v>4268.7105294118</v>
       </c>
       <c r="O695" t="n">
-        <v>76836.7810344834</v>
+        <v>76836.7895294124</v>
       </c>
       <c r="P695" t="n">
         <v>6900</v>
@@ -32420,10 +32420,10 @@
         <v>56</v>
       </c>
       <c r="N719" t="n">
-        <v>1516.0387544268</v>
+        <v>1516.0387516479</v>
       </c>
       <c r="O719" t="n">
-        <v>84898.17024790081</v>
+        <v>84898.17009228239</v>
       </c>
       <c r="P719" t="n">
         <v>2300</v>
@@ -32694,10 +32694,10 @@
         <v>211</v>
       </c>
       <c r="N725" t="n">
-        <v>2079.3834145441</v>
+        <v>2079.3834072432</v>
       </c>
       <c r="O725" t="n">
-        <v>438749.9004688051</v>
+        <v>438749.8989283152</v>
       </c>
       <c r="P725" t="n">
         <v>2900</v>
@@ -32740,10 +32740,10 @@
         <v>110</v>
       </c>
       <c r="N726" t="n">
-        <v>1803.0163011152</v>
+        <v>1803.0163058036</v>
       </c>
       <c r="O726" t="n">
-        <v>198331.793122672</v>
+        <v>198331.793638396</v>
       </c>
       <c r="P726" t="n">
         <v>2500</v>
@@ -32786,10 +32786,10 @@
         <v>108</v>
       </c>
       <c r="N727" t="n">
-        <v>3306.5944700461</v>
+        <v>3306.5944615385</v>
       </c>
       <c r="O727" t="n">
-        <v>357112.2027649788</v>
+        <v>357112.201846158</v>
       </c>
       <c r="P727" t="n">
         <v>4900</v>
@@ -33016,10 +33016,10 @@
         <v>113</v>
       </c>
       <c r="N732" t="n">
-        <v>1655.9297327394</v>
+        <v>1655.9297098214</v>
       </c>
       <c r="O732" t="n">
-        <v>187120.0597995522</v>
+        <v>187120.0572098182</v>
       </c>
       <c r="P732" t="n">
         <v>2500</v>
@@ -33518,10 +33518,10 @@
         <v>13</v>
       </c>
       <c r="N743" t="n">
-        <v>3033.6906410256</v>
+        <v>3033.6882666667</v>
       </c>
       <c r="O743" t="n">
-        <v>39437.9783333328</v>
+        <v>39437.9474666671</v>
       </c>
       <c r="P743" t="n">
         <v>4500</v>
@@ -33610,10 +33610,10 @@
         <v>55</v>
       </c>
       <c r="N745" t="n">
-        <v>1668.6384251969</v>
+        <v>1668.6387301587</v>
       </c>
       <c r="O745" t="n">
-        <v>91775.11338582951</v>
+        <v>91775.1301587285</v>
       </c>
       <c r="P745" t="n">
         <v>2500</v>
@@ -34193,10 +34193,10 @@
         </is>
       </c>
       <c r="J758" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K758" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L758" t="n">
         <v>0</v>
@@ -35457,7 +35457,7 @@
         </is>
       </c>
       <c r="J785" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K785" t="n">
         <v>0</v>
@@ -35466,19 +35466,19 @@
         <v>0</v>
       </c>
       <c r="M785" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N785" t="n">
         <v>3629.36</v>
       </c>
       <c r="O785" t="n">
-        <v>54440.4</v>
+        <v>79845.92</v>
       </c>
       <c r="P785" t="n">
         <v>3900</v>
       </c>
       <c r="Q785" t="n">
-        <v>58500</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="786">
@@ -36823,10 +36823,10 @@
         <v>3</v>
       </c>
       <c r="N814" t="n">
-        <v>3907.5003418803</v>
+        <v>3907.5003448276</v>
       </c>
       <c r="O814" t="n">
-        <v>11722.5010256409</v>
+        <v>11722.5010344828</v>
       </c>
       <c r="P814" t="n">
         <v>3900</v>
@@ -37916,10 +37916,10 @@
         <v>1023</v>
       </c>
       <c r="N838" t="n">
-        <v>517.72052761748</v>
+        <v>517.29416017244</v>
       </c>
       <c r="O838" t="n">
-        <v>529628.099752682</v>
+        <v>529191.9258564061</v>
       </c>
       <c r="P838" t="n">
         <v>900</v>
@@ -38419,7 +38419,7 @@
         </is>
       </c>
       <c r="J849" t="n">
-        <v>171</v>
+        <v>297</v>
       </c>
       <c r="K849" t="n">
         <v>0</v>
@@ -38428,19 +38428,19 @@
         <v>0</v>
       </c>
       <c r="M849" t="n">
-        <v>171</v>
+        <v>297</v>
       </c>
       <c r="N849" t="n">
-        <v>3110.8390217391</v>
+        <v>3110.8380493577</v>
       </c>
       <c r="O849" t="n">
-        <v>531953.4727173861</v>
+        <v>923918.9006592369</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
       </c>
       <c r="Q849" t="n">
-        <v>769500</v>
+        <v>1336500</v>
       </c>
     </row>
     <row r="850">
@@ -38843,10 +38843,10 @@
         <v>983</v>
       </c>
       <c r="N858" t="n">
-        <v>703.86725350482</v>
+        <v>703.79482873668</v>
       </c>
       <c r="O858" t="n">
-        <v>691901.5101952381</v>
+        <v>691830.3166481564</v>
       </c>
       <c r="P858" t="n">
         <v>900</v>
@@ -42076,10 +42076,10 @@
         <v>14</v>
       </c>
       <c r="N926" t="n">
-        <v>9746.8802</v>
+        <v>9746.8802020202</v>
       </c>
       <c r="O926" t="n">
-        <v>136456.3228</v>
+        <v>136456.3228282828</v>
       </c>
       <c r="P926" t="n">
         <v>18500</v>
@@ -42404,7 +42404,7 @@
         </is>
       </c>
       <c r="J933" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K933" t="n">
         <v>0</v>
@@ -42413,19 +42413,19 @@
         <v>0</v>
       </c>
       <c r="M933" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N933" t="n">
         <v>2992.5720967742</v>
       </c>
       <c r="O933" t="n">
-        <v>77806.8745161292</v>
+        <v>95762.3070967744</v>
       </c>
       <c r="P933" t="n">
         <v>6000</v>
       </c>
       <c r="Q933" t="n">
-        <v>156000</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="934">
@@ -45565,10 +45565,10 @@
         <v>2</v>
       </c>
       <c r="N999" t="n">
-        <v>8975.6103797468</v>
+        <v>8919.16</v>
       </c>
       <c r="O999" t="n">
-        <v>17951.2207594936</v>
+        <v>17838.32</v>
       </c>
       <c r="P999" t="n">
         <v>10000</v>
@@ -46186,10 +46186,10 @@
         <v>85</v>
       </c>
       <c r="N1012" t="n">
-        <v>7046.939827363</v>
+        <v>7046.9398272138</v>
       </c>
       <c r="O1012" t="n">
-        <v>598989.885325855</v>
+        <v>598989.8853131729</v>
       </c>
       <c r="P1012" t="n">
         <v>9900</v>
@@ -48439,10 +48439,10 @@
         <v>9</v>
       </c>
       <c r="N1061" t="n">
-        <v>2523.3377457627</v>
+        <v>2523.3377451257</v>
       </c>
       <c r="O1061" t="n">
-        <v>22710.0397118643</v>
+        <v>22710.0397061313</v>
       </c>
       <c r="P1061" t="n">
         <v>2800</v>
@@ -48659,10 +48659,10 @@
         </is>
       </c>
       <c r="J1066" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K1066" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L1066" t="n">
         <v>0</v>
@@ -48720,10 +48720,10 @@
         <v>5</v>
       </c>
       <c r="N1067" t="n">
-        <v>5150.0503597122</v>
+        <v>5077</v>
       </c>
       <c r="O1067" t="n">
-        <v>25750.251798561</v>
+        <v>25385</v>
       </c>
       <c r="P1067" t="n">
         <v>8500</v>
@@ -50556,7 +50556,7 @@
         </is>
       </c>
       <c r="J1107" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K1107" t="n">
         <v>0</v>
@@ -50565,19 +50565,19 @@
         <v>0</v>
       </c>
       <c r="M1107" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N1107" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O1107" t="n">
-        <v>87373.71000000001</v>
+        <v>106790.09</v>
       </c>
       <c r="P1107" t="n">
         <v>10200</v>
       </c>
       <c r="Q1107" t="n">
-        <v>91800</v>
+        <v>112200</v>
       </c>
     </row>
     <row r="1108">
@@ -51016,7 +51016,7 @@
         </is>
       </c>
       <c r="J1117" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K1117" t="n">
         <v>0</v>
@@ -51025,19 +51025,19 @@
         <v>0</v>
       </c>
       <c r="M1117" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N1117" t="n">
         <v>17986.24</v>
       </c>
       <c r="O1117" t="n">
-        <v>89931.20000000001</v>
+        <v>143889.92</v>
       </c>
       <c r="P1117" t="n">
         <v>18500</v>
       </c>
       <c r="Q1117" t="n">
-        <v>92500</v>
+        <v>148000</v>
       </c>
     </row>
     <row r="1118">
@@ -51292,7 +51292,7 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
@@ -51301,19 +51301,19 @@
         <v>0</v>
       </c>
       <c r="M1123" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="N1123" t="n">
         <v>7480</v>
       </c>
       <c r="O1123" t="n">
-        <v>254320</v>
+        <v>433840</v>
       </c>
       <c r="P1123" t="n">
         <v>9500</v>
       </c>
       <c r="Q1123" t="n">
-        <v>323000</v>
+        <v>551000</v>
       </c>
     </row>
     <row r="1124">
@@ -51798,7 +51798,7 @@
         </is>
       </c>
       <c r="J1134" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K1134" t="n">
         <v>0</v>
@@ -51807,19 +51807,19 @@
         <v>0</v>
       </c>
       <c r="M1134" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N1134" t="n">
         <v>9240</v>
       </c>
       <c r="O1134" t="n">
-        <v>369600</v>
+        <v>554400</v>
       </c>
       <c r="P1134" t="n">
         <v>11500</v>
       </c>
       <c r="Q1134" t="n">
-        <v>460000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="1135">
@@ -53837,7 +53837,7 @@
         </is>
       </c>
       <c r="J1178" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K1178" t="n">
         <v>0</v>
@@ -53846,19 +53846,19 @@
         <v>0</v>
       </c>
       <c r="M1178" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="N1178" t="n">
         <v>1319.3609287926</v>
       </c>
       <c r="O1178" t="n">
-        <v>22429.1357894742</v>
+        <v>27706.5795046446</v>
       </c>
       <c r="P1178" t="n">
         <v>3500</v>
       </c>
       <c r="Q1178" t="n">
-        <v>59500</v>
+        <v>73500</v>
       </c>
     </row>
     <row r="1179">
@@ -53980,7 +53980,7 @@
         </is>
       </c>
       <c r="J1181" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K1181" t="n">
         <v>0</v>
@@ -53989,19 +53989,19 @@
         <v>0</v>
       </c>
       <c r="M1181" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="N1181" t="n">
         <v>571.87</v>
       </c>
       <c r="O1181" t="n">
-        <v>37171.55</v>
+        <v>42890.25</v>
       </c>
       <c r="P1181" t="n">
         <v>2500</v>
       </c>
       <c r="Q1181" t="n">
-        <v>162500</v>
+        <v>187500</v>
       </c>
     </row>
     <row r="1182">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -4244,10 +4244,10 @@
         <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>22267.552777778</v>
+        <v>26721.063333333</v>
       </c>
       <c r="O92" t="n">
-        <v>22267.552777778</v>
+        <v>26721.063333333</v>
       </c>
       <c r="P92" t="n">
         <v>46300</v>
@@ -4570,10 +4570,10 @@
         <v>6</v>
       </c>
       <c r="N99" t="n">
-        <v>141416.88462046</v>
+        <v>141885.15245033</v>
       </c>
       <c r="O99" t="n">
-        <v>848501.3077227601</v>
+        <v>851310.9147019801</v>
       </c>
       <c r="P99" t="n">
         <v>251900</v>
@@ -4612,10 +4612,10 @@
         <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>200072.20216981</v>
+        <v>201977.65171429</v>
       </c>
       <c r="O100" t="n">
-        <v>1000361.01084905</v>
+        <v>1009888.25857145</v>
       </c>
       <c r="P100" t="n">
         <v>312000</v>
@@ -9055,10 +9055,10 @@
         <v>82</v>
       </c>
       <c r="N202" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O202" t="n">
-        <v>211744.9212109334</v>
+        <v>211744.9207235418</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9690,10 +9690,10 @@
         <v>54</v>
       </c>
       <c r="N216" t="n">
-        <v>8214</v>
+        <v>8701.9603960396</v>
       </c>
       <c r="O216" t="n">
-        <v>443556</v>
+        <v>469905.8613861384</v>
       </c>
       <c r="P216" t="n">
         <v>7900</v>
@@ -14545,10 +14545,10 @@
         <v>13</v>
       </c>
       <c r="N323" t="n">
-        <v>11921.4</v>
+        <v>11949.761776368</v>
       </c>
       <c r="O323" t="n">
-        <v>154978.2</v>
+        <v>155346.903092784</v>
       </c>
       <c r="P323" t="n">
         <v>19900</v>
@@ -15142,10 +15142,10 @@
         <v>220</v>
       </c>
       <c r="N336" t="n">
-        <v>1630.9242345815</v>
+        <v>1630.9242415885</v>
       </c>
       <c r="O336" t="n">
-        <v>358803.33160793</v>
+        <v>358803.33314947</v>
       </c>
       <c r="P336" t="n">
         <v>2500</v>
@@ -15372,10 +15372,10 @@
         <v>384</v>
       </c>
       <c r="N341" t="n">
-        <v>2403.516914488</v>
+        <v>2403.5169237057</v>
       </c>
       <c r="O341" t="n">
-        <v>922950.495163392</v>
+        <v>922950.4987029887</v>
       </c>
       <c r="P341" t="n">
         <v>3500</v>
@@ -15418,10 +15418,10 @@
         <v>5</v>
       </c>
       <c r="N342" t="n">
-        <v>2521.3785714286</v>
+        <v>2521.3667391304</v>
       </c>
       <c r="O342" t="n">
-        <v>12606.892857143</v>
+        <v>12606.833695652</v>
       </c>
       <c r="P342" t="n">
         <v>3900</v>
@@ -19911,10 +19911,10 @@
         <v>11</v>
       </c>
       <c r="N445" t="n">
-        <v>4814.2679274047</v>
+        <v>4814.2679269747</v>
       </c>
       <c r="O445" t="n">
-        <v>52956.94720145169</v>
+        <v>52956.9471967217</v>
       </c>
       <c r="P445" t="n">
         <v>9900</v>
@@ -20735,10 +20735,10 @@
         <v>17</v>
       </c>
       <c r="N464" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="O464" t="n">
-        <v>288569.73</v>
+        <v>290340.096441718</v>
       </c>
       <c r="P464" t="n">
         <v>26900</v>
@@ -21611,10 +21611,10 @@
         <v>9</v>
       </c>
       <c r="N484" t="n">
-        <v>9627.34</v>
+        <v>11147.446315789</v>
       </c>
       <c r="O484" t="n">
-        <v>86646.06</v>
+        <v>100327.016842101</v>
       </c>
       <c r="P484" t="n">
         <v>15900</v>
@@ -23124,10 +23124,10 @@
         <v>104</v>
       </c>
       <c r="N518" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="O518" t="n">
-        <v>800800</v>
+        <v>812504.7503045097</v>
       </c>
       <c r="P518" t="n">
         <v>13900</v>
@@ -23538,10 +23538,10 @@
         <v>4</v>
       </c>
       <c r="N527" t="n">
-        <v>5218.1705812417</v>
+        <v>5218.1705827815</v>
       </c>
       <c r="O527" t="n">
-        <v>20872.6823249668</v>
+        <v>20872.682331126</v>
       </c>
       <c r="P527" t="n">
         <v>8500</v>
@@ -32420,10 +32420,10 @@
         <v>56</v>
       </c>
       <c r="N719" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O719" t="n">
-        <v>84898.17009228239</v>
+        <v>84898.1700781032</v>
       </c>
       <c r="P719" t="n">
         <v>2300</v>
@@ -33518,10 +33518,10 @@
         <v>13</v>
       </c>
       <c r="N743" t="n">
-        <v>3033.6882666667</v>
+        <v>3033.6856944444</v>
       </c>
       <c r="O743" t="n">
-        <v>39437.9474666671</v>
+        <v>39437.91402777719</v>
       </c>
       <c r="P743" t="n">
         <v>4500</v>
@@ -33610,10 +33610,10 @@
         <v>55</v>
       </c>
       <c r="N745" t="n">
-        <v>1668.6387301587</v>
+        <v>1668.64</v>
       </c>
       <c r="O745" t="n">
-        <v>91775.1301587285</v>
+        <v>91775.20000000001</v>
       </c>
       <c r="P745" t="n">
         <v>2500</v>
@@ -37916,10 +37916,10 @@
         <v>1023</v>
       </c>
       <c r="N838" t="n">
-        <v>517.29416017244</v>
+        <v>517.81142476254</v>
       </c>
       <c r="O838" t="n">
-        <v>529191.9258564061</v>
+        <v>529721.0875320784</v>
       </c>
       <c r="P838" t="n">
         <v>900</v>
@@ -38843,10 +38843,10 @@
         <v>983</v>
       </c>
       <c r="N858" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O858" t="n">
-        <v>691830.3166481564</v>
+        <v>691830.315862248</v>
       </c>
       <c r="P858" t="n">
         <v>900</v>
@@ -48222,10 +48222,10 @@
         <v>114</v>
       </c>
       <c r="N1056" t="n">
-        <v>3181.9</v>
+        <v>3248.0517671518</v>
       </c>
       <c r="O1056" t="n">
-        <v>362736.6</v>
+        <v>370277.9014553052</v>
       </c>
       <c r="P1056" t="n">
         <v>5100</v>
@@ -50246,10 +50246,10 @@
         <v>19</v>
       </c>
       <c r="N1100" t="n">
-        <v>3504.16</v>
+        <v>5649.5640816327</v>
       </c>
       <c r="O1100" t="n">
-        <v>66579.03999999999</v>
+        <v>107341.7175510213</v>
       </c>
       <c r="P1100" t="n">
         <v>3900</v>
@@ -50522,10 +50522,10 @@
         <v>61</v>
       </c>
       <c r="N1106" t="n">
-        <v>1952.66</v>
+        <v>1991.055</v>
       </c>
       <c r="O1106" t="n">
-        <v>119112.26</v>
+        <v>121454.355</v>
       </c>
       <c r="P1106" t="n">
         <v>3500</v>
@@ -51350,10 +51350,10 @@
         <v>48</v>
       </c>
       <c r="N1124" t="n">
-        <v>6336</v>
+        <v>6620.7640449438</v>
       </c>
       <c r="O1124" t="n">
-        <v>304128</v>
+        <v>317796.6741573024</v>
       </c>
       <c r="P1124" t="n">
         <v>7500</v>
@@ -53946,10 +53946,10 @@
         <v>61</v>
       </c>
       <c r="N1180" t="n">
-        <v>751.45</v>
+        <v>1093.0181818182</v>
       </c>
       <c r="O1180" t="n">
-        <v>45838.45</v>
+        <v>66674.10909091021</v>
       </c>
       <c r="P1180" t="n">
         <v>2500</v>
@@ -54792,10 +54792,10 @@
         <v>48</v>
       </c>
       <c r="N1198" t="n">
-        <v>4171.6685988024</v>
+        <v>4171.6685954382</v>
       </c>
       <c r="O1198" t="n">
-        <v>200240.0927425152</v>
+        <v>200240.0925810336</v>
       </c>
       <c r="P1198" t="n">
         <v>5000</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -3666,10 +3666,10 @@
         <v>7</v>
       </c>
       <c r="N78" t="n">
-        <v>16486.40779661</v>
+        <v>16486.407586207</v>
       </c>
       <c r="O78" t="n">
-        <v>115404.85457627</v>
+        <v>115404.853103449</v>
       </c>
       <c r="P78" t="n">
         <v>30500</v>
@@ -3708,10 +3708,10 @@
         <v>13</v>
       </c>
       <c r="N79" t="n">
-        <v>15711.964444444</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O79" t="n">
-        <v>204255.537777772</v>
+        <v>204255.536488094</v>
       </c>
       <c r="P79" t="n">
         <v>28500</v>
@@ -3802,10 +3802,10 @@
         <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>13712.841538462</v>
+        <v>13712.84</v>
       </c>
       <c r="O81" t="n">
-        <v>54851.366153848</v>
+        <v>54851.36</v>
       </c>
       <c r="P81" t="n">
         <v>22600</v>
@@ -4244,10 +4244,10 @@
         <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>26721.063333333</v>
+        <v>22267.553333333</v>
       </c>
       <c r="O92" t="n">
-        <v>26721.063333333</v>
+        <v>22267.553333333</v>
       </c>
       <c r="P92" t="n">
         <v>46300</v>
@@ -4570,10 +4570,10 @@
         <v>6</v>
       </c>
       <c r="N99" t="n">
-        <v>141885.15245033</v>
+        <v>141416.88463576</v>
       </c>
       <c r="O99" t="n">
-        <v>851310.9147019801</v>
+        <v>848501.3078145601</v>
       </c>
       <c r="P99" t="n">
         <v>251900</v>
@@ -4612,10 +4612,10 @@
         <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>201977.65171429</v>
+        <v>200072.20240385</v>
       </c>
       <c r="O100" t="n">
-        <v>1009888.25857145</v>
+        <v>1000361.01201925</v>
       </c>
       <c r="P100" t="n">
         <v>312000</v>
@@ -7617,10 +7617,10 @@
         <v>35</v>
       </c>
       <c r="N169" t="n">
-        <v>1950.2144208289</v>
+        <v>1950.2140408627</v>
       </c>
       <c r="O169" t="n">
-        <v>68257.5047290115</v>
+        <v>68257.4914301945</v>
       </c>
       <c r="P169" t="n">
         <v>2900</v>
@@ -7745,10 +7745,10 @@
         <v>108</v>
       </c>
       <c r="N172" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.3101659125</v>
       </c>
       <c r="O172" t="n">
-        <v>533229.497864658</v>
+        <v>533229.49791855</v>
       </c>
       <c r="P172" t="n">
         <v>7500</v>
@@ -8040,10 +8040,10 @@
         <v>316</v>
       </c>
       <c r="N179" t="n">
-        <v>1098.0632479443</v>
+        <v>1098.0633365079</v>
       </c>
       <c r="O179" t="n">
-        <v>346987.9863503988</v>
+        <v>346988.0143364964</v>
       </c>
       <c r="P179" t="n">
         <v>1500</v>
@@ -9055,10 +9055,10 @@
         <v>82</v>
       </c>
       <c r="N202" t="n">
-        <v>2582.2551307749</v>
+        <v>2582.2550693069</v>
       </c>
       <c r="O202" t="n">
-        <v>211744.9207235418</v>
+        <v>211744.9156831658</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9193,10 +9193,10 @@
         <v>38</v>
       </c>
       <c r="N205" t="n">
-        <v>5216.895979825</v>
+        <v>5216.8959750483</v>
       </c>
       <c r="O205" t="n">
-        <v>198242.04723335</v>
+        <v>198242.0470518354</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -9239,10 +9239,10 @@
         <v>6</v>
       </c>
       <c r="N206" t="n">
-        <v>2033.5002040816</v>
+        <v>2033.4991752577</v>
       </c>
       <c r="O206" t="n">
-        <v>12201.0012244896</v>
+        <v>12200.9950515462</v>
       </c>
       <c r="P206" t="n">
         <v>4100</v>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9687,19 +9687,19 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="N216" t="n">
-        <v>8701.9603960396</v>
+        <v>8214</v>
       </c>
       <c r="O216" t="n">
-        <v>469905.8613861384</v>
+        <v>640692</v>
       </c>
       <c r="P216" t="n">
         <v>7900</v>
       </c>
       <c r="Q216" t="n">
-        <v>426600</v>
+        <v>616200</v>
       </c>
     </row>
     <row r="217">
@@ -10514,10 +10514,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>4890.9300509879</v>
+        <v>4890.9300510856</v>
       </c>
       <c r="O234" t="n">
-        <v>58691.16061185481</v>
+        <v>58691.1606130272</v>
       </c>
       <c r="P234" t="n">
         <v>8200</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10747,19 +10747,19 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N239" t="n">
         <v>5888</v>
       </c>
       <c r="O239" t="n">
-        <v>41216</v>
+        <v>64768</v>
       </c>
       <c r="P239" t="n">
         <v>9500</v>
       </c>
       <c r="Q239" t="n">
-        <v>66500</v>
+        <v>104500</v>
       </c>
     </row>
     <row r="240">
@@ -10883,10 +10883,10 @@
         <v>81</v>
       </c>
       <c r="N242" t="n">
-        <v>2267.0481103035</v>
+        <v>2267.0481062554</v>
       </c>
       <c r="O242" t="n">
-        <v>183630.8969345835</v>
+        <v>183630.8966066874</v>
       </c>
       <c r="P242" t="n">
         <v>3900</v>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -11064,19 +11064,19 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N246" t="n">
         <v>8012</v>
       </c>
       <c r="O246" t="n">
-        <v>64096</v>
+        <v>80120</v>
       </c>
       <c r="P246" t="n">
         <v>13200</v>
       </c>
       <c r="Q246" t="n">
-        <v>105600</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="247">
@@ -11290,10 +11290,10 @@
         <v>32</v>
       </c>
       <c r="N251" t="n">
-        <v>3594.2532489451</v>
+        <v>3594.2532155477</v>
       </c>
       <c r="O251" t="n">
-        <v>115016.1039662432</v>
+        <v>115016.1028975264</v>
       </c>
       <c r="P251" t="n">
         <v>6500</v>
@@ -11462,10 +11462,10 @@
         <v>99</v>
       </c>
       <c r="N255" t="n">
-        <v>3240.8500492611</v>
+        <v>3240.8500493827</v>
       </c>
       <c r="O255" t="n">
-        <v>320844.1548768489</v>
+        <v>320844.1548888873</v>
       </c>
       <c r="P255" t="n">
         <v>5200</v>
@@ -12230,10 +12230,10 @@
         <v>6</v>
       </c>
       <c r="N272" t="n">
-        <v>12422.462939145</v>
+        <v>12422.462940415</v>
       </c>
       <c r="O272" t="n">
-        <v>74534.77763487</v>
+        <v>74534.77764248999</v>
       </c>
       <c r="P272" t="n">
         <v>19900</v>
@@ -12690,10 +12690,10 @@
         <v>5</v>
       </c>
       <c r="N282" t="n">
-        <v>3041.6600139179</v>
+        <v>3041.660013947</v>
       </c>
       <c r="O282" t="n">
-        <v>15208.3000695895</v>
+        <v>15208.300069735</v>
       </c>
       <c r="P282" t="n">
         <v>5500</v>
@@ -12818,10 +12818,10 @@
         <v>11</v>
       </c>
       <c r="N285" t="n">
-        <v>4371.1712622683</v>
+        <v>4371.1712623543</v>
       </c>
       <c r="O285" t="n">
-        <v>48082.8838849513</v>
+        <v>48082.8838858973</v>
       </c>
       <c r="P285" t="n">
         <v>8900</v>
@@ -12954,10 +12954,10 @@
         <v>244</v>
       </c>
       <c r="N288" t="n">
-        <v>1592.5654664342</v>
+        <v>1592.5654585153</v>
       </c>
       <c r="O288" t="n">
-        <v>388585.9738099448</v>
+        <v>388585.9718777332</v>
       </c>
       <c r="P288" t="n">
         <v>3900</v>
@@ -14035,10 +14035,10 @@
         <v>23</v>
       </c>
       <c r="N312" t="n">
-        <v>2021.7211300122</v>
+        <v>2021.7211313869</v>
       </c>
       <c r="O312" t="n">
-        <v>46499.5859902806</v>
+        <v>46499.5860218987</v>
       </c>
       <c r="P312" t="n">
         <v>2400</v>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14542,19 +14542,19 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N323" t="n">
-        <v>11949.761776368</v>
+        <v>11921.4</v>
       </c>
       <c r="O323" t="n">
-        <v>155346.903092784</v>
+        <v>190742.4</v>
       </c>
       <c r="P323" t="n">
         <v>19900</v>
       </c>
       <c r="Q323" t="n">
-        <v>258700</v>
+        <v>318400</v>
       </c>
     </row>
     <row r="324">
@@ -15142,10 +15142,10 @@
         <v>220</v>
       </c>
       <c r="N336" t="n">
-        <v>1630.9242415885</v>
+        <v>1630.9242710358</v>
       </c>
       <c r="O336" t="n">
-        <v>358803.33314947</v>
+        <v>358803.339627876</v>
       </c>
       <c r="P336" t="n">
         <v>2500</v>
@@ -15234,10 +15234,10 @@
         <v>32</v>
       </c>
       <c r="N338" t="n">
-        <v>1690.5851822323</v>
+        <v>1690.5835202864</v>
       </c>
       <c r="O338" t="n">
-        <v>54098.7258314336</v>
+        <v>54098.6726491648</v>
       </c>
       <c r="P338" t="n">
         <v>2900</v>
@@ -15280,10 +15280,10 @@
         <v>675</v>
       </c>
       <c r="N339" t="n">
-        <v>1550.19440684</v>
+        <v>1550.1944427152</v>
       </c>
       <c r="O339" t="n">
-        <v>1046381.224617</v>
+        <v>1046381.24883276</v>
       </c>
       <c r="P339" t="n">
         <v>2500</v>
@@ -15326,10 +15326,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>1579.3856972112</v>
+        <v>1579.38564</v>
       </c>
       <c r="O340" t="n">
-        <v>1579.3856972112</v>
+        <v>1579.38564</v>
       </c>
       <c r="P340" t="n">
         <v>2900</v>
@@ -15372,10 +15372,10 @@
         <v>384</v>
       </c>
       <c r="N341" t="n">
-        <v>2403.5169237057</v>
+        <v>2403.5172431982</v>
       </c>
       <c r="O341" t="n">
-        <v>922950.4987029887</v>
+        <v>922950.6213881088</v>
       </c>
       <c r="P341" t="n">
         <v>3500</v>
@@ -15418,10 +15418,10 @@
         <v>5</v>
       </c>
       <c r="N342" t="n">
-        <v>2521.3667391304</v>
+        <v>2521.33775</v>
       </c>
       <c r="O342" t="n">
-        <v>12606.833695652</v>
+        <v>12606.68875</v>
       </c>
       <c r="P342" t="n">
         <v>3900</v>
@@ -18070,7 +18070,7 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
@@ -18079,19 +18079,19 @@
         <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N402" t="n">
         <v>2610</v>
       </c>
       <c r="O402" t="n">
-        <v>36540</v>
+        <v>44370</v>
       </c>
       <c r="P402" t="n">
         <v>3200</v>
       </c>
       <c r="Q402" t="n">
-        <v>44800</v>
+        <v>54400</v>
       </c>
     </row>
     <row r="403">
@@ -18456,10 +18456,10 @@
         <v>178</v>
       </c>
       <c r="N411" t="n">
-        <v>2029.8740827436</v>
+        <v>2029.8740849673</v>
       </c>
       <c r="O411" t="n">
-        <v>361317.5867283608</v>
+        <v>361317.5871241794</v>
       </c>
       <c r="P411" t="n">
         <v>3600</v>
@@ -19483,10 +19483,10 @@
         <v>16</v>
       </c>
       <c r="N435" t="n">
-        <v>4285.1961725395</v>
+        <v>4285.1962026862</v>
       </c>
       <c r="O435" t="n">
-        <v>68563.13876063201</v>
+        <v>68563.1392429792</v>
       </c>
       <c r="P435" t="n">
         <v>6900</v>
@@ -20044,10 +20044,10 @@
         <v>12</v>
       </c>
       <c r="N448" t="n">
-        <v>13513.643333333</v>
+        <v>13513.643445378</v>
       </c>
       <c r="O448" t="n">
-        <v>162163.719999996</v>
+        <v>162163.721344536</v>
       </c>
       <c r="P448" t="n">
         <v>21900</v>
@@ -20090,10 +20090,10 @@
         <v>3</v>
       </c>
       <c r="N449" t="n">
-        <v>12005.159829787</v>
+        <v>12005.15982684</v>
       </c>
       <c r="O449" t="n">
-        <v>36015.479489361</v>
+        <v>36015.47948052</v>
       </c>
       <c r="P449" t="n">
         <v>19500</v>
@@ -20723,7 +20723,7 @@
         </is>
       </c>
       <c r="J464" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K464" t="n">
         <v>0</v>
@@ -20732,19 +20732,19 @@
         <v>0</v>
       </c>
       <c r="M464" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N464" t="n">
-        <v>17078.829202454</v>
+        <v>16974.69</v>
       </c>
       <c r="O464" t="n">
-        <v>290340.096441718</v>
+        <v>322519.11</v>
       </c>
       <c r="P464" t="n">
         <v>26900</v>
       </c>
       <c r="Q464" t="n">
-        <v>457300</v>
+        <v>511100</v>
       </c>
     </row>
     <row r="465">
@@ -21599,7 +21599,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -21608,19 +21608,19 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="N484" t="n">
-        <v>11147.446315789</v>
+        <v>9627.34</v>
       </c>
       <c r="O484" t="n">
-        <v>100327.016842101</v>
+        <v>317702.22</v>
       </c>
       <c r="P484" t="n">
         <v>15900</v>
       </c>
       <c r="Q484" t="n">
-        <v>143100</v>
+        <v>524700</v>
       </c>
     </row>
     <row r="485">
@@ -23112,7 +23112,7 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -23121,19 +23121,19 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="N518" t="n">
-        <v>7812.5456760049</v>
+        <v>7700</v>
       </c>
       <c r="O518" t="n">
-        <v>812504.7503045097</v>
+        <v>893200</v>
       </c>
       <c r="P518" t="n">
         <v>13900</v>
       </c>
       <c r="Q518" t="n">
-        <v>1445600</v>
+        <v>1612400</v>
       </c>
     </row>
     <row r="519">
@@ -23216,10 +23216,10 @@
         <v>33</v>
       </c>
       <c r="N520" t="n">
-        <v>3113.8900281294</v>
+        <v>3113.8900282885</v>
       </c>
       <c r="O520" t="n">
-        <v>102758.3709282702</v>
+        <v>102758.3709335205</v>
       </c>
       <c r="P520" t="n">
         <v>5000</v>
@@ -24240,10 +24240,10 @@
         <v>34</v>
       </c>
       <c r="N542" t="n">
-        <v>1664.3416707617</v>
+        <v>1664.3413895782</v>
       </c>
       <c r="O542" t="n">
-        <v>56587.6168058978</v>
+        <v>56587.6072456588</v>
       </c>
       <c r="P542" t="n">
         <v>2900</v>
@@ -27813,10 +27813,10 @@
         <v>174</v>
       </c>
       <c r="N619" t="n">
-        <v>2252.2978962963</v>
+        <v>2252.2979080119</v>
       </c>
       <c r="O619" t="n">
-        <v>391899.8339555562</v>
+        <v>391899.8359940706</v>
       </c>
       <c r="P619" t="n">
         <v>3900</v>
@@ -28405,7 +28405,7 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
@@ -28414,19 +28414,19 @@
         <v>0</v>
       </c>
       <c r="M632" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N632" t="n">
         <v>32332</v>
       </c>
       <c r="O632" t="n">
-        <v>161660</v>
+        <v>193992</v>
       </c>
       <c r="P632" t="n">
         <v>55900</v>
       </c>
       <c r="Q632" t="n">
-        <v>279500</v>
+        <v>335400</v>
       </c>
     </row>
     <row r="633">
@@ -28969,10 +28969,10 @@
         <v>27</v>
       </c>
       <c r="N644" t="n">
-        <v>4907.82254</v>
+        <v>4907.8225450902</v>
       </c>
       <c r="O644" t="n">
-        <v>132511.20858</v>
+        <v>132511.2087174354</v>
       </c>
       <c r="P644" t="n">
         <v>8200</v>
@@ -29233,7 +29233,7 @@
         </is>
       </c>
       <c r="J650" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="K650" t="n">
         <v>0</v>
@@ -29242,19 +29242,19 @@
         <v>0</v>
       </c>
       <c r="M650" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="N650" t="n">
-        <v>3903.7388764045</v>
+        <v>3903.7389254766</v>
       </c>
       <c r="O650" t="n">
-        <v>331817.8044943825</v>
+        <v>472352.4099826686</v>
       </c>
       <c r="P650" t="n">
         <v>7500</v>
       </c>
       <c r="Q650" t="n">
-        <v>637500</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="651">
@@ -30056,7 +30056,7 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K668" t="n">
         <v>0</v>
@@ -30065,19 +30065,19 @@
         <v>0</v>
       </c>
       <c r="M668" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N668" t="n">
         <v>3898</v>
       </c>
       <c r="O668" t="n">
-        <v>70164</v>
+        <v>187104</v>
       </c>
       <c r="P668" t="n">
         <v>6900</v>
       </c>
       <c r="Q668" t="n">
-        <v>124200</v>
+        <v>331200</v>
       </c>
     </row>
     <row r="669">
@@ -31672,7 +31672,7 @@
         </is>
       </c>
       <c r="J703" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K703" t="n">
         <v>0</v>
@@ -31681,19 +31681,19 @@
         <v>0</v>
       </c>
       <c r="M703" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N703" t="n">
         <v>3639.35</v>
       </c>
       <c r="O703" t="n">
-        <v>120098.55</v>
+        <v>131016.6</v>
       </c>
       <c r="P703" t="n">
         <v>7500</v>
       </c>
       <c r="Q703" t="n">
-        <v>247500</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="704">
@@ -32270,7 +32270,7 @@
         </is>
       </c>
       <c r="J716" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K716" t="n">
         <v>0</v>
@@ -32279,19 +32279,19 @@
         <v>0</v>
       </c>
       <c r="M716" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N716" t="n">
         <v>15223.06</v>
       </c>
       <c r="O716" t="n">
-        <v>45669.18</v>
+        <v>60892.24</v>
       </c>
       <c r="P716" t="n">
         <v>17500</v>
       </c>
       <c r="Q716" t="n">
-        <v>52500</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="717">
@@ -32556,10 +32556,10 @@
         <v>283</v>
       </c>
       <c r="N722" t="n">
-        <v>2458.5126365879</v>
+        <v>2458.5126313933</v>
       </c>
       <c r="O722" t="n">
-        <v>695759.0761543757</v>
+        <v>695759.074684304</v>
       </c>
       <c r="P722" t="n">
         <v>3500</v>
@@ -32602,10 +32602,10 @@
         <v>148</v>
       </c>
       <c r="N723" t="n">
-        <v>1907.3927252503</v>
+        <v>1907.3925257143</v>
       </c>
       <c r="O723" t="n">
-        <v>282294.1233370444</v>
+        <v>282294.0938057164</v>
       </c>
       <c r="P723" t="n">
         <v>2500</v>
@@ -32694,10 +32694,10 @@
         <v>211</v>
       </c>
       <c r="N725" t="n">
-        <v>2079.3834072432</v>
+        <v>2079.3833876946</v>
       </c>
       <c r="O725" t="n">
-        <v>438749.8989283152</v>
+        <v>438749.8948035606</v>
       </c>
       <c r="P725" t="n">
         <v>2900</v>
@@ -32740,10 +32740,10 @@
         <v>110</v>
       </c>
       <c r="N726" t="n">
-        <v>1803.0163058036</v>
+        <v>1803.0164892802</v>
       </c>
       <c r="O726" t="n">
-        <v>198331.793638396</v>
+        <v>198331.813820822</v>
       </c>
       <c r="P726" t="n">
         <v>2500</v>
@@ -32878,10 +32878,10 @@
         <v>73</v>
       </c>
       <c r="N729" t="n">
-        <v>2108.7956032172</v>
+        <v>2108.7956591928</v>
       </c>
       <c r="O729" t="n">
-        <v>153942.0790348556</v>
+        <v>153942.0831210744</v>
       </c>
       <c r="P729" t="n">
         <v>2900</v>
@@ -32924,10 +32924,10 @@
         <v>225</v>
       </c>
       <c r="N730" t="n">
-        <v>2056.0823271375</v>
+        <v>2056.0823128492</v>
       </c>
       <c r="O730" t="n">
-        <v>462618.5236059375</v>
+        <v>462618.5203910701</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
@@ -32970,10 +32970,10 @@
         <v>194</v>
       </c>
       <c r="N731" t="n">
-        <v>3224.5693668237</v>
+        <v>3224.5693815514</v>
       </c>
       <c r="O731" t="n">
-        <v>625566.4571637978</v>
+        <v>625566.4600209716</v>
       </c>
       <c r="P731" t="n">
         <v>4500</v>
@@ -33472,10 +33472,10 @@
         <v>19</v>
       </c>
       <c r="N742" t="n">
-        <v>1906.1788059701</v>
+        <v>1906.178</v>
       </c>
       <c r="O742" t="n">
-        <v>36217.3973134319</v>
+        <v>36217.38200000001</v>
       </c>
       <c r="P742" t="n">
         <v>2900</v>
@@ -33518,10 +33518,10 @@
         <v>13</v>
       </c>
       <c r="N743" t="n">
-        <v>3033.6856944444</v>
+        <v>3033.6715254237</v>
       </c>
       <c r="O743" t="n">
-        <v>39437.91402777719</v>
+        <v>39437.7298305081</v>
       </c>
       <c r="P743" t="n">
         <v>4500</v>
@@ -33610,10 +33610,10 @@
         <v>55</v>
       </c>
       <c r="N745" t="n">
-        <v>1668.64</v>
+        <v>1668.6406666667</v>
       </c>
       <c r="O745" t="n">
-        <v>91775.20000000001</v>
+        <v>91775.23666666851</v>
       </c>
       <c r="P745" t="n">
         <v>2500</v>
@@ -36297,10 +36297,10 @@
         <v>37</v>
       </c>
       <c r="N803" t="n">
-        <v>1690.870009298</v>
+        <v>1690.8700093371</v>
       </c>
       <c r="O803" t="n">
-        <v>62562.190344026</v>
+        <v>62562.19034547271</v>
       </c>
       <c r="P803" t="n">
         <v>3000</v>
@@ -36965,10 +36965,10 @@
         <v>494</v>
       </c>
       <c r="N817" t="n">
-        <v>711.33664937221</v>
+        <v>711.3366477489</v>
       </c>
       <c r="O817" t="n">
-        <v>351400.3047898717</v>
+        <v>351400.3039879566</v>
       </c>
       <c r="P817" t="n">
         <v>900</v>
@@ -37818,10 +37818,10 @@
         <v>22</v>
       </c>
       <c r="N836" t="n">
-        <v>4032.396796875</v>
+        <v>4032.3967885117</v>
       </c>
       <c r="O836" t="n">
-        <v>88712.72953124999</v>
+        <v>88712.72934725739</v>
       </c>
       <c r="P836" t="n">
         <v>4200</v>
@@ -37916,10 +37916,10 @@
         <v>1023</v>
       </c>
       <c r="N838" t="n">
-        <v>517.81142476254</v>
+        <v>517.29429288703</v>
       </c>
       <c r="O838" t="n">
-        <v>529721.0875320784</v>
+        <v>529192.0616234317</v>
       </c>
       <c r="P838" t="n">
         <v>900</v>
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="J847" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K847" t="n">
         <v>0</v>
@@ -38333,19 +38333,19 @@
         <v>0</v>
       </c>
       <c r="M847" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N847" t="n">
         <v>3259.1344047619</v>
       </c>
       <c r="O847" t="n">
-        <v>55405.2848809523</v>
+        <v>74960.0913095237</v>
       </c>
       <c r="P847" t="n">
         <v>3600</v>
       </c>
       <c r="Q847" t="n">
-        <v>61200</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="848">
@@ -38431,10 +38431,10 @@
         <v>297</v>
       </c>
       <c r="N849" t="n">
-        <v>3110.8380493577</v>
+        <v>3110.8379516019</v>
       </c>
       <c r="O849" t="n">
-        <v>923918.9006592369</v>
+        <v>923918.8716257643</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
@@ -38799,10 +38799,10 @@
         <v>27</v>
       </c>
       <c r="N857" t="n">
-        <v>3002.0210014306</v>
+        <v>3002.0210028653</v>
       </c>
       <c r="O857" t="n">
-        <v>81054.56703862619</v>
+        <v>81054.5670773631</v>
       </c>
       <c r="P857" t="n">
         <v>4500</v>
@@ -38843,10 +38843,10 @@
         <v>983</v>
       </c>
       <c r="N858" t="n">
-        <v>703.79482793718</v>
+        <v>703.79482106458</v>
       </c>
       <c r="O858" t="n">
-        <v>691830.315862248</v>
+        <v>691830.3091064821</v>
       </c>
       <c r="P858" t="n">
         <v>900</v>
@@ -43031,10 +43031,10 @@
         <v>16</v>
       </c>
       <c r="N946" t="n">
-        <v>3067.0906122449</v>
+        <v>3067.0906143345</v>
       </c>
       <c r="O946" t="n">
-        <v>49073.4497959184</v>
+        <v>49073.449829352</v>
       </c>
       <c r="P946" t="n">
         <v>7200</v>
@@ -43611,10 +43611,10 @@
         <v>12</v>
       </c>
       <c r="N958" t="n">
-        <v>1783.7988756856</v>
+        <v>1783.7988736264</v>
       </c>
       <c r="O958" t="n">
-        <v>21405.5865082272</v>
+        <v>21405.5864835168</v>
       </c>
       <c r="P958" t="n">
         <v>1500</v>
@@ -44191,10 +44191,10 @@
         <v>2253</v>
       </c>
       <c r="N970" t="n">
-        <v>286.61333044868</v>
+        <v>286.61335546613</v>
       </c>
       <c r="O970" t="n">
-        <v>645739.8335008761</v>
+        <v>645739.8898651908</v>
       </c>
       <c r="P970" t="n">
         <v>350</v>
@@ -47347,10 +47347,10 @@
         <v>126</v>
       </c>
       <c r="N1036" t="n">
-        <v>465.8709683605</v>
+        <v>465.8709970385</v>
       </c>
       <c r="O1036" t="n">
-        <v>58699.742013423</v>
+        <v>58699.745626851</v>
       </c>
       <c r="P1036" t="n">
         <v>2500</v>
@@ -47607,10 +47607,10 @@
         <v>597</v>
       </c>
       <c r="N1042" t="n">
-        <v>704.8968946963899</v>
+        <v>704.89694272446</v>
       </c>
       <c r="O1042" t="n">
-        <v>420823.4461337448</v>
+        <v>420823.4748065026</v>
       </c>
       <c r="P1042" t="n">
         <v>900</v>
@@ -48210,7 +48210,7 @@
         </is>
       </c>
       <c r="J1056" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="K1056" t="n">
         <v>0</v>
@@ -48219,19 +48219,19 @@
         <v>0</v>
       </c>
       <c r="M1056" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="N1056" t="n">
-        <v>3248.0517671518</v>
+        <v>3181.9</v>
       </c>
       <c r="O1056" t="n">
-        <v>370277.9014553052</v>
+        <v>490012.6</v>
       </c>
       <c r="P1056" t="n">
         <v>5100</v>
       </c>
       <c r="Q1056" t="n">
-        <v>581400</v>
+        <v>785400</v>
       </c>
     </row>
     <row r="1057">
@@ -48307,10 +48307,10 @@
         <v>50</v>
       </c>
       <c r="N1058" t="n">
-        <v>1794.287966004</v>
+        <v>1794.2879651247</v>
       </c>
       <c r="O1058" t="n">
-        <v>89714.3983002</v>
+        <v>89714.398256235</v>
       </c>
       <c r="P1058" t="n">
         <v>1600</v>
@@ -48351,10 +48351,10 @@
         <v>4</v>
       </c>
       <c r="N1059" t="n">
-        <v>2830.2251488095</v>
+        <v>2830.2251641791</v>
       </c>
       <c r="O1059" t="n">
-        <v>11320.900595238</v>
+        <v>11320.9006567164</v>
       </c>
       <c r="P1059" t="n">
         <v>2400</v>
@@ -48439,10 +48439,10 @@
         <v>9</v>
       </c>
       <c r="N1061" t="n">
-        <v>2523.3377451257</v>
+        <v>2523.3377380952</v>
       </c>
       <c r="O1061" t="n">
-        <v>22710.0397061313</v>
+        <v>22710.0396428568</v>
       </c>
       <c r="P1061" t="n">
         <v>2800</v>
@@ -50234,7 +50234,7 @@
         </is>
       </c>
       <c r="J1100" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="K1100" t="n">
         <v>0</v>
@@ -50243,19 +50243,19 @@
         <v>0</v>
       </c>
       <c r="M1100" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="N1100" t="n">
-        <v>5649.5640816327</v>
+        <v>3504.16</v>
       </c>
       <c r="O1100" t="n">
-        <v>107341.7175510213</v>
+        <v>171703.84</v>
       </c>
       <c r="P1100" t="n">
         <v>3900</v>
       </c>
       <c r="Q1100" t="n">
-        <v>74100</v>
+        <v>191100</v>
       </c>
     </row>
     <row r="1101">
@@ -50464,7 +50464,7 @@
         </is>
       </c>
       <c r="J1105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K1105" t="n">
         <v>0</v>
@@ -50473,19 +50473,19 @@
         <v>0</v>
       </c>
       <c r="M1105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N1105" t="n">
         <v>14576.2</v>
       </c>
       <c r="O1105" t="n">
-        <v>87457.20000000001</v>
+        <v>102033.4</v>
       </c>
       <c r="P1105" t="n">
         <v>19000</v>
       </c>
       <c r="Q1105" t="n">
-        <v>114000</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="1106">
@@ -50510,7 +50510,7 @@
         </is>
       </c>
       <c r="J1106" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="K1106" t="n">
         <v>0</v>
@@ -50519,19 +50519,19 @@
         <v>0</v>
       </c>
       <c r="M1106" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="N1106" t="n">
-        <v>1991.055</v>
+        <v>1952.66</v>
       </c>
       <c r="O1106" t="n">
-        <v>121454.355</v>
+        <v>146449.5</v>
       </c>
       <c r="P1106" t="n">
         <v>3500</v>
       </c>
       <c r="Q1106" t="n">
-        <v>213500</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="1107">
@@ -51350,10 +51350,10 @@
         <v>48</v>
       </c>
       <c r="N1124" t="n">
-        <v>6620.7640449438</v>
+        <v>6336</v>
       </c>
       <c r="O1124" t="n">
-        <v>317796.6741573024</v>
+        <v>304128</v>
       </c>
       <c r="P1124" t="n">
         <v>7500</v>
@@ -51384,7 +51384,7 @@
         </is>
       </c>
       <c r="J1125" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K1125" t="n">
         <v>0</v>
@@ -51393,19 +51393,19 @@
         <v>0</v>
       </c>
       <c r="M1125" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N1125" t="n">
         <v>5280</v>
       </c>
       <c r="O1125" t="n">
-        <v>121440</v>
+        <v>153120</v>
       </c>
       <c r="P1125" t="n">
         <v>6900</v>
       </c>
       <c r="Q1125" t="n">
-        <v>158700</v>
+        <v>200100</v>
       </c>
     </row>
     <row r="1126">
@@ -52856,7 +52856,7 @@
         </is>
       </c>
       <c r="J1157" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K1157" t="n">
         <v>0</v>
@@ -52865,19 +52865,19 @@
         <v>0</v>
       </c>
       <c r="M1157" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="N1157" t="n">
         <v>415.07</v>
       </c>
       <c r="O1157" t="n">
-        <v>15357.59</v>
+        <v>18263.08</v>
       </c>
       <c r="P1157" t="n">
         <v>2900</v>
       </c>
       <c r="Q1157" t="n">
-        <v>107300</v>
+        <v>127600</v>
       </c>
     </row>
     <row r="1158">
@@ -53178,7 +53178,7 @@
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
@@ -53187,19 +53187,19 @@
         <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N1164" t="n">
         <v>910.85</v>
       </c>
       <c r="O1164" t="n">
-        <v>5465.1</v>
+        <v>8197.65</v>
       </c>
       <c r="P1164" t="n">
         <v>7900</v>
       </c>
       <c r="Q1164" t="n">
-        <v>47400</v>
+        <v>71100</v>
       </c>
     </row>
     <row r="1165">
@@ -53934,7 +53934,7 @@
         </is>
       </c>
       <c r="J1180" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="K1180" t="n">
         <v>0</v>
@@ -53943,19 +53943,19 @@
         <v>0</v>
       </c>
       <c r="M1180" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="N1180" t="n">
-        <v>1093.0181818182</v>
+        <v>751.45</v>
       </c>
       <c r="O1180" t="n">
-        <v>66674.10909091021</v>
+        <v>68381.95</v>
       </c>
       <c r="P1180" t="n">
         <v>2500</v>
       </c>
       <c r="Q1180" t="n">
-        <v>152500</v>
+        <v>227500</v>
       </c>
     </row>
     <row r="1181">
@@ -54792,10 +54792,10 @@
         <v>48</v>
       </c>
       <c r="N1198" t="n">
-        <v>4171.6685954382</v>
+        <v>4171.6685869565</v>
       </c>
       <c r="O1198" t="n">
-        <v>200240.0925810336</v>
+        <v>200240.092173912</v>
       </c>
       <c r="P1198" t="n">
         <v>5000</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -944,10 +944,10 @@
         <v>26</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3087912088</v>
+        <v>1811.3088176353</v>
       </c>
       <c r="O13" t="n">
-        <v>47094.0285714288</v>
+        <v>47094.0292585178</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1376,10 +1376,10 @@
         <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>15970.739066667</v>
+        <v>15970.739014085</v>
       </c>
       <c r="O24" t="n">
-        <v>143736.651600003</v>
+        <v>143736.651126765</v>
       </c>
       <c r="P24" t="n">
         <v>26900</v>
@@ -3666,10 +3666,10 @@
         <v>7</v>
       </c>
       <c r="N78" t="n">
-        <v>16486.407586207</v>
+        <v>16486.407256637</v>
       </c>
       <c r="O78" t="n">
-        <v>115404.853103449</v>
+        <v>115404.850796459</v>
       </c>
       <c r="P78" t="n">
         <v>30500</v>
@@ -3802,10 +3802,10 @@
         <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>13712.84</v>
+        <v>13712.837142857</v>
       </c>
       <c r="O81" t="n">
-        <v>54851.36</v>
+        <v>54851.348571428</v>
       </c>
       <c r="P81" t="n">
         <v>22600</v>
@@ -8040,10 +8040,10 @@
         <v>316</v>
       </c>
       <c r="N179" t="n">
-        <v>1098.0633365079</v>
+        <v>1098.0633810433</v>
       </c>
       <c r="O179" t="n">
-        <v>346988.0143364964</v>
+        <v>346988.0284096828</v>
       </c>
       <c r="P179" t="n">
         <v>1500</v>
@@ -9511,10 +9511,10 @@
         <v>351</v>
       </c>
       <c r="N212" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O212" t="n">
-        <v>1108760.153529471</v>
+        <v>1108760.153762465</v>
       </c>
       <c r="P212" t="n">
         <v>5600</v>
@@ -10289,10 +10289,10 @@
         <v>34</v>
       </c>
       <c r="N229" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O229" t="n">
-        <v>129054.1402588998</v>
+        <v>129054.1402589474</v>
       </c>
       <c r="P229" t="n">
         <v>6200</v>
@@ -10883,10 +10883,10 @@
         <v>81</v>
       </c>
       <c r="N242" t="n">
-        <v>2267.0481062554</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O242" t="n">
-        <v>183630.8966066874</v>
+        <v>183630.8962773738</v>
       </c>
       <c r="P242" t="n">
         <v>3900</v>
@@ -12954,10 +12954,10 @@
         <v>244</v>
       </c>
       <c r="N288" t="n">
-        <v>1592.5654585153</v>
+        <v>1592.5654545455</v>
       </c>
       <c r="O288" t="n">
-        <v>388585.9718777332</v>
+        <v>388585.970909102</v>
       </c>
       <c r="P288" t="n">
         <v>3900</v>
@@ -15280,10 +15280,10 @@
         <v>675</v>
       </c>
       <c r="N339" t="n">
-        <v>1550.1944427152</v>
+        <v>1550.1944587288</v>
       </c>
       <c r="O339" t="n">
-        <v>1046381.24883276</v>
+        <v>1046381.25964194</v>
       </c>
       <c r="P339" t="n">
         <v>2500</v>
@@ -15326,10 +15326,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>1579.38564</v>
+        <v>1579.3847234043</v>
       </c>
       <c r="O340" t="n">
-        <v>1579.38564</v>
+        <v>1579.3847234043</v>
       </c>
       <c r="P340" t="n">
         <v>2900</v>
@@ -15372,10 +15372,10 @@
         <v>384</v>
       </c>
       <c r="N341" t="n">
-        <v>2403.5172431982</v>
+        <v>2403.5172815804</v>
       </c>
       <c r="O341" t="n">
-        <v>922950.6213881088</v>
+        <v>922950.6361268735</v>
       </c>
       <c r="P341" t="n">
         <v>3500</v>
@@ -15418,10 +15418,10 @@
         <v>5</v>
       </c>
       <c r="N342" t="n">
-        <v>2521.33775</v>
+        <v>2521.3197297297</v>
       </c>
       <c r="O342" t="n">
-        <v>12606.68875</v>
+        <v>12606.5986486485</v>
       </c>
       <c r="P342" t="n">
         <v>3900</v>
@@ -15495,10 +15495,10 @@
         <v>59</v>
       </c>
       <c r="N344" t="n">
-        <v>1232.8060309278</v>
+        <v>1232.8059585492</v>
       </c>
       <c r="O344" t="n">
-        <v>72735.55582474021</v>
+        <v>72735.5515544028</v>
       </c>
       <c r="P344" t="n">
         <v>2400</v>
@@ -16617,10 +16617,10 @@
         <v>5</v>
       </c>
       <c r="N369" t="n">
-        <v>204.05094594595</v>
+        <v>204.05098591549</v>
       </c>
       <c r="O369" t="n">
-        <v>1020.25472972975</v>
+        <v>1020.25492957745</v>
       </c>
       <c r="P369" t="n">
         <v>500</v>
@@ -18456,10 +18456,10 @@
         <v>178</v>
       </c>
       <c r="N411" t="n">
-        <v>2029.8740849673</v>
+        <v>2029.874091653</v>
       </c>
       <c r="O411" t="n">
-        <v>361317.5871241794</v>
+        <v>361317.588314234</v>
       </c>
       <c r="P411" t="n">
         <v>3600</v>
@@ -20090,10 +20090,10 @@
         <v>3</v>
       </c>
       <c r="N449" t="n">
-        <v>12005.15982684</v>
+        <v>12005.159823789</v>
       </c>
       <c r="O449" t="n">
-        <v>36015.47948052</v>
+        <v>36015.479471367</v>
       </c>
       <c r="P449" t="n">
         <v>19500</v>
@@ -28969,10 +28969,10 @@
         <v>27</v>
       </c>
       <c r="N644" t="n">
-        <v>4907.8225450902</v>
+        <v>4907.8225656566</v>
       </c>
       <c r="O644" t="n">
-        <v>132511.2087174354</v>
+        <v>132511.2092727282</v>
       </c>
       <c r="P644" t="n">
         <v>8200</v>
@@ -32420,10 +32420,10 @@
         <v>56</v>
       </c>
       <c r="N719" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O719" t="n">
-        <v>84898.1700781032</v>
+        <v>84898.17004972241</v>
       </c>
       <c r="P719" t="n">
         <v>2300</v>
@@ -32740,10 +32740,10 @@
         <v>110</v>
       </c>
       <c r="N726" t="n">
-        <v>1803.0164892802</v>
+        <v>1803.016504221</v>
       </c>
       <c r="O726" t="n">
-        <v>198331.813820822</v>
+        <v>198331.81546431</v>
       </c>
       <c r="P726" t="n">
         <v>2500</v>
@@ -32924,10 +32924,10 @@
         <v>225</v>
       </c>
       <c r="N730" t="n">
-        <v>2056.0823128492</v>
+        <v>2056.0822725571</v>
       </c>
       <c r="O730" t="n">
-        <v>462618.5203910701</v>
+        <v>462618.5113253475</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
@@ -33656,10 +33656,10 @@
         <v>133</v>
       </c>
       <c r="N746" t="n">
-        <v>2546.982132964</v>
+        <v>2546.9817919075</v>
       </c>
       <c r="O746" t="n">
-        <v>338748.623684212</v>
+        <v>338748.5783236975</v>
       </c>
       <c r="P746" t="n">
         <v>3900</v>
@@ -37916,10 +37916,10 @@
         <v>1023</v>
       </c>
       <c r="N838" t="n">
-        <v>517.29429288703</v>
+        <v>517.29430006698</v>
       </c>
       <c r="O838" t="n">
-        <v>529192.0616234317</v>
+        <v>529192.0689685205</v>
       </c>
       <c r="P838" t="n">
         <v>900</v>
@@ -43611,10 +43611,10 @@
         <v>12</v>
       </c>
       <c r="N958" t="n">
-        <v>1783.7988736264</v>
+        <v>1783.7988731104</v>
       </c>
       <c r="O958" t="n">
-        <v>21405.5864835168</v>
+        <v>21405.5864773248</v>
       </c>
       <c r="P958" t="n">
         <v>1500</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -3621,22 +3621,22 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N77" t="n">
-        <v>16486.407256637</v>
+        <v>16486.407142857</v>
       </c>
       <c r="O77" t="n">
-        <v>115404.850796459</v>
+        <v>98918.44285714198</v>
       </c>
       <c r="P77" t="n">
         <v>30500</v>
       </c>
       <c r="Q77" t="n">
-        <v>213500</v>
+        <v>183000</v>
       </c>
     </row>
     <row r="78">
@@ -7572,22 +7572,22 @@
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M168" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N168" t="n">
-        <v>1950.2139862543</v>
+        <v>1950.2139585731</v>
       </c>
       <c r="O168" t="n">
-        <v>66307.27553264619</v>
+        <v>62406.8466743392</v>
       </c>
       <c r="P168" t="n">
         <v>2900</v>
       </c>
       <c r="Q168" t="n">
-        <v>98600</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="169">
@@ -7706,10 +7706,10 @@
         <v>108</v>
       </c>
       <c r="N171" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.310165538</v>
       </c>
       <c r="O171" t="n">
-        <v>533229.497864658</v>
+        <v>533229.497878104</v>
       </c>
       <c r="P171" t="n">
         <v>7500</v>
@@ -7823,22 +7823,22 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N174" t="n">
         <v>3456.13</v>
       </c>
       <c r="O174" t="n">
-        <v>38017.43</v>
+        <v>34561.3</v>
       </c>
       <c r="P174" t="n">
         <v>5700</v>
       </c>
       <c r="Q174" t="n">
-        <v>62700</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="175">
@@ -8447,10 +8447,10 @@
         <v>10</v>
       </c>
       <c r="N188" t="n">
-        <v>13593.35</v>
+        <v>13626.343567961</v>
       </c>
       <c r="O188" t="n">
-        <v>135933.5</v>
+        <v>136263.43567961</v>
       </c>
       <c r="P188" t="n">
         <v>25500</v>
@@ -9016,10 +9016,10 @@
         <v>82</v>
       </c>
       <c r="N201" t="n">
-        <v>2582.2550509317</v>
+        <v>2582.2550435432</v>
       </c>
       <c r="O201" t="n">
-        <v>211744.9141763994</v>
+        <v>211744.9135705424</v>
       </c>
       <c r="P201" t="n">
         <v>4500</v>
@@ -9154,10 +9154,10 @@
         <v>38</v>
       </c>
       <c r="N204" t="n">
-        <v>5216.8959642591</v>
+        <v>5220.0054239309</v>
       </c>
       <c r="O204" t="n">
-        <v>198242.0466418458</v>
+        <v>198360.2061093742</v>
       </c>
       <c r="P204" t="n">
         <v>8500</v>
@@ -10163,10 +10163,10 @@
         <v>25</v>
       </c>
       <c r="N226" t="n">
-        <v>6507</v>
+        <v>6513.4596293845</v>
       </c>
       <c r="O226" t="n">
-        <v>162675</v>
+        <v>162836.4907346125</v>
       </c>
       <c r="P226" t="n">
         <v>9900</v>
@@ -10890,10 +10890,10 @@
         <v>1</v>
       </c>
       <c r="N242" t="n">
-        <v>7041</v>
+        <v>7062.9802289282</v>
       </c>
       <c r="O242" t="n">
-        <v>7041</v>
+        <v>7062.9802289282</v>
       </c>
       <c r="P242" t="n">
         <v>11500</v>
@@ -11028,10 +11028,10 @@
         <v>10</v>
       </c>
       <c r="N245" t="n">
-        <v>8012</v>
+        <v>8051.1465798046</v>
       </c>
       <c r="O245" t="n">
-        <v>80120</v>
+        <v>80511.465798046</v>
       </c>
       <c r="P245" t="n">
         <v>13200</v>
@@ -11074,10 +11074,10 @@
         <v>6</v>
       </c>
       <c r="N246" t="n">
-        <v>8662</v>
+        <v>8680.102403343801</v>
       </c>
       <c r="O246" t="n">
-        <v>51972</v>
+        <v>52080.6144200628</v>
       </c>
       <c r="P246" t="n">
         <v>14200</v>
@@ -11245,22 +11245,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N250" t="n">
-        <v>3594.2531526391</v>
+        <v>3594.2531477516</v>
       </c>
       <c r="O250" t="n">
-        <v>100639.0882738948</v>
+        <v>97044.8349892932</v>
       </c>
       <c r="P250" t="n">
         <v>6500</v>
       </c>
       <c r="Q250" t="n">
-        <v>182000</v>
+        <v>175500</v>
       </c>
     </row>
     <row r="251">
@@ -11607,10 +11607,10 @@
         <v>10</v>
       </c>
       <c r="N258" t="n">
-        <v>14822.378827839</v>
+        <v>14840.499095355</v>
       </c>
       <c r="O258" t="n">
-        <v>148223.78827839</v>
+        <v>148404.99095355</v>
       </c>
       <c r="P258" t="n">
         <v>24900</v>
@@ -12009,10 +12009,10 @@
         <v>46</v>
       </c>
       <c r="N267" t="n">
-        <v>2665.4</v>
+        <v>2668.7380087664</v>
       </c>
       <c r="O267" t="n">
-        <v>122608.4</v>
+        <v>122761.9484032544</v>
       </c>
       <c r="P267" t="n">
         <v>20900</v>
@@ -12915,10 +12915,10 @@
         <v>243</v>
       </c>
       <c r="N287" t="n">
-        <v>1592.5653777778</v>
+        <v>1592.5653736655</v>
       </c>
       <c r="O287" t="n">
-        <v>386993.3868000054</v>
+        <v>386993.3858007165</v>
       </c>
       <c r="P287" t="n">
         <v>3900</v>
@@ -13266,10 +13266,10 @@
         <v>31</v>
       </c>
       <c r="N295" t="n">
-        <v>6242.93</v>
+        <v>6260.7161253561</v>
       </c>
       <c r="O295" t="n">
-        <v>193530.83</v>
+        <v>194082.1998860391</v>
       </c>
       <c r="P295" t="n">
         <v>10400</v>
@@ -15011,10 +15011,10 @@
         <v>7</v>
       </c>
       <c r="N333" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="O333" t="n">
-        <v>69321</v>
+        <v>69429.31406250001</v>
       </c>
       <c r="P333" t="n">
         <v>15900</v>
@@ -15103,10 +15103,10 @@
         <v>220</v>
       </c>
       <c r="N335" t="n">
-        <v>1630.9243202247</v>
+        <v>1630.9243287363</v>
       </c>
       <c r="O335" t="n">
-        <v>358803.350449434</v>
+        <v>358803.352321986</v>
       </c>
       <c r="P335" t="n">
         <v>2500</v>
@@ -15235,22 +15235,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M338" t="n">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="N338" t="n">
-        <v>1550.1945107573</v>
+        <v>1550.1945200974</v>
       </c>
       <c r="O338" t="n">
-        <v>1023128.377099818</v>
+        <v>999875.465462823</v>
       </c>
       <c r="P338" t="n">
         <v>2500</v>
       </c>
       <c r="Q338" t="n">
-        <v>1650000</v>
+        <v>1612500</v>
       </c>
     </row>
     <row r="339">
@@ -15327,22 +15327,22 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M340" t="n">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="N340" t="n">
-        <v>2403.5178067661</v>
+        <v>2403.5178733813</v>
       </c>
       <c r="O340" t="n">
-        <v>908529.7309575857</v>
+        <v>886898.0952776996</v>
       </c>
       <c r="P340" t="n">
         <v>3500</v>
       </c>
       <c r="Q340" t="n">
-        <v>1323000</v>
+        <v>1291500</v>
       </c>
     </row>
     <row r="341">
@@ -18411,22 +18411,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M410" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N410" t="n">
-        <v>2029.8740983607</v>
+        <v>2029.8741050903</v>
       </c>
       <c r="O410" t="n">
-        <v>355227.9672131225</v>
+        <v>349138.3460755316</v>
       </c>
       <c r="P410" t="n">
         <v>3600</v>
       </c>
       <c r="Q410" t="n">
-        <v>630000</v>
+        <v>619200</v>
       </c>
     </row>
     <row r="411">
@@ -19872,10 +19872,10 @@
         <v>11</v>
       </c>
       <c r="N444" t="n">
-        <v>4814.2679269747</v>
+        <v>4817.516083662</v>
       </c>
       <c r="O444" t="n">
-        <v>52956.9471967217</v>
+        <v>52992.676920282</v>
       </c>
       <c r="P444" t="n">
         <v>9900</v>
@@ -19959,10 +19959,10 @@
         <v>12</v>
       </c>
       <c r="N446" t="n">
-        <v>11562.038418079</v>
+        <v>11660.859259259</v>
       </c>
       <c r="O446" t="n">
-        <v>138744.461016948</v>
+        <v>139930.311111108</v>
       </c>
       <c r="P446" t="n">
         <v>18500</v>
@@ -20005,10 +20005,10 @@
         <v>12</v>
       </c>
       <c r="N447" t="n">
-        <v>13513.643445378</v>
+        <v>13744.645897436</v>
       </c>
       <c r="O447" t="n">
-        <v>162163.721344536</v>
+        <v>164935.750769232</v>
       </c>
       <c r="P447" t="n">
         <v>21900</v>
@@ -20737,10 +20737,10 @@
         <v>4</v>
       </c>
       <c r="N464" t="n">
-        <v>4100.45</v>
+        <v>4114.8123467601</v>
       </c>
       <c r="O464" t="n">
-        <v>16401.8</v>
+        <v>16459.2493870404</v>
       </c>
       <c r="P464" t="n">
         <v>26900</v>
@@ -20910,22 +20910,22 @@
         <v>0</v>
       </c>
       <c r="L468" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M468" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="N468" t="n">
-        <v>1561.0038892883</v>
+        <v>1561.0040101523</v>
       </c>
       <c r="O468" t="n">
-        <v>131124.3267002172</v>
+        <v>112392.2887309656</v>
       </c>
       <c r="P468" t="n">
         <v>2900</v>
       </c>
       <c r="Q468" t="n">
-        <v>243600</v>
+        <v>208800</v>
       </c>
     </row>
     <row r="469">
@@ -21354,10 +21354,10 @@
         <v>6</v>
       </c>
       <c r="N478" t="n">
-        <v>7969.950169361</v>
+        <v>7988.3991280864</v>
       </c>
       <c r="O478" t="n">
-        <v>47819.701016166</v>
+        <v>47930.3947685184</v>
       </c>
       <c r="P478" t="n">
         <v>12900</v>
@@ -21572,10 +21572,10 @@
         <v>33</v>
       </c>
       <c r="N483" t="n">
-        <v>9627.34</v>
+        <v>9794.2880924855</v>
       </c>
       <c r="O483" t="n">
-        <v>317702.22</v>
+        <v>323211.5070520215</v>
       </c>
       <c r="P483" t="n">
         <v>15900</v>
@@ -24195,22 +24195,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M541" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N541" t="n">
-        <v>1664.3409571788</v>
+        <v>1664.3408838384</v>
       </c>
       <c r="O541" t="n">
-        <v>51594.5696725428</v>
+        <v>49930.226515152</v>
       </c>
       <c r="P541" t="n">
         <v>2900</v>
       </c>
       <c r="Q541" t="n">
-        <v>89900</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="542">
@@ -25133,10 +25133,10 @@
         <v>4</v>
       </c>
       <c r="N561" t="n">
-        <v>25749.15</v>
+        <v>24523</v>
       </c>
       <c r="O561" t="n">
-        <v>102996.6</v>
+        <v>98092</v>
       </c>
       <c r="P561" t="n">
         <v>41900</v>
@@ -25225,10 +25225,10 @@
         <v>7</v>
       </c>
       <c r="N563" t="n">
-        <v>22739</v>
+        <v>22855.411262799</v>
       </c>
       <c r="O563" t="n">
-        <v>159173</v>
+        <v>159987.878839593</v>
       </c>
       <c r="P563" t="n">
         <v>36900</v>
@@ -25406,22 +25406,22 @@
         <v>0</v>
       </c>
       <c r="L567" t="n">
+        <v>2</v>
+      </c>
+      <c r="M567" t="n">
         <v>1</v>
-      </c>
-      <c r="M567" t="n">
-        <v>2</v>
       </c>
       <c r="N567" t="n">
         <v>26956</v>
       </c>
       <c r="O567" t="n">
-        <v>53912</v>
+        <v>26956</v>
       </c>
       <c r="P567" t="n">
         <v>44900</v>
       </c>
       <c r="Q567" t="n">
-        <v>89800</v>
+        <v>44900</v>
       </c>
     </row>
     <row r="568">
@@ -26853,10 +26853,10 @@
         <v>37</v>
       </c>
       <c r="N598" t="n">
-        <v>13687</v>
+        <v>13795.340369393</v>
       </c>
       <c r="O598" t="n">
-        <v>506419</v>
+        <v>510427.593667541</v>
       </c>
       <c r="P598" t="n">
         <v>21900</v>
@@ -27452,10 +27452,10 @@
         <v>23</v>
       </c>
       <c r="N611" t="n">
-        <v>8858.16</v>
+        <v>8872.673642818099</v>
       </c>
       <c r="O611" t="n">
-        <v>203737.68</v>
+        <v>204071.4937848163</v>
       </c>
       <c r="P611" t="n">
         <v>15500</v>
@@ -29206,10 +29206,10 @@
         <v>121</v>
       </c>
       <c r="N649" t="n">
-        <v>3903.7390742358</v>
+        <v>3903.7391243433</v>
       </c>
       <c r="O649" t="n">
-        <v>472352.4279825318</v>
+        <v>472352.4340455393</v>
       </c>
       <c r="P649" t="n">
         <v>7500</v>
@@ -29247,10 +29247,10 @@
         <v>10</v>
       </c>
       <c r="N650" t="n">
-        <v>20726</v>
+        <v>21127.148387097</v>
       </c>
       <c r="O650" t="n">
-        <v>207260</v>
+        <v>211271.48387097</v>
       </c>
       <c r="P650" t="n">
         <v>33900</v>
@@ -29339,10 +29339,10 @@
         <v>4</v>
       </c>
       <c r="N652" t="n">
-        <v>12113</v>
+        <v>13082.04</v>
       </c>
       <c r="O652" t="n">
-        <v>48452</v>
+        <v>52328.16</v>
       </c>
       <c r="P652" t="n">
         <v>19900</v>
@@ -29385,10 +29385,10 @@
         <v>6</v>
       </c>
       <c r="N653" t="n">
-        <v>33000</v>
+        <v>33980.198019802</v>
       </c>
       <c r="O653" t="n">
-        <v>198000</v>
+        <v>203881.188118812</v>
       </c>
       <c r="P653" t="n">
         <v>52900</v>
@@ -29707,10 +29707,10 @@
         <v>39</v>
       </c>
       <c r="N660" t="n">
-        <v>6849.2</v>
+        <v>6855.7044634378</v>
       </c>
       <c r="O660" t="n">
-        <v>267118.8</v>
+        <v>267372.4740740742</v>
       </c>
       <c r="P660" t="n">
         <v>11500</v>
@@ -32381,10 +32381,10 @@
         <v>56</v>
       </c>
       <c r="N718" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O718" t="n">
-        <v>84898.16980040481</v>
+        <v>84898.1697503296</v>
       </c>
       <c r="P718" t="n">
         <v>2300</v>
@@ -32511,22 +32511,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M721" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N721" t="n">
-        <v>2458.5126157653</v>
+        <v>2500.9617517986</v>
       </c>
       <c r="O721" t="n">
-        <v>685925.0197985186</v>
+        <v>695267.3670000108</v>
       </c>
       <c r="P721" t="n">
         <v>3500</v>
       </c>
       <c r="Q721" t="n">
-        <v>976500</v>
+        <v>973000</v>
       </c>
     </row>
     <row r="722">
@@ -32609,10 +32609,10 @@
         <v>114</v>
       </c>
       <c r="N723" t="n">
-        <v>1771.089398827</v>
+        <v>1835.6884042553</v>
       </c>
       <c r="O723" t="n">
-        <v>201904.191466278</v>
+        <v>209268.4780851042</v>
       </c>
       <c r="P723" t="n">
         <v>2500</v>
@@ -32649,22 +32649,22 @@
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M724" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N724" t="n">
-        <v>2079.3833258511</v>
+        <v>2079.3833208536</v>
       </c>
       <c r="O724" t="n">
-        <v>436670.498428731</v>
+        <v>432511.7307375488</v>
       </c>
       <c r="P724" t="n">
         <v>2900</v>
       </c>
       <c r="Q724" t="n">
-        <v>609000</v>
+        <v>603200</v>
       </c>
     </row>
     <row r="725">
@@ -32701,10 +32701,10 @@
         <v>110</v>
       </c>
       <c r="N725" t="n">
-        <v>1803.0166107644</v>
+        <v>1837.4143839428</v>
       </c>
       <c r="O725" t="n">
-        <v>198331.827184084</v>
+        <v>202115.582233708</v>
       </c>
       <c r="P725" t="n">
         <v>2500</v>
@@ -32747,10 +32747,10 @@
         <v>108</v>
       </c>
       <c r="N726" t="n">
-        <v>3306.5944272446</v>
+        <v>3645.1535836177</v>
       </c>
       <c r="O726" t="n">
-        <v>357112.1981424168</v>
+        <v>393676.5870307116</v>
       </c>
       <c r="P726" t="n">
         <v>4900</v>
@@ -32885,10 +32885,10 @@
         <v>225</v>
       </c>
       <c r="N729" t="n">
-        <v>2056.0822493428</v>
+        <v>2093.8229560229</v>
       </c>
       <c r="O729" t="n">
-        <v>462618.50610213</v>
+        <v>471110.1651051525</v>
       </c>
       <c r="P729" t="n">
         <v>2900</v>
@@ -32977,10 +32977,10 @@
         <v>111</v>
       </c>
       <c r="N731" t="n">
-        <v>1655.9295385779</v>
+        <v>1751.31108</v>
       </c>
       <c r="O731" t="n">
-        <v>183808.1787821469</v>
+        <v>194395.52988</v>
       </c>
       <c r="P731" t="n">
         <v>2500</v>
@@ -33250,22 +33250,22 @@
         <v>0</v>
       </c>
       <c r="L737" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M737" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N737" t="n">
-        <v>1592.2824611033</v>
+        <v>1592.2825142045</v>
       </c>
       <c r="O737" t="n">
-        <v>151266.8338048135</v>
+        <v>146489.991306814</v>
       </c>
       <c r="P737" t="n">
         <v>2500</v>
       </c>
       <c r="Q737" t="n">
-        <v>237500</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="738">
@@ -33433,10 +33433,10 @@
         <v>19</v>
       </c>
       <c r="N741" t="n">
-        <v>1906.1764864865</v>
+        <v>1906.1759813084</v>
       </c>
       <c r="O741" t="n">
-        <v>36217.3532432435</v>
+        <v>36217.3436448596</v>
       </c>
       <c r="P741" t="n">
         <v>2900</v>
@@ -33571,10 +33571,10 @@
         <v>49</v>
       </c>
       <c r="N744" t="n">
-        <v>1668.6443636364</v>
+        <v>1668.6458215962</v>
       </c>
       <c r="O744" t="n">
-        <v>81763.57381818359</v>
+        <v>81763.6452582138</v>
       </c>
       <c r="P744" t="n">
         <v>2500</v>
@@ -34166,10 +34166,10 @@
         <v>10</v>
       </c>
       <c r="N757" t="n">
-        <v>9736</v>
+        <v>9760.865567680499</v>
       </c>
       <c r="O757" t="n">
-        <v>97360</v>
+        <v>97608.65567680499</v>
       </c>
       <c r="P757" t="n">
         <v>15900</v>
@@ -34215,10 +34215,10 @@
         <v>21</v>
       </c>
       <c r="N758" t="n">
-        <v>5215</v>
+        <v>5227.7693437806</v>
       </c>
       <c r="O758" t="n">
-        <v>109515</v>
+        <v>109783.1562193926</v>
       </c>
       <c r="P758" t="n">
         <v>8900</v>
@@ -34447,10 +34447,10 @@
         <v>9</v>
       </c>
       <c r="N763" t="n">
-        <v>15423.36</v>
+        <v>15646.886956522</v>
       </c>
       <c r="O763" t="n">
-        <v>138810.24</v>
+        <v>140821.982608698</v>
       </c>
       <c r="P763" t="n">
         <v>24900</v>
@@ -37877,10 +37877,10 @@
         <v>1023</v>
       </c>
       <c r="N837" t="n">
-        <v>517.2943625967</v>
+        <v>517.29445253004</v>
       </c>
       <c r="O837" t="n">
-        <v>529192.1329364241</v>
+        <v>529192.2249382309</v>
       </c>
       <c r="P837" t="n">
         <v>900</v>
@@ -38392,10 +38392,10 @@
         <v>297</v>
       </c>
       <c r="N848" t="n">
-        <v>3110.8379310345</v>
+        <v>3110.8378564067</v>
       </c>
       <c r="O848" t="n">
-        <v>923918.8655172464</v>
+        <v>923918.84335279</v>
       </c>
       <c r="P848" t="n">
         <v>4500</v>
@@ -38804,10 +38804,10 @@
         <v>936</v>
       </c>
       <c r="N857" t="n">
-        <v>703.79481075491</v>
+        <v>703.79479136392</v>
       </c>
       <c r="O857" t="n">
-        <v>658751.9428665958</v>
+        <v>658751.9247166291</v>
       </c>
       <c r="P857" t="n">
         <v>900</v>
@@ -48768,10 +48768,10 @@
         <v>46</v>
       </c>
       <c r="N1068" t="n">
-        <v>4985.4069767442</v>
+        <v>4985.4071856287</v>
       </c>
       <c r="O1068" t="n">
-        <v>229328.7209302332</v>
+        <v>229328.7305389202</v>
       </c>
       <c r="P1068" t="n">
         <v>7900</v>
@@ -48864,22 +48864,22 @@
         <v>0</v>
       </c>
       <c r="L1070" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1070" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N1070" t="n">
-        <v>1757.3206205251</v>
+        <v>1757.3206220096</v>
       </c>
       <c r="O1070" t="n">
-        <v>101924.5959904558</v>
+        <v>100167.2754545472</v>
       </c>
       <c r="P1070" t="n">
         <v>2000</v>
       </c>
       <c r="Q1070" t="n">
-        <v>116000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="1071">
@@ -48910,22 +48910,22 @@
         <v>0</v>
       </c>
       <c r="L1071" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1071" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N1071" t="n">
         <v>1561.33</v>
       </c>
       <c r="O1071" t="n">
-        <v>56207.88</v>
+        <v>54646.55</v>
       </c>
       <c r="P1071" t="n">
         <v>2000</v>
       </c>
       <c r="Q1071" t="n">
-        <v>72000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="1072">
@@ -51535,22 +51535,22 @@
         <v>0</v>
       </c>
       <c r="L1128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1128" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N1128" t="n">
         <v>6160</v>
       </c>
       <c r="O1128" t="n">
-        <v>61600</v>
+        <v>49280</v>
       </c>
       <c r="P1128" t="n">
         <v>7900</v>
       </c>
       <c r="Q1128" t="n">
-        <v>79000</v>
+        <v>63200</v>
       </c>
     </row>
     <row r="1129">
@@ -51811,22 +51811,22 @@
         <v>0</v>
       </c>
       <c r="L1134" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M1134" t="n">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="N1134" t="n">
         <v>2288</v>
       </c>
       <c r="O1134" t="n">
-        <v>761904</v>
+        <v>697840</v>
       </c>
       <c r="P1134" t="n">
         <v>2900</v>
       </c>
       <c r="Q1134" t="n">
-        <v>965700</v>
+        <v>884500</v>
       </c>
     </row>
     <row r="1135">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -3669,10 +3669,10 @@
         <v>13</v>
       </c>
       <c r="N78" t="n">
-        <v>15899.011607143</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O78" t="n">
-        <v>206687.150892859</v>
+        <v>204255.536488094</v>
       </c>
       <c r="P78" t="n">
         <v>28500</v>
@@ -5571,10 +5571,10 @@
         <v>19</v>
       </c>
       <c r="N122" t="n">
-        <v>544.6367953668</v>
+        <v>538.40061776062</v>
       </c>
       <c r="O122" t="n">
-        <v>10348.0991119692</v>
+        <v>10229.61173745178</v>
       </c>
       <c r="P122" t="n">
         <v>6800</v>
@@ -6049,10 +6049,10 @@
         <v>27</v>
       </c>
       <c r="N133" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="O133" t="n">
-        <v>71391.27884892031</v>
+        <v>69394.31999999999</v>
       </c>
       <c r="P133" t="n">
         <v>4700</v>
@@ -6730,10 +6730,10 @@
         <v>11</v>
       </c>
       <c r="N149" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="O149" t="n">
-        <v>29250.8237383175</v>
+        <v>28196.74</v>
       </c>
       <c r="P149" t="n">
         <v>4700</v>
@@ -7501,10 +7501,10 @@
         <v>12</v>
       </c>
       <c r="N166" t="n">
-        <v>10897.588251121</v>
+        <v>10752.93</v>
       </c>
       <c r="O166" t="n">
-        <v>130771.059013452</v>
+        <v>129035.16</v>
       </c>
       <c r="P166" t="n">
         <v>18400</v>
@@ -8401,10 +8401,10 @@
         <v>7</v>
       </c>
       <c r="N187" t="n">
-        <v>12796.783333333</v>
+        <v>12587</v>
       </c>
       <c r="O187" t="n">
-        <v>89577.48333333099</v>
+        <v>88109</v>
       </c>
       <c r="P187" t="n">
         <v>18900</v>
@@ -8488,10 +8488,10 @@
         <v>13</v>
       </c>
       <c r="N189" t="n">
-        <v>17263.007447496</v>
+        <v>17207.41</v>
       </c>
       <c r="O189" t="n">
-        <v>224419.096817448</v>
+        <v>223696.33</v>
       </c>
       <c r="P189" t="n">
         <v>20000</v>
@@ -10844,10 +10844,10 @@
         <v>81</v>
       </c>
       <c r="N241" t="n">
-        <v>2271.9151051954</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O241" t="n">
-        <v>184025.1235208274</v>
+        <v>183630.8962773738</v>
       </c>
       <c r="P241" t="n">
         <v>3900</v>
@@ -11245,22 +11245,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N250" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O250" t="n">
-        <v>97044.83419354921</v>
+        <v>89856.3275862075</v>
       </c>
       <c r="P250" t="n">
         <v>6500</v>
       </c>
       <c r="Q250" t="n">
-        <v>175500</v>
+        <v>162500</v>
       </c>
     </row>
     <row r="251">
@@ -12327,10 +12327,10 @@
         <v>6</v>
       </c>
       <c r="N274" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O274" t="n">
-        <v>16313.050886076</v>
+        <v>16176.54</v>
       </c>
       <c r="P274" t="n">
         <v>8200</v>
@@ -13266,10 +13266,10 @@
         <v>31</v>
       </c>
       <c r="N295" t="n">
-        <v>6260.7161253561</v>
+        <v>6242.93</v>
       </c>
       <c r="O295" t="n">
-        <v>194082.1998860391</v>
+        <v>193530.83</v>
       </c>
       <c r="P295" t="n">
         <v>10400</v>
@@ -13671,10 +13671,10 @@
         <v>2</v>
       </c>
       <c r="N304" t="n">
-        <v>1660.4491721419</v>
+        <v>1647.46</v>
       </c>
       <c r="O304" t="n">
-        <v>3320.8983442838</v>
+        <v>3294.92</v>
       </c>
       <c r="P304" t="n">
         <v>2900</v>
@@ -13903,10 +13903,10 @@
         <v>61</v>
       </c>
       <c r="N309" t="n">
-        <v>4752.0246648045</v>
+        <v>4635.49</v>
       </c>
       <c r="O309" t="n">
-        <v>289873.5045530745</v>
+        <v>282764.89</v>
       </c>
       <c r="P309" t="n">
         <v>7500</v>
@@ -15538,10 +15538,10 @@
         <v>23</v>
       </c>
       <c r="N345" t="n">
-        <v>11749.140699301</v>
+        <v>11507.72</v>
       </c>
       <c r="O345" t="n">
-        <v>270230.236083923</v>
+        <v>264677.56</v>
       </c>
       <c r="P345" t="n">
         <v>25800</v>
@@ -17742,22 +17742,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M394" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N394" t="n">
         <v>9338</v>
       </c>
       <c r="O394" t="n">
-        <v>317492</v>
+        <v>298816</v>
       </c>
       <c r="P394" t="n">
         <v>15500</v>
       </c>
       <c r="Q394" t="n">
-        <v>527000</v>
+        <v>496000</v>
       </c>
     </row>
     <row r="395">
@@ -18043,10 +18043,10 @@
         <v>17</v>
       </c>
       <c r="N401" t="n">
-        <v>2633.2</v>
+        <v>2610</v>
       </c>
       <c r="O401" t="n">
-        <v>44764.39999999999</v>
+        <v>44370</v>
       </c>
       <c r="P401" t="n">
         <v>3200</v>
@@ -18288,22 +18288,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M407" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="N407" t="n">
         <v>2567</v>
       </c>
       <c r="O407" t="n">
-        <v>277236</v>
+        <v>246432</v>
       </c>
       <c r="P407" t="n">
         <v>4500</v>
       </c>
       <c r="Q407" t="n">
-        <v>486000</v>
+        <v>432000</v>
       </c>
     </row>
     <row r="408">
@@ -18786,10 +18786,10 @@
         <v>2</v>
       </c>
       <c r="N419" t="n">
-        <v>4355.2256097561</v>
+        <v>4355.2256790123</v>
       </c>
       <c r="O419" t="n">
-        <v>8710.451219512201</v>
+        <v>8710.4513580246</v>
       </c>
       <c r="P419" t="n">
         <v>7900</v>
@@ -20476,10 +20476,10 @@
         <v>2</v>
       </c>
       <c r="N458" t="n">
-        <v>27637.186666667</v>
+        <v>20727.89</v>
       </c>
       <c r="O458" t="n">
-        <v>55274.373333334</v>
+        <v>41455.78</v>
       </c>
       <c r="P458" t="n">
         <v>33500</v>
@@ -20568,10 +20568,10 @@
         <v>9</v>
       </c>
       <c r="N460" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O460" t="n">
-        <v>245100.202363638</v>
+        <v>244113.883454547</v>
       </c>
       <c r="P460" t="n">
         <v>44500</v>
@@ -20916,10 +20916,10 @@
         <v>71</v>
       </c>
       <c r="N468" t="n">
-        <v>1561.0041954445</v>
+        <v>1561.004375</v>
       </c>
       <c r="O468" t="n">
-        <v>110831.2978765595</v>
+        <v>110831.310625</v>
       </c>
       <c r="P468" t="n">
         <v>2900</v>
@@ -21354,10 +21354,10 @@
         <v>6</v>
       </c>
       <c r="N478" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O478" t="n">
-        <v>47930.3947685184</v>
+        <v>47819.7010185186</v>
       </c>
       <c r="P478" t="n">
         <v>12900</v>
@@ -21572,10 +21572,10 @@
         <v>33</v>
       </c>
       <c r="N483" t="n">
-        <v>9794.2880924855</v>
+        <v>9627.34</v>
       </c>
       <c r="O483" t="n">
-        <v>323211.5070520215</v>
+        <v>317702.22</v>
       </c>
       <c r="P483" t="n">
         <v>15900</v>
@@ -23177,10 +23177,10 @@
         <v>33</v>
       </c>
       <c r="N519" t="n">
-        <v>3131.5075106082</v>
+        <v>3113.8900282885</v>
       </c>
       <c r="O519" t="n">
-        <v>103339.7478500706</v>
+        <v>102758.3709335205</v>
       </c>
       <c r="P519" t="n">
         <v>5000</v>
@@ -23407,10 +23407,10 @@
         <v>1</v>
       </c>
       <c r="N524" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="O524" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="P524" t="n">
         <v>4100</v>
@@ -23971,10 +23971,10 @@
         <v>11</v>
       </c>
       <c r="N536" t="n">
-        <v>5859.18</v>
+        <v>5791.05</v>
       </c>
       <c r="O536" t="n">
-        <v>64450.98</v>
+        <v>63701.55</v>
       </c>
       <c r="P536" t="n">
         <v>9300</v>
@@ -24394,10 +24394,10 @@
         <v>15</v>
       </c>
       <c r="N545" t="n">
-        <v>9379.0968275862</v>
+        <v>9188.98</v>
       </c>
       <c r="O545" t="n">
-        <v>140686.452413793</v>
+        <v>137834.7</v>
       </c>
       <c r="P545" t="n">
         <v>12900</v>
@@ -25271,10 +25271,10 @@
         <v>13</v>
       </c>
       <c r="N564" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O564" t="n">
-        <v>209208.801742915</v>
+        <v>208754</v>
       </c>
       <c r="P564" t="n">
         <v>25900</v>
@@ -25317,10 +25317,10 @@
         <v>8</v>
       </c>
       <c r="N565" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O565" t="n">
-        <v>204615.122060472</v>
+        <v>204272</v>
       </c>
       <c r="P565" t="n">
         <v>40900</v>
@@ -25547,10 +25547,10 @@
         <v>17</v>
       </c>
       <c r="N570" t="n">
-        <v>9927.272727272701</v>
+        <v>9750</v>
       </c>
       <c r="O570" t="n">
-        <v>168763.6363636359</v>
+        <v>165750</v>
       </c>
       <c r="P570" t="n">
         <v>15600</v>
@@ -25639,10 +25639,10 @@
         <v>53</v>
       </c>
       <c r="N572" t="n">
-        <v>7278.6868686869</v>
+        <v>7230</v>
       </c>
       <c r="O572" t="n">
-        <v>385770.4040404057</v>
+        <v>383190</v>
       </c>
       <c r="P572" t="n">
         <v>11600</v>
@@ -26758,10 +26758,10 @@
         <v>37</v>
       </c>
       <c r="N596" t="n">
-        <v>13795.055263158</v>
+        <v>13687</v>
       </c>
       <c r="O596" t="n">
-        <v>510417.044736846</v>
+        <v>506419</v>
       </c>
       <c r="P596" t="n">
         <v>21900</v>
@@ -26988,10 +26988,10 @@
         <v>1</v>
       </c>
       <c r="N601" t="n">
-        <v>20960.318181818</v>
+        <v>20049</v>
       </c>
       <c r="O601" t="n">
-        <v>20960.318181818</v>
+        <v>20049</v>
       </c>
       <c r="P601" t="n">
         <v>32900</v>
@@ -27403,10 +27403,10 @@
         <v>24</v>
       </c>
       <c r="N610" t="n">
-        <v>10485.899280576</v>
+        <v>10411</v>
       </c>
       <c r="O610" t="n">
-        <v>251661.582733824</v>
+        <v>249864</v>
       </c>
       <c r="P610" t="n">
         <v>16900</v>
@@ -28283,10 +28283,10 @@
         <v>6</v>
       </c>
       <c r="N629" t="n">
-        <v>32566.857142857</v>
+        <v>32332</v>
       </c>
       <c r="O629" t="n">
-        <v>195401.142857142</v>
+        <v>193992</v>
       </c>
       <c r="P629" t="n">
         <v>55900</v>
@@ -28789,10 +28789,10 @@
         <v>20</v>
       </c>
       <c r="N640" t="n">
-        <v>3412.5148218527</v>
+        <v>3396.38</v>
       </c>
       <c r="O640" t="n">
-        <v>68250.296437054</v>
+        <v>67927.60000000001</v>
       </c>
       <c r="P640" t="n">
         <v>6500</v>
@@ -28973,10 +28973,10 @@
         <v>14</v>
       </c>
       <c r="N644" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O644" t="n">
-        <v>185265.598591556</v>
+        <v>184940</v>
       </c>
       <c r="P644" t="n">
         <v>23900</v>
@@ -29520,10 +29520,10 @@
         <v>156</v>
       </c>
       <c r="N656" t="n">
-        <v>2657.2435094002</v>
+        <v>2629</v>
       </c>
       <c r="O656" t="n">
-        <v>414529.9874664312</v>
+        <v>410124</v>
       </c>
       <c r="P656" t="n">
         <v>4500</v>
@@ -29612,10 +29612,10 @@
         <v>39</v>
       </c>
       <c r="N658" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O658" t="n">
-        <v>268392.0068636781</v>
+        <v>267118.8</v>
       </c>
       <c r="P658" t="n">
         <v>11500</v>
@@ -29750,10 +29750,10 @@
         <v>8</v>
       </c>
       <c r="N661" t="n">
-        <v>6279.1629563669</v>
+        <v>6268</v>
       </c>
       <c r="O661" t="n">
-        <v>50233.3036509352</v>
+        <v>50144</v>
       </c>
       <c r="P661" t="n">
         <v>10900</v>
@@ -30026,10 +30026,10 @@
         <v>15</v>
       </c>
       <c r="N667" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O667" t="n">
-        <v>114589.0699300695</v>
+        <v>114525</v>
       </c>
       <c r="P667" t="n">
         <v>13900</v>
@@ -30351,10 +30351,10 @@
         <v>46</v>
       </c>
       <c r="N674" t="n">
-        <v>766.64130434783</v>
+        <v>753</v>
       </c>
       <c r="O674" t="n">
-        <v>35265.50000000018</v>
+        <v>34638</v>
       </c>
       <c r="P674" t="n">
         <v>1600</v>
@@ -30535,10 +30535,10 @@
         <v>2</v>
       </c>
       <c r="N678" t="n">
-        <v>11478.737327189</v>
+        <v>11348</v>
       </c>
       <c r="O678" t="n">
-        <v>22957.474654378</v>
+        <v>22696</v>
       </c>
       <c r="P678" t="n">
         <v>19900</v>
@@ -31228,10 +31228,10 @@
         <v>83</v>
       </c>
       <c r="N693" t="n">
-        <v>5322.5257731959</v>
+        <v>5215</v>
       </c>
       <c r="O693" t="n">
-        <v>441769.6391752597</v>
+        <v>432845</v>
       </c>
       <c r="P693" t="n">
         <v>8900</v>
@@ -31504,10 +31504,10 @@
         <v>20</v>
       </c>
       <c r="N699" t="n">
-        <v>8721.3759213759</v>
+        <v>8700</v>
       </c>
       <c r="O699" t="n">
-        <v>174427.518427518</v>
+        <v>174000</v>
       </c>
       <c r="P699" t="n">
         <v>14900</v>
@@ -31872,10 +31872,10 @@
         <v>8</v>
       </c>
       <c r="N707" t="n">
-        <v>21884.258426966</v>
+        <v>21762</v>
       </c>
       <c r="O707" t="n">
-        <v>175074.067415728</v>
+        <v>174096</v>
       </c>
       <c r="P707" t="n">
         <v>35900</v>
@@ -31918,10 +31918,10 @@
         <v>92</v>
       </c>
       <c r="N708" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O708" t="n">
-        <v>351772.6105407248</v>
+        <v>351532</v>
       </c>
       <c r="P708" t="n">
         <v>5900</v>
@@ -32056,10 +32056,10 @@
         <v>63</v>
       </c>
       <c r="N711" t="n">
-        <v>7295.3326848249</v>
+        <v>7253</v>
       </c>
       <c r="O711" t="n">
-        <v>459605.9591439687</v>
+        <v>456939</v>
       </c>
       <c r="P711" t="n">
         <v>11900</v>
@@ -33522,10 +33522,10 @@
         <v>133</v>
       </c>
       <c r="N743" t="n">
-        <v>2546.9807189542</v>
+        <v>2546.9805333333</v>
       </c>
       <c r="O743" t="n">
-        <v>338748.4356209086</v>
+        <v>338748.4109333289</v>
       </c>
       <c r="P743" t="n">
         <v>3900</v>
@@ -33976,10 +33976,10 @@
         <v>1002</v>
       </c>
       <c r="N753" t="n">
-        <v>1955.7828121686</v>
+        <v>1955.2371130338</v>
       </c>
       <c r="O753" t="n">
-        <v>1959694.377792937</v>
+        <v>1959147.587259867</v>
       </c>
       <c r="P753" t="n">
         <v>3000</v>
@@ -34022,10 +34022,10 @@
         <v>618</v>
       </c>
       <c r="N754" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="O754" t="n">
-        <v>732833.4763909824</v>
+        <v>732527.4915288108</v>
       </c>
       <c r="P754" t="n">
         <v>1900</v>
@@ -34114,22 +34114,22 @@
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M756" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N756" t="n">
         <v>5215</v>
       </c>
       <c r="O756" t="n">
-        <v>109515</v>
+        <v>93870</v>
       </c>
       <c r="P756" t="n">
         <v>8900</v>
       </c>
       <c r="Q756" t="n">
-        <v>186900</v>
+        <v>160200</v>
       </c>
     </row>
     <row r="757">
@@ -34727,10 +34727,10 @@
         <v>30</v>
       </c>
       <c r="N769" t="n">
-        <v>3256.3775316456</v>
+        <v>3026.5160126582</v>
       </c>
       <c r="O769" t="n">
-        <v>97691.32594936799</v>
+        <v>90795.480379746</v>
       </c>
       <c r="P769" t="n">
         <v>7000</v>
@@ -35010,10 +35010,10 @@
         <v>28</v>
       </c>
       <c r="N775" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O775" t="n">
-        <v>43062.831234668</v>
+        <v>42852.5977105492</v>
       </c>
       <c r="P775" t="n">
         <v>2600</v>
@@ -38703,22 +38703,22 @@
         <v>0</v>
       </c>
       <c r="L855" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="M855" t="n">
-        <v>908</v>
+        <v>812</v>
       </c>
       <c r="N855" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O855" t="n">
-        <v>639045.6525720218</v>
+        <v>572196.7867967212</v>
       </c>
       <c r="P855" t="n">
         <v>900</v>
       </c>
       <c r="Q855" t="n">
-        <v>817200</v>
+        <v>730800</v>
       </c>
     </row>
     <row r="856">
@@ -43237,10 +43237,10 @@
         <v>9</v>
       </c>
       <c r="N950" t="n">
-        <v>5370.6369361702</v>
+        <v>5347.88</v>
       </c>
       <c r="O950" t="n">
-        <v>48335.7324255318</v>
+        <v>48130.92</v>
       </c>
       <c r="P950" t="n">
         <v>7900</v>
@@ -43286,10 +43286,10 @@
         <v>19</v>
       </c>
       <c r="N951" t="n">
-        <v>4593.1990728477</v>
+        <v>4578.04</v>
       </c>
       <c r="O951" t="n">
-        <v>87270.78238410631</v>
+        <v>86982.75999999999</v>
       </c>
       <c r="P951" t="n">
         <v>7500</v>
@@ -45060,10 +45060,10 @@
         <v>9</v>
       </c>
       <c r="N988" t="n">
-        <v>10912.902659574</v>
+        <v>10798.03</v>
       </c>
       <c r="O988" t="n">
-        <v>98216.123936166</v>
+        <v>97182.27</v>
       </c>
       <c r="P988" t="n">
         <v>45000</v>
@@ -45570,10 +45570,10 @@
         <v>10</v>
       </c>
       <c r="N999" t="n">
-        <v>5272.2028268551</v>
+        <v>5216.9</v>
       </c>
       <c r="O999" t="n">
-        <v>52722.028268551</v>
+        <v>52169</v>
       </c>
       <c r="P999" t="n">
         <v>20500</v>
@@ -45954,10 +45954,10 @@
         <v>1</v>
       </c>
       <c r="N1007" t="n">
-        <v>7605.4495327103</v>
+        <v>7465.9</v>
       </c>
       <c r="O1007" t="n">
-        <v>7605.4495327103</v>
+        <v>7465.9</v>
       </c>
       <c r="P1007" t="n">
         <v>11900</v>
@@ -46389,10 +46389,10 @@
         <v>1</v>
       </c>
       <c r="N1016" t="n">
-        <v>44654.875337423</v>
+        <v>44113.604171779</v>
       </c>
       <c r="O1016" t="n">
-        <v>44654.875337423</v>
+        <v>44113.604171779</v>
       </c>
       <c r="P1016" t="n">
         <v>71900</v>
@@ -48088,10 +48088,10 @@
         <v>154</v>
       </c>
       <c r="N1053" t="n">
-        <v>3186.7802147239</v>
+        <v>3181.9</v>
       </c>
       <c r="O1053" t="n">
-        <v>490764.1530674806</v>
+        <v>490012.6</v>
       </c>
       <c r="P1053" t="n">
         <v>5100</v>
@@ -48586,10 +48586,10 @@
         <v>5</v>
       </c>
       <c r="N1064" t="n">
-        <v>5959.9565217391</v>
+        <v>5077</v>
       </c>
       <c r="O1064" t="n">
-        <v>29799.7826086955</v>
+        <v>25385</v>
       </c>
       <c r="P1064" t="n">
         <v>8500</v>
@@ -48632,10 +48632,10 @@
         <v>140</v>
       </c>
       <c r="N1065" t="n">
-        <v>707.69883076923</v>
+        <v>705.5279692307701</v>
       </c>
       <c r="O1065" t="n">
-        <v>99077.8363076922</v>
+        <v>98773.91569230781</v>
       </c>
       <c r="P1065" t="n">
         <v>1500</v>
@@ -50345,10 +50345,10 @@
         <v>14</v>
       </c>
       <c r="N1102" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O1102" t="n">
-        <v>37177.2097658864</v>
+        <v>37028.6</v>
       </c>
       <c r="P1102" t="n">
         <v>3900</v>
@@ -52151,10 +52151,10 @@
         <v>6</v>
       </c>
       <c r="N1141" t="n">
-        <v>6162.2222222222</v>
+        <v>5900</v>
       </c>
       <c r="O1141" t="n">
-        <v>36973.3333333332</v>
+        <v>35400</v>
       </c>
       <c r="P1141" t="n">
         <v>7100</v>
@@ -52243,10 +52243,10 @@
         <v>7</v>
       </c>
       <c r="N1143" t="n">
-        <v>26102.941176471</v>
+        <v>25000</v>
       </c>
       <c r="O1143" t="n">
-        <v>182720.588235297</v>
+        <v>175000</v>
       </c>
       <c r="P1143" t="n">
         <v>30000</v>
@@ -53485,10 +53485,10 @@
         <v>2</v>
       </c>
       <c r="N1170" t="n">
-        <v>1494.6085714286</v>
+        <v>1482.84</v>
       </c>
       <c r="O1170" t="n">
-        <v>2989.2171428572</v>
+        <v>2965.68</v>
       </c>
       <c r="P1170" t="n">
         <v>6500</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -2339,10 +2339,10 @@
         <v>14</v>
       </c>
       <c r="N48" t="n">
-        <v>31566.3666</v>
+        <v>31409.32</v>
       </c>
       <c r="O48" t="n">
-        <v>441929.1324</v>
+        <v>439730.48</v>
       </c>
       <c r="P48" t="n">
         <v>45500</v>
@@ -7411,10 +7411,10 @@
         <v>8</v>
       </c>
       <c r="N164" t="n">
-        <v>15210</v>
+        <v>13520</v>
       </c>
       <c r="O164" t="n">
-        <v>121680</v>
+        <v>108160</v>
       </c>
       <c r="P164" t="n">
         <v>14000</v>
@@ -7501,10 +7501,10 @@
         <v>9</v>
       </c>
       <c r="N166" t="n">
-        <v>10899.560863636</v>
+        <v>10752.93</v>
       </c>
       <c r="O166" t="n">
-        <v>98096.04777272399</v>
+        <v>96776.37</v>
       </c>
       <c r="P166" t="n">
         <v>18400</v>
@@ -7578,10 +7578,10 @@
         <v>29</v>
       </c>
       <c r="N168" t="n">
-        <v>1953.5860864553</v>
+        <v>1950.2139481268</v>
       </c>
       <c r="O168" t="n">
-        <v>56653.99650720369</v>
+        <v>56556.2044956772</v>
       </c>
       <c r="P168" t="n">
         <v>2900</v>
@@ -8447,10 +8447,10 @@
         <v>9</v>
       </c>
       <c r="N188" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="O188" t="n">
-        <v>122488.982299269</v>
+        <v>122340.15</v>
       </c>
       <c r="P188" t="n">
         <v>25500</v>
@@ -9016,10 +9016,10 @@
         <v>74</v>
       </c>
       <c r="N201" t="n">
-        <v>2583.5545646704</v>
+        <v>2582.2549874182</v>
       </c>
       <c r="O201" t="n">
-        <v>191183.0377856096</v>
+        <v>191086.8690689468</v>
       </c>
       <c r="P201" t="n">
         <v>4500</v>
@@ -9518,10 +9518,10 @@
         <v>338</v>
       </c>
       <c r="N212" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O212" t="n">
-        <v>1068332.298177388</v>
+        <v>1067694.963642232</v>
       </c>
       <c r="P212" t="n">
         <v>5600</v>
@@ -9697,10 +9697,10 @@
         <v>76</v>
       </c>
       <c r="N216" t="n">
-        <v>8252.563380281699</v>
+        <v>8214</v>
       </c>
       <c r="O216" t="n">
-        <v>627194.8169014092</v>
+        <v>624264</v>
       </c>
       <c r="P216" t="n">
         <v>7900</v>
@@ -9746,10 +9746,10 @@
         <v>74</v>
       </c>
       <c r="N217" t="n">
-        <v>3283.163260274</v>
+        <v>3230.0662191781</v>
       </c>
       <c r="O217" t="n">
-        <v>242954.081260276</v>
+        <v>239024.9002191794</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -10117,10 +10117,10 @@
         <v>67</v>
       </c>
       <c r="N225" t="n">
-        <v>8820</v>
+        <v>8796</v>
       </c>
       <c r="O225" t="n">
-        <v>590940</v>
+        <v>589332</v>
       </c>
       <c r="P225" t="n">
         <v>14900</v>
@@ -12871,10 +12871,10 @@
         <v>8</v>
       </c>
       <c r="N286" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O286" t="n">
-        <v>34976.523739516</v>
+        <v>34969.3701029664</v>
       </c>
       <c r="P286" t="n">
         <v>8900</v>
@@ -13135,10 +13135,10 @@
         <v>37</v>
       </c>
       <c r="N292" t="n">
-        <v>5371.5779551122</v>
+        <v>5331.69</v>
       </c>
       <c r="O292" t="n">
-        <v>198748.3843391514</v>
+        <v>197272.53</v>
       </c>
       <c r="P292" t="n">
         <v>7900</v>
@@ -13541,10 +13541,10 @@
         <v>34</v>
       </c>
       <c r="N301" t="n">
-        <v>1534.4227525419</v>
+        <v>1532.6290227489</v>
       </c>
       <c r="O301" t="n">
-        <v>52170.3735864246</v>
+        <v>52109.3867734626</v>
       </c>
       <c r="P301" t="n">
         <v>1200</v>
@@ -14462,10 +14462,10 @@
         <v>58</v>
       </c>
       <c r="N321" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O321" t="n">
-        <v>219020.6217616574</v>
+        <v>218172.8</v>
       </c>
       <c r="P321" t="n">
         <v>6900</v>
@@ -15671,10 +15671,10 @@
         <v>1</v>
       </c>
       <c r="N348" t="n">
-        <v>19114.611111111</v>
+        <v>18598</v>
       </c>
       <c r="O348" t="n">
-        <v>19114.611111111</v>
+        <v>18598</v>
       </c>
       <c r="P348" t="n">
         <v>21900</v>
@@ -16895,10 +16895,10 @@
         <v>35</v>
       </c>
       <c r="N375" t="n">
-        <v>14292.620246914</v>
+        <v>14118.32</v>
       </c>
       <c r="O375" t="n">
-        <v>500241.70864199</v>
+        <v>494141.2</v>
       </c>
       <c r="P375" t="n">
         <v>17900</v>
@@ -16941,10 +16941,10 @@
         <v>14</v>
       </c>
       <c r="N376" t="n">
-        <v>9446.666666666701</v>
+        <v>8720</v>
       </c>
       <c r="O376" t="n">
-        <v>132253.3333333338</v>
+        <v>122080</v>
       </c>
       <c r="P376" t="n">
         <v>10900</v>
@@ -17075,10 +17075,10 @@
         <v>11</v>
       </c>
       <c r="N379" t="n">
-        <v>19359</v>
+        <v>19120</v>
       </c>
       <c r="O379" t="n">
-        <v>212949</v>
+        <v>210320</v>
       </c>
       <c r="P379" t="n">
         <v>23900</v>
@@ -18012,10 +18012,10 @@
         <v>2</v>
       </c>
       <c r="N400" t="n">
-        <v>7719.830483871</v>
+        <v>7537.4723387097</v>
       </c>
       <c r="O400" t="n">
-        <v>15439.660967742</v>
+        <v>15074.9446774194</v>
       </c>
       <c r="P400" t="n">
         <v>8900</v>
@@ -18217,10 +18217,10 @@
         <v>11</v>
       </c>
       <c r="N405" t="n">
-        <v>1974.990872211</v>
+        <v>1969</v>
       </c>
       <c r="O405" t="n">
-        <v>21724.899594321</v>
+        <v>21659</v>
       </c>
       <c r="P405" t="n">
         <v>1500</v>
@@ -18299,10 +18299,10 @@
         <v>52</v>
       </c>
       <c r="N407" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O407" t="n">
-        <v>457572.2077097496</v>
+        <v>457312.96</v>
       </c>
       <c r="P407" t="n">
         <v>14500</v>
@@ -19313,10 +19313,10 @@
         <v>4</v>
       </c>
       <c r="N431" t="n">
-        <v>57801.91954023</v>
+        <v>56503</v>
       </c>
       <c r="O431" t="n">
-        <v>231207.67816092</v>
+        <v>226012</v>
       </c>
       <c r="P431" t="n">
         <v>90500</v>
@@ -20527,10 +20527,10 @@
         <v>23</v>
       </c>
       <c r="N459" t="n">
-        <v>22761.155411606</v>
+        <v>22730.48</v>
       </c>
       <c r="O459" t="n">
-        <v>523506.574466938</v>
+        <v>522801.04</v>
       </c>
       <c r="P459" t="n">
         <v>36900</v>
@@ -20829,7 +20829,7 @@
         <v>0</v>
       </c>
       <c r="N466" t="n">
-        <v>4102.8563673709</v>
+        <v>4100.45</v>
       </c>
       <c r="O466" t="n">
         <v>0</v>
@@ -20962,10 +20962,10 @@
         <v>44</v>
       </c>
       <c r="N469" t="n">
-        <v>5455.0456387665</v>
+        <v>5431.12</v>
       </c>
       <c r="O469" t="n">
-        <v>240022.008105726</v>
+        <v>238969.28</v>
       </c>
       <c r="P469" t="n">
         <v>8900</v>
@@ -24437,10 +24437,10 @@
         <v>34</v>
       </c>
       <c r="N546" t="n">
-        <v>3351.5905882353</v>
+        <v>3079.84</v>
       </c>
       <c r="O546" t="n">
-        <v>113954.0800000002</v>
+        <v>104714.56</v>
       </c>
       <c r="P546" t="n">
         <v>2900</v>
@@ -24486,10 +24486,10 @@
         <v>13</v>
       </c>
       <c r="N547" t="n">
-        <v>9252.7923611111</v>
+        <v>9188.98</v>
       </c>
       <c r="O547" t="n">
-        <v>120286.3006944443</v>
+        <v>119456.74</v>
       </c>
       <c r="P547" t="n">
         <v>12900</v>
@@ -25317,10 +25317,10 @@
         <v>7</v>
       </c>
       <c r="N565" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O565" t="n">
-        <v>126162.4448</v>
+        <v>126112</v>
       </c>
       <c r="P565" t="n">
         <v>29900</v>
@@ -26522,10 +26522,10 @@
         <v>16</v>
       </c>
       <c r="N591" t="n">
-        <v>7961.912</v>
+        <v>7108.85</v>
       </c>
       <c r="O591" t="n">
-        <v>127390.592</v>
+        <v>113741.6</v>
       </c>
       <c r="P591" t="n">
         <v>7900</v>
@@ -27034,10 +27034,10 @@
         <v>46</v>
       </c>
       <c r="N602" t="n">
-        <v>3950.9108864697</v>
+        <v>3938.66</v>
       </c>
       <c r="O602" t="n">
-        <v>181741.9007776062</v>
+        <v>181178.36</v>
       </c>
       <c r="P602" t="n">
         <v>4500</v>
@@ -27495,10 +27495,10 @@
         <v>23</v>
       </c>
       <c r="N612" t="n">
-        <v>10448.584837545</v>
+        <v>10411</v>
       </c>
       <c r="O612" t="n">
-        <v>240317.451263535</v>
+        <v>239453</v>
       </c>
       <c r="P612" t="n">
         <v>16900</v>
@@ -27679,10 +27679,10 @@
         <v>12</v>
       </c>
       <c r="N616" t="n">
-        <v>6074.962962963</v>
+        <v>5858</v>
       </c>
       <c r="O616" t="n">
-        <v>72899.555555556</v>
+        <v>70296</v>
       </c>
       <c r="P616" t="n">
         <v>9500</v>
@@ -30857,10 +30857,10 @@
         <v>129</v>
       </c>
       <c r="N685" t="n">
-        <v>60093.865363735</v>
+        <v>59834</v>
       </c>
       <c r="O685" t="n">
-        <v>7752108.631921815</v>
+        <v>7718586</v>
       </c>
       <c r="P685" t="n">
         <v>7900</v>
@@ -31458,10 +31458,10 @@
         <v>27</v>
       </c>
       <c r="N698" t="n">
-        <v>40318.846625767</v>
+        <v>40073</v>
       </c>
       <c r="O698" t="n">
-        <v>1088608.858895709</v>
+        <v>1081971</v>
       </c>
       <c r="P698" t="n">
         <v>64900</v>
@@ -31642,10 +31642,10 @@
         <v>33</v>
       </c>
       <c r="N702" t="n">
-        <v>3652.664695122</v>
+        <v>3639.35</v>
       </c>
       <c r="O702" t="n">
-        <v>120537.934939026</v>
+        <v>120098.55</v>
       </c>
       <c r="P702" t="n">
         <v>7500</v>
@@ -32240,10 +32240,10 @@
         <v>3</v>
       </c>
       <c r="N715" t="n">
-        <v>15334.994264706</v>
+        <v>15223.06</v>
       </c>
       <c r="O715" t="n">
-        <v>46004.982794118</v>
+        <v>45669.18</v>
       </c>
       <c r="P715" t="n">
         <v>17500</v>
@@ -32514,10 +32514,10 @@
         <v>313</v>
       </c>
       <c r="N721" t="n">
-        <v>2463.8091310592</v>
+        <v>2458.5124991023</v>
       </c>
       <c r="O721" t="n">
-        <v>771172.2580215295</v>
+        <v>769514.4122190198</v>
       </c>
       <c r="P721" t="n">
         <v>3500</v>
@@ -33568,10 +33568,10 @@
         <v>42</v>
       </c>
       <c r="N744" t="n">
-        <v>1692.9473786408</v>
+        <v>1668.6473786408</v>
       </c>
       <c r="O744" t="n">
-        <v>71103.7899029136</v>
+        <v>70083.1899029136</v>
       </c>
       <c r="P744" t="n">
         <v>2500</v>
@@ -35476,10 +35476,10 @@
         <v>19</v>
       </c>
       <c r="N785" t="n">
-        <v>3650.5019029126</v>
+        <v>3629.36</v>
       </c>
       <c r="O785" t="n">
-        <v>69359.5361553394</v>
+        <v>68957.84</v>
       </c>
       <c r="P785" t="n">
         <v>3900</v>
@@ -36076,10 +36076,10 @@
         <v>22</v>
       </c>
       <c r="N798" t="n">
-        <v>2479.6920689655</v>
+        <v>2357.74</v>
       </c>
       <c r="O798" t="n">
-        <v>54553.22551724099</v>
+        <v>51870.28</v>
       </c>
       <c r="P798" t="n">
         <v>3000</v>
@@ -36781,10 +36781,10 @@
         <v>772</v>
       </c>
       <c r="N813" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O813" t="n">
-        <v>266829.6717691022</v>
+        <v>266771.0739744293</v>
       </c>
       <c r="P813" t="n">
         <v>600</v>
@@ -36972,10 +36972,10 @@
         <v>472</v>
       </c>
       <c r="N817" t="n">
-        <v>711.87861852814</v>
+        <v>711.33664519481</v>
       </c>
       <c r="O817" t="n">
-        <v>336006.7079452821</v>
+        <v>335750.8965319503</v>
       </c>
       <c r="P817" t="n">
         <v>900</v>
@@ -38343,10 +38343,10 @@
         <v>21</v>
       </c>
       <c r="N847" t="n">
-        <v>3285.20748</v>
+        <v>3259.13444</v>
       </c>
       <c r="O847" t="n">
-        <v>68989.35708</v>
+        <v>68441.82324</v>
       </c>
       <c r="P847" t="n">
         <v>3600</v>
@@ -41841,10 +41841,10 @@
         <v>3</v>
       </c>
       <c r="N921" t="n">
-        <v>7887.3163636364</v>
+        <v>7230.04</v>
       </c>
       <c r="O921" t="n">
-        <v>23661.9490909092</v>
+        <v>21690.12</v>
       </c>
       <c r="P921" t="n">
         <v>15900</v>
@@ -42518,10 +42518,10 @@
         <v>33</v>
       </c>
       <c r="N935" t="n">
-        <v>5480.6844036697</v>
+        <v>5430.86</v>
       </c>
       <c r="O935" t="n">
-        <v>180862.5853211001</v>
+        <v>179218.38</v>
       </c>
       <c r="P935" t="n">
         <v>13900</v>
@@ -42711,10 +42711,10 @@
         <v>27</v>
       </c>
       <c r="N939" t="n">
-        <v>4726.0862068966</v>
+        <v>4568.55</v>
       </c>
       <c r="O939" t="n">
-        <v>127604.3275862082</v>
+        <v>123350.85</v>
       </c>
       <c r="P939" t="n">
         <v>6900</v>
@@ -43280,10 +43280,10 @@
         <v>30</v>
       </c>
       <c r="N951" t="n">
-        <v>4234.4238541667</v>
+        <v>4190.77</v>
       </c>
       <c r="O951" t="n">
-        <v>127032.715625001</v>
+        <v>125723.1</v>
       </c>
       <c r="P951" t="n">
         <v>5900</v>
@@ -43329,10 +43329,10 @@
         <v>15</v>
       </c>
       <c r="N952" t="n">
-        <v>3503.9263942308</v>
+        <v>3499.72</v>
       </c>
       <c r="O952" t="n">
-        <v>52558.89591346199</v>
+        <v>52495.8</v>
       </c>
       <c r="P952" t="n">
         <v>6900</v>
@@ -43378,10 +43378,10 @@
         <v>6</v>
       </c>
       <c r="N953" t="n">
-        <v>5370.7341880342</v>
+        <v>5347.88</v>
       </c>
       <c r="O953" t="n">
-        <v>32224.4051282052</v>
+        <v>32087.28</v>
       </c>
       <c r="P953" t="n">
         <v>7900</v>
@@ -43427,10 +43427,10 @@
         <v>16</v>
       </c>
       <c r="N954" t="n">
-        <v>4593.2494352159</v>
+        <v>4578.04</v>
       </c>
       <c r="O954" t="n">
-        <v>73491.9909634544</v>
+        <v>73248.64</v>
       </c>
       <c r="P954" t="n">
         <v>7500</v>
@@ -44105,10 +44105,10 @@
         <v>27</v>
       </c>
       <c r="N968" t="n">
-        <v>5045.3355555556</v>
+        <v>4697.3814814815</v>
       </c>
       <c r="O968" t="n">
-        <v>136224.0600000012</v>
+        <v>126829.3000000005</v>
       </c>
       <c r="P968" t="n">
         <v>10900</v>
@@ -46193,10 +46193,10 @@
         <v>79</v>
       </c>
       <c r="N1012" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O1012" t="n">
-        <v>557430.7748950903</v>
+        <v>556708.2463292237</v>
       </c>
       <c r="P1012" t="n">
         <v>9900</v>
@@ -48062,10 +48062,10 @@
         <v>8</v>
       </c>
       <c r="N1052" t="n">
-        <v>2490.4710359188</v>
+        <v>2489.1752628839</v>
       </c>
       <c r="O1052" t="n">
-        <v>19923.7682873504</v>
+        <v>19913.4021030712</v>
       </c>
       <c r="P1052" t="n">
         <v>3000</v>
@@ -48314,10 +48314,10 @@
         <v>43</v>
       </c>
       <c r="N1058" t="n">
-        <v>1796.1048285838</v>
+        <v>1794.2879574714</v>
       </c>
       <c r="O1058" t="n">
-        <v>77232.50762910341</v>
+        <v>77154.3821712702</v>
       </c>
       <c r="P1058" t="n">
         <v>1600</v>
@@ -50348,10 +50348,10 @@
         <v>3</v>
       </c>
       <c r="N1102" t="n">
-        <v>12545.454545455</v>
+        <v>12000</v>
       </c>
       <c r="O1102" t="n">
-        <v>37636.363636365</v>
+        <v>36000</v>
       </c>
       <c r="P1102" t="n">
         <v>15000</v>
@@ -51084,10 +51084,10 @@
         <v>7</v>
       </c>
       <c r="N1118" t="n">
-        <v>18186.087111111</v>
+        <v>17986.24</v>
       </c>
       <c r="O1118" t="n">
-        <v>127302.609777777</v>
+        <v>125903.68</v>
       </c>
       <c r="P1118" t="n">
         <v>18500</v>
@@ -51360,10 +51360,10 @@
         <v>35</v>
       </c>
       <c r="N1124" t="n">
-        <v>7496.4757709251</v>
+        <v>7480</v>
       </c>
       <c r="O1124" t="n">
-        <v>262376.6519823785</v>
+        <v>261800</v>
       </c>
       <c r="P1124" t="n">
         <v>9500</v>
@@ -51406,10 +51406,10 @@
         <v>38</v>
       </c>
       <c r="N1125" t="n">
-        <v>6525.1343283582</v>
+        <v>6336</v>
       </c>
       <c r="O1125" t="n">
-        <v>247955.1044776116</v>
+        <v>240768</v>
       </c>
       <c r="P1125" t="n">
         <v>7500</v>
@@ -51498,10 +51498,10 @@
         <v>27</v>
       </c>
       <c r="N1127" t="n">
-        <v>5320.824742268</v>
+        <v>5280</v>
       </c>
       <c r="O1127" t="n">
-        <v>143662.268041236</v>
+        <v>142560</v>
       </c>
       <c r="P1127" t="n">
         <v>6900</v>
@@ -53442,10 +53442,10 @@
         <v>6</v>
       </c>
       <c r="N1169" t="n">
-        <v>965.501</v>
+        <v>910.85</v>
       </c>
       <c r="O1169" t="n">
-        <v>5793.005999999999</v>
+        <v>5465.1</v>
       </c>
       <c r="P1169" t="n">
         <v>7900</v>
@@ -53534,10 +53534,10 @@
         <v>2</v>
       </c>
       <c r="N1171" t="n">
-        <v>4936.5625</v>
+        <v>3949.25</v>
       </c>
       <c r="O1171" t="n">
-        <v>9873.125</v>
+        <v>7898.5</v>
       </c>
       <c r="P1171" t="n">
         <v>12500</v>
@@ -54998,10 +54998,10 @@
         <v>41</v>
       </c>
       <c r="N1202" t="n">
-        <v>2547.0191593353</v>
+        <v>2539.5717399804</v>
       </c>
       <c r="O1202" t="n">
-        <v>104427.7855327473</v>
+        <v>104122.4413391964</v>
       </c>
       <c r="P1202" t="n">
         <v>2900</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -15759,10 +15759,10 @@
         <v>12</v>
       </c>
       <c r="N350" t="n">
-        <v>1302.8935476464</v>
+        <v>1301.3994029851</v>
       </c>
       <c r="O350" t="n">
-        <v>15634.7225717568</v>
+        <v>15616.7928358212</v>
       </c>
       <c r="P350" t="n">
         <v>2000</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -1654,22 +1654,22 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
         <v>3585</v>
       </c>
       <c r="O31" t="n">
-        <v>86040</v>
+        <v>68115</v>
       </c>
       <c r="P31" t="n">
         <v>4500</v>
       </c>
       <c r="Q31" t="n">
-        <v>108000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="32">
@@ -3406,22 +3406,22 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N72" t="n">
         <v>12837.974883721</v>
       </c>
       <c r="O72" t="n">
-        <v>102703.799069768</v>
+        <v>89865.824186047</v>
       </c>
       <c r="P72" t="n">
         <v>22900</v>
       </c>
       <c r="Q72" t="n">
-        <v>183200</v>
+        <v>160300</v>
       </c>
     </row>
     <row r="73">
@@ -3757,22 +3757,22 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N80" t="n">
         <v>13712.833333333</v>
       </c>
       <c r="O80" t="n">
-        <v>54851.333333332</v>
+        <v>27425.666666666</v>
       </c>
       <c r="P80" t="n">
         <v>22600</v>
       </c>
       <c r="Q80" t="n">
-        <v>90400</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="81">
@@ -12737,22 +12737,22 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M283" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N283" t="n">
         <v>3041.6600141844</v>
       </c>
       <c r="O283" t="n">
-        <v>21291.6200992908</v>
+        <v>6083.3200283688</v>
       </c>
       <c r="P283" t="n">
         <v>5500</v>
       </c>
       <c r="Q283" t="n">
-        <v>38500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="284">
@@ -16086,22 +16086,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M357" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="N357" t="n">
         <v>1965</v>
       </c>
       <c r="O357" t="n">
-        <v>86460</v>
+        <v>62880</v>
       </c>
       <c r="P357" t="n">
         <v>3700</v>
       </c>
       <c r="Q357" t="n">
-        <v>162800</v>
+        <v>118400</v>
       </c>
     </row>
     <row r="358">
@@ -25500,22 +25500,22 @@
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M569" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N569" t="n">
         <v>5148</v>
       </c>
       <c r="O569" t="n">
-        <v>231660</v>
+        <v>216216</v>
       </c>
       <c r="P569" t="n">
         <v>8600</v>
       </c>
       <c r="Q569" t="n">
-        <v>387000</v>
+        <v>361200</v>
       </c>
     </row>
     <row r="570">
@@ -29749,22 +29749,22 @@
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M661" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="N661" t="n">
         <v>4984</v>
       </c>
       <c r="O661" t="n">
-        <v>518336</v>
+        <v>458528</v>
       </c>
       <c r="P661" t="n">
         <v>7900</v>
       </c>
       <c r="Q661" t="n">
-        <v>821600</v>
+        <v>726800</v>
       </c>
     </row>
     <row r="662">
@@ -46241,22 +46241,22 @@
         <v>0</v>
       </c>
       <c r="L1013" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1013" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N1013" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1013" t="n">
-        <v>194707.76</v>
+        <v>121692.35</v>
       </c>
       <c r="P1013" t="n">
         <v>27900</v>
       </c>
       <c r="Q1013" t="n">
-        <v>223200</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="1014">
@@ -47111,22 +47111,22 @@
         <v>0</v>
       </c>
       <c r="L1031" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1031" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N1031" t="n">
         <v>1262.07</v>
       </c>
       <c r="O1031" t="n">
-        <v>153972.54</v>
+        <v>150186.33</v>
       </c>
       <c r="P1031" t="n">
         <v>8900</v>
       </c>
       <c r="Q1031" t="n">
-        <v>1085800</v>
+        <v>1059100</v>
       </c>
     </row>
     <row r="1032">
@@ -47160,22 +47160,22 @@
         <v>0</v>
       </c>
       <c r="L1032" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1032" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="N1032" t="n">
         <v>540.40121359223</v>
       </c>
       <c r="O1032" t="n">
-        <v>42151.29466019394</v>
+        <v>36747.28252427164</v>
       </c>
       <c r="P1032" t="n">
         <v>2500</v>
       </c>
       <c r="Q1032" t="n">
-        <v>195000</v>
+        <v>170000</v>
       </c>
     </row>
     <row r="1033">
@@ -51684,22 +51684,22 @@
         <v>0</v>
       </c>
       <c r="L1131" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1131" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="N1131" t="n">
         <v>4400</v>
       </c>
       <c r="O1131" t="n">
-        <v>365200</v>
+        <v>312400</v>
       </c>
       <c r="P1131" t="n">
         <v>5900</v>
       </c>
       <c r="Q1131" t="n">
-        <v>489700</v>
+        <v>418900</v>
       </c>
     </row>
     <row r="1132">
@@ -51926,22 +51926,22 @@
         <v>0</v>
       </c>
       <c r="L1136" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1136" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="N1136" t="n">
         <v>3520</v>
       </c>
       <c r="O1136" t="n">
-        <v>147840</v>
+        <v>119680</v>
       </c>
       <c r="P1136" t="n">
         <v>4500</v>
       </c>
       <c r="Q1136" t="n">
-        <v>189000</v>
+        <v>153000</v>
       </c>
     </row>
     <row r="1137">
@@ -52892,22 +52892,22 @@
         <v>0</v>
       </c>
       <c r="L1157" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M1157" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="N1157" t="n">
         <v>1900</v>
       </c>
       <c r="O1157" t="n">
-        <v>106400</v>
+        <v>38000</v>
       </c>
       <c r="P1157" t="n">
         <v>2300</v>
       </c>
       <c r="Q1157" t="n">
-        <v>128800</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="1158">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -944,10 +944,10 @@
         <v>26</v>
       </c>
       <c r="N13" t="n">
-        <v>1830.8488673139</v>
+        <v>1811.3101499423</v>
       </c>
       <c r="O13" t="n">
-        <v>47602.0705501614</v>
+        <v>47094.0638984998</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1579,19 +1579,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="N29" t="n">
         <v>18777.5</v>
       </c>
       <c r="O29" t="n">
-        <v>168997.5</v>
+        <v>544547.5</v>
       </c>
       <c r="P29" t="n">
         <v>27300</v>
       </c>
       <c r="Q29" t="n">
-        <v>245700</v>
+        <v>791700</v>
       </c>
     </row>
     <row r="30">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="K40" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2297,19 +2297,19 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N47" t="n">
         <v>27000</v>
       </c>
       <c r="O47" t="n">
-        <v>405000</v>
+        <v>378000</v>
       </c>
       <c r="P47" t="n">
         <v>30000</v>
       </c>
       <c r="Q47" t="n">
-        <v>450000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="48">
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2950,19 +2950,19 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
         <v>29000</v>
       </c>
       <c r="O62" t="n">
-        <v>145000</v>
+        <v>116000</v>
       </c>
       <c r="P62" t="n">
         <v>34800</v>
       </c>
       <c r="Q62" t="n">
-        <v>174000</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="63">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4197,10 +4197,10 @@
         <v>7</v>
       </c>
       <c r="N91" t="n">
-        <v>8171.5883333333</v>
+        <v>8171.5877777778</v>
       </c>
       <c r="O91" t="n">
-        <v>57201.1183333331</v>
+        <v>57201.1144444446</v>
       </c>
       <c r="P91" t="n">
         <v>17200</v>
@@ -4612,10 +4612,10 @@
         <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>200072.20240385</v>
+        <v>200072.2037234</v>
       </c>
       <c r="O100" t="n">
-        <v>1000361.01201925</v>
+        <v>1000361.018617</v>
       </c>
       <c r="P100" t="n">
         <v>312000</v>
@@ -4659,10 +4659,10 @@
         <v>3</v>
       </c>
       <c r="N101" t="n">
-        <v>344599.17844444</v>
+        <v>344599.17815789</v>
       </c>
       <c r="O101" t="n">
-        <v>1033797.53533332</v>
+        <v>1033797.53447367</v>
       </c>
       <c r="P101" t="n">
         <v>532900</v>
@@ -5518,10 +5518,10 @@
         <v>4</v>
       </c>
       <c r="N121" t="n">
-        <v>427.91886524823</v>
+        <v>427.91884892086</v>
       </c>
       <c r="O121" t="n">
-        <v>1711.67546099292</v>
+        <v>1711.67539568344</v>
       </c>
       <c r="P121" t="n">
         <v>6800</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="K138" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K139" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -7617,10 +7617,10 @@
         <v>29</v>
       </c>
       <c r="N169" t="n">
-        <v>1950.2139095128</v>
+        <v>1950.2137350835</v>
       </c>
       <c r="O169" t="n">
-        <v>56556.2033758712</v>
+        <v>56556.1983174215</v>
       </c>
       <c r="P169" t="n">
         <v>2900</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
         <v>319</v>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K192" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>35</v>
       </c>
       <c r="N205" t="n">
-        <v>5216.8958858357</v>
+        <v>5216.8958827104</v>
       </c>
       <c r="O205" t="n">
-        <v>182591.3560042495</v>
+        <v>182591.355894864</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -9331,19 +9331,19 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="N208" t="n">
         <v>5503.85</v>
       </c>
       <c r="O208" t="n">
-        <v>66046.20000000001</v>
+        <v>231161.7</v>
       </c>
       <c r="P208" t="n">
         <v>9500</v>
       </c>
       <c r="Q208" t="n">
-        <v>114000</v>
+        <v>399000</v>
       </c>
     </row>
     <row r="209">
@@ -9545,28 +9545,28 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="N213" t="n">
-        <v>3158.86083922</v>
+        <v>3158.8608398885</v>
       </c>
       <c r="O213" t="n">
-        <v>1064536.10281714</v>
+        <v>1013994.329604208</v>
       </c>
       <c r="P213" t="n">
         <v>5600</v>
       </c>
       <c r="Q213" t="n">
-        <v>1887200</v>
+        <v>1797600</v>
       </c>
     </row>
     <row r="214">
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="K217" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9782,19 +9782,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N218" t="n">
-        <v>3230.0662191781</v>
+        <v>3230.0661983471</v>
       </c>
       <c r="O218" t="n">
-        <v>239024.9002191794</v>
+        <v>232564.7662809912</v>
       </c>
       <c r="P218" t="n">
         <v>6200</v>
       </c>
       <c r="Q218" t="n">
-        <v>458800</v>
+        <v>446400</v>
       </c>
     </row>
     <row r="219">
@@ -9969,10 +9969,10 @@
         <v>169</v>
       </c>
       <c r="N222" t="n">
-        <v>2694.8230922931</v>
+        <v>2694.8230326296</v>
       </c>
       <c r="O222" t="n">
-        <v>455425.102597534</v>
+        <v>455425.0925144025</v>
       </c>
       <c r="P222" t="n">
         <v>4900</v>
@@ -10335,10 +10335,10 @@
         <v>34</v>
       </c>
       <c r="N230" t="n">
-        <v>3795.7100076234</v>
+        <v>3795.7100076292</v>
       </c>
       <c r="O230" t="n">
-        <v>129054.1402591956</v>
+        <v>129054.1402593928</v>
       </c>
       <c r="P230" t="n">
         <v>6200</v>
@@ -10416,22 +10416,22 @@
         <v>0</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M232" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="N232" t="n">
         <v>2612.77</v>
       </c>
       <c r="O232" t="n">
-        <v>323983.48</v>
+        <v>292630.24</v>
       </c>
       <c r="P232" t="n">
         <v>4900</v>
       </c>
       <c r="Q232" t="n">
-        <v>607600</v>
+        <v>548800</v>
       </c>
     </row>
     <row r="233">
@@ -10456,28 +10456,28 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N233" t="n">
         <v>4357.55</v>
       </c>
       <c r="O233" t="n">
-        <v>1407488.65</v>
+        <v>1398773.55</v>
       </c>
       <c r="P233" t="n">
         <v>7500</v>
       </c>
       <c r="Q233" t="n">
-        <v>2422500</v>
+        <v>2407500</v>
       </c>
     </row>
     <row r="234">
@@ -10548,13 +10548,13 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
         <v>8</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10747,19 +10747,19 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N239" t="n">
         <v>1203.38</v>
       </c>
       <c r="O239" t="n">
-        <v>36101.4</v>
+        <v>27677.74</v>
       </c>
       <c r="P239" t="n">
         <v>1900</v>
       </c>
       <c r="Q239" t="n">
-        <v>57000</v>
+        <v>43700</v>
       </c>
     </row>
     <row r="240">
@@ -11240,22 +11240,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N250" t="n">
         <v>10716.34</v>
       </c>
       <c r="O250" t="n">
-        <v>128596.08</v>
+        <v>107163.4</v>
       </c>
       <c r="P250" t="n">
         <v>39000</v>
       </c>
       <c r="Q250" t="n">
-        <v>468000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="251">
@@ -11336,10 +11336,10 @@
         <v>23</v>
       </c>
       <c r="N252" t="n">
-        <v>3594.2529978118</v>
+        <v>3594.2529721816</v>
       </c>
       <c r="O252" t="n">
-        <v>82667.8189496714</v>
+        <v>82667.8183601768</v>
       </c>
       <c r="P252" t="n">
         <v>6500</v>
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -11782,19 +11782,19 @@
         <v>2</v>
       </c>
       <c r="M262" t="n">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="N262" t="n">
         <v>2090.85</v>
       </c>
       <c r="O262" t="n">
-        <v>692071.35</v>
+        <v>625164.15</v>
       </c>
       <c r="P262" t="n">
         <v>2900</v>
       </c>
       <c r="Q262" t="n">
-        <v>959900</v>
+        <v>867100</v>
       </c>
     </row>
     <row r="263">
@@ -12495,22 +12495,22 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
         <v>66</v>
       </c>
       <c r="N278" t="n">
-        <v>3472.276224504</v>
+        <v>3472.2762270961</v>
       </c>
       <c r="O278" t="n">
-        <v>229170.230817264</v>
+        <v>229170.2309883426</v>
       </c>
       <c r="P278" t="n">
         <v>5900</v>
@@ -12782,10 +12782,10 @@
         <v>2</v>
       </c>
       <c r="N284" t="n">
-        <v>3041.6600141945</v>
+        <v>3041.6600142959</v>
       </c>
       <c r="O284" t="n">
-        <v>6083.320028389</v>
+        <v>6083.3200285918</v>
       </c>
       <c r="P284" t="n">
         <v>5500</v>
@@ -12910,10 +12910,10 @@
         <v>8</v>
       </c>
       <c r="N287" t="n">
-        <v>4371.7675214841</v>
+        <v>4371.1712631292</v>
       </c>
       <c r="O287" t="n">
-        <v>34974.1401718728</v>
+        <v>34969.3701050336</v>
       </c>
       <c r="P287" t="n">
         <v>8900</v>
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13043,19 +13043,19 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="N290" t="n">
-        <v>1592.5651537745</v>
+        <v>1592.5649367089</v>
       </c>
       <c r="O290" t="n">
-        <v>348771.7686766155</v>
+        <v>315327.8574683622</v>
       </c>
       <c r="P290" t="n">
         <v>3900</v>
       </c>
       <c r="Q290" t="n">
-        <v>854100</v>
+        <v>772200</v>
       </c>
     </row>
     <row r="291">
@@ -13121,7 +13121,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13130,19 +13130,19 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N292" t="n">
-        <v>3668.2806919793</v>
+        <v>3655.96</v>
       </c>
       <c r="O292" t="n">
-        <v>176077.4732150064</v>
+        <v>153550.32</v>
       </c>
       <c r="P292" t="n">
         <v>5500</v>
       </c>
       <c r="Q292" t="n">
-        <v>264000</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="293">
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13443,19 +13443,19 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="N299" t="n">
-        <v>4649.4131187686</v>
+        <v>4648.6</v>
       </c>
       <c r="O299" t="n">
-        <v>423096.5938079426</v>
+        <v>469508.6</v>
       </c>
       <c r="P299" t="n">
         <v>8900</v>
       </c>
       <c r="Q299" t="n">
-        <v>809900</v>
+        <v>898900</v>
       </c>
     </row>
     <row r="300">
@@ -13878,7 +13878,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -13887,19 +13887,19 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N309" t="n">
         <v>1387.55</v>
       </c>
       <c r="O309" t="n">
-        <v>187319.25</v>
+        <v>181769.05</v>
       </c>
       <c r="P309" t="n">
         <v>2300</v>
       </c>
       <c r="Q309" t="n">
-        <v>310500</v>
+        <v>301300</v>
       </c>
     </row>
     <row r="310">
@@ -14208,7 +14208,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -14217,19 +14217,19 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N316" t="n">
         <v>16897</v>
       </c>
       <c r="O316" t="n">
-        <v>118279</v>
+        <v>101382</v>
       </c>
       <c r="P316" t="n">
         <v>27900</v>
       </c>
       <c r="Q316" t="n">
-        <v>195300</v>
+        <v>167400</v>
       </c>
     </row>
     <row r="317">
@@ -14489,7 +14489,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14498,19 +14498,19 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="N322" t="n">
         <v>3761.6</v>
       </c>
       <c r="O322" t="n">
-        <v>218172.8</v>
+        <v>244504</v>
       </c>
       <c r="P322" t="n">
         <v>6900</v>
       </c>
       <c r="Q322" t="n">
-        <v>400200</v>
+        <v>448500</v>
       </c>
     </row>
     <row r="323">
@@ -14625,28 +14625,28 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M325" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N325" t="n">
         <v>11921.4</v>
       </c>
       <c r="O325" t="n">
-        <v>143056.8</v>
+        <v>190742.4</v>
       </c>
       <c r="P325" t="n">
         <v>19900</v>
       </c>
       <c r="Q325" t="n">
-        <v>238800</v>
+        <v>318400</v>
       </c>
     </row>
     <row r="326">
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K334" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -15222,28 +15222,28 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="N338" t="n">
-        <v>1630.9246075494</v>
+        <v>1630.9246283479</v>
       </c>
       <c r="O338" t="n">
-        <v>194080.0282983786</v>
+        <v>172878.0106048774</v>
       </c>
       <c r="P338" t="n">
         <v>2500</v>
       </c>
       <c r="Q338" t="n">
-        <v>297500</v>
+        <v>265000</v>
       </c>
     </row>
     <row r="339">
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
@@ -15323,19 +15323,19 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N340" t="n">
-        <v>1699.5482625995</v>
+        <v>1690.5792942743</v>
       </c>
       <c r="O340" t="n">
-        <v>39089.6100397885</v>
+        <v>33811.585885486</v>
       </c>
       <c r="P340" t="n">
         <v>2900</v>
       </c>
       <c r="Q340" t="n">
-        <v>66700</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="341">
@@ -15360,28 +15360,28 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>650</v>
+        <v>622</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="N341" t="n">
-        <v>1551.3666948085</v>
+        <v>1550.1947087933</v>
       </c>
       <c r="O341" t="n">
-        <v>994426.0513722484</v>
+        <v>964221.1088694326</v>
       </c>
       <c r="P341" t="n">
         <v>2500</v>
       </c>
       <c r="Q341" t="n">
-        <v>1602500</v>
+        <v>1555000</v>
       </c>
     </row>
     <row r="342">
@@ -15418,10 +15418,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>1579.3828229665</v>
+        <v>1579.3814948454</v>
       </c>
       <c r="O342" t="n">
-        <v>1579.3828229665</v>
+        <v>1579.3814948454</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
@@ -15452,28 +15452,28 @@
         </is>
       </c>
       <c r="J343" t="n">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="K343" t="n">
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="N343" t="n">
-        <v>2407.4618268285</v>
+        <v>2403.5207171448</v>
       </c>
       <c r="O343" t="n">
-        <v>775202.708238777</v>
+        <v>740284.3808805984</v>
       </c>
       <c r="P343" t="n">
         <v>3500</v>
       </c>
       <c r="Q343" t="n">
-        <v>1127000</v>
+        <v>1078000</v>
       </c>
     </row>
     <row r="344">
@@ -16922,10 +16922,10 @@
         </is>
       </c>
       <c r="J376" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K376" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -16968,7 +16968,7 @@
         </is>
       </c>
       <c r="J377" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K377" t="n">
         <v>0</v>
@@ -16977,19 +16977,19 @@
         <v>0</v>
       </c>
       <c r="M377" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N377" t="n">
         <v>8720</v>
       </c>
       <c r="O377" t="n">
-        <v>122080</v>
+        <v>104640</v>
       </c>
       <c r="P377" t="n">
         <v>10900</v>
       </c>
       <c r="Q377" t="n">
-        <v>152600</v>
+        <v>130800</v>
       </c>
     </row>
     <row r="378">
@@ -17867,7 +17867,7 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K397" t="n">
         <v>0</v>
@@ -17876,19 +17876,19 @@
         <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N397" t="n">
         <v>9338</v>
       </c>
       <c r="O397" t="n">
-        <v>298816</v>
+        <v>280140</v>
       </c>
       <c r="P397" t="n">
         <v>15500</v>
       </c>
       <c r="Q397" t="n">
-        <v>496000</v>
+        <v>465000</v>
       </c>
     </row>
     <row r="398">
@@ -17911,7 +17911,7 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
@@ -17920,19 +17920,19 @@
         <v>0</v>
       </c>
       <c r="M398" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N398" t="n">
-        <v>4196.872541806</v>
+        <v>4196.8725453531</v>
       </c>
       <c r="O398" t="n">
-        <v>104921.81354515</v>
+        <v>83937.450907062</v>
       </c>
       <c r="P398" t="n">
         <v>5900</v>
       </c>
       <c r="Q398" t="n">
-        <v>147500</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="399">
@@ -18039,7 +18039,7 @@
         </is>
       </c>
       <c r="J401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K401" t="n">
         <v>0</v>
@@ -18048,19 +18048,19 @@
         <v>0</v>
       </c>
       <c r="M401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N401" t="n">
-        <v>7537.4723387097</v>
+        <v>7537.4723577236</v>
       </c>
       <c r="O401" t="n">
-        <v>15074.9446774194</v>
+        <v>7537.4723577236</v>
       </c>
       <c r="P401" t="n">
         <v>8900</v>
       </c>
       <c r="Q401" t="n">
-        <v>17800</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="402">
@@ -18174,10 +18174,10 @@
         <v>17</v>
       </c>
       <c r="N404" t="n">
-        <v>2613.8724035608</v>
+        <v>2610</v>
       </c>
       <c r="O404" t="n">
-        <v>44435.83086053361</v>
+        <v>44370</v>
       </c>
       <c r="P404" t="n">
         <v>3200</v>
@@ -18215,10 +18215,10 @@
         <v>35</v>
       </c>
       <c r="N405" t="n">
-        <v>2086.0024038462</v>
+        <v>2081</v>
       </c>
       <c r="O405" t="n">
-        <v>73010.08413461701</v>
+        <v>72835</v>
       </c>
       <c r="P405" t="n">
         <v>3200</v>
@@ -18244,7 +18244,7 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
@@ -18253,19 +18253,19 @@
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N406" t="n">
         <v>1969</v>
       </c>
       <c r="O406" t="n">
-        <v>21659</v>
+        <v>31504</v>
       </c>
       <c r="P406" t="n">
         <v>1500</v>
       </c>
       <c r="Q406" t="n">
-        <v>16500</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="407">
@@ -18326,7 +18326,7 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K408" t="n">
         <v>0</v>
@@ -18335,19 +18335,19 @@
         <v>0</v>
       </c>
       <c r="M408" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N408" t="n">
         <v>8794.48</v>
       </c>
       <c r="O408" t="n">
-        <v>457312.96</v>
+        <v>448518.48</v>
       </c>
       <c r="P408" t="n">
         <v>14500</v>
       </c>
       <c r="Q408" t="n">
-        <v>754000</v>
+        <v>739500</v>
       </c>
     </row>
     <row r="409">
@@ -18413,13 +18413,13 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K410" t="n">
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M410" t="n">
         <v>81</v>
@@ -18507,10 +18507,10 @@
         <v>59</v>
       </c>
       <c r="N412" t="n">
-        <v>2545.636406397</v>
+        <v>2517.22</v>
       </c>
       <c r="O412" t="n">
-        <v>150192.547977423</v>
+        <v>148515.98</v>
       </c>
       <c r="P412" t="n">
         <v>4200</v>
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
@@ -19006,19 +19006,19 @@
         <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N424" t="n">
         <v>14060.64</v>
       </c>
       <c r="O424" t="n">
-        <v>239030.88</v>
+        <v>224970.24</v>
       </c>
       <c r="P424" t="n">
         <v>22900</v>
       </c>
       <c r="Q424" t="n">
-        <v>389300</v>
+        <v>366400</v>
       </c>
     </row>
     <row r="425">
@@ -19432,10 +19432,10 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K434" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L434" t="n">
         <v>0</v>
@@ -19621,10 +19621,10 @@
         <v>40</v>
       </c>
       <c r="N438" t="n">
-        <v>4285.1963819095</v>
+        <v>4285.1964141414</v>
       </c>
       <c r="O438" t="n">
-        <v>171407.85527638</v>
+        <v>171407.856565656</v>
       </c>
       <c r="P438" t="n">
         <v>6900</v>
@@ -20513,10 +20513,10 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K459" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L459" t="n">
         <v>0</v>
@@ -20867,22 +20867,22 @@
         <v>0</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M467" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N467" t="n">
         <v>16974.69</v>
       </c>
       <c r="O467" t="n">
-        <v>254620.35</v>
+        <v>237645.66</v>
       </c>
       <c r="P467" t="n">
         <v>26900</v>
       </c>
       <c r="Q467" t="n">
-        <v>403500</v>
+        <v>376600</v>
       </c>
     </row>
     <row r="468">
@@ -20907,13 +20907,13 @@
         </is>
       </c>
       <c r="J468" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K468" t="n">
         <v>0</v>
       </c>
       <c r="L468" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M468" t="n">
         <v>7</v>
@@ -21040,28 +21040,28 @@
         </is>
       </c>
       <c r="J471" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="K471" t="n">
         <v>0</v>
       </c>
       <c r="L471" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M471" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="N471" t="n">
-        <v>1600.4118322476</v>
+        <v>1561.0054931836</v>
       </c>
       <c r="O471" t="n">
-        <v>72018.532451142</v>
+        <v>156100.54931836</v>
       </c>
       <c r="P471" t="n">
         <v>2900</v>
       </c>
       <c r="Q471" t="n">
-        <v>130500</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="472">
@@ -21383,7 +21383,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -21392,19 +21392,19 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N479" t="n">
         <v>2214.48</v>
       </c>
       <c r="O479" t="n">
-        <v>46504.08</v>
+        <v>44289.6</v>
       </c>
       <c r="P479" t="n">
         <v>4700</v>
       </c>
       <c r="Q479" t="n">
-        <v>98700</v>
+        <v>94000</v>
       </c>
     </row>
     <row r="480">
@@ -21490,10 +21490,10 @@
         <v>6</v>
       </c>
       <c r="N481" t="n">
-        <v>7969.9501706749</v>
+        <v>7969.9501710731</v>
       </c>
       <c r="O481" t="n">
-        <v>47819.7010240494</v>
+        <v>47819.7010264386</v>
       </c>
       <c r="P481" t="n">
         <v>12900</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -21754,19 +21754,19 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="N487" t="n">
         <v>1200</v>
       </c>
       <c r="O487" t="n">
-        <v>314400</v>
+        <v>310800</v>
       </c>
       <c r="P487" t="n">
         <v>1500</v>
       </c>
       <c r="Q487" t="n">
-        <v>393000</v>
+        <v>388500</v>
       </c>
     </row>
     <row r="488">
@@ -22499,10 +22499,10 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K504" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L504" t="n">
         <v>0</v>
@@ -22548,7 +22548,7 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -22557,19 +22557,19 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N505" t="n">
         <v>6232.24</v>
       </c>
       <c r="O505" t="n">
-        <v>93483.59999999999</v>
+        <v>87251.36</v>
       </c>
       <c r="P505" t="n">
         <v>7900</v>
       </c>
       <c r="Q505" t="n">
-        <v>118500</v>
+        <v>110600</v>
       </c>
     </row>
     <row r="506">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
@@ -22603,19 +22603,19 @@
         <v>0</v>
       </c>
       <c r="M506" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N506" t="n">
         <v>5875.95</v>
       </c>
       <c r="O506" t="n">
-        <v>94015.2</v>
+        <v>88139.25</v>
       </c>
       <c r="P506" t="n">
         <v>5900</v>
       </c>
       <c r="Q506" t="n">
-        <v>94400</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="507">
@@ -22684,7 +22684,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -22693,19 +22693,19 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N508" t="n">
         <v>5470.94</v>
       </c>
       <c r="O508" t="n">
-        <v>60180.34</v>
+        <v>65651.28</v>
       </c>
       <c r="P508" t="n">
         <v>6900</v>
       </c>
       <c r="Q508" t="n">
-        <v>75900</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="509">
@@ -22994,7 +22994,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23003,19 +23003,19 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N515" t="n">
         <v>8562.18</v>
       </c>
       <c r="O515" t="n">
-        <v>94183.98000000001</v>
+        <v>68497.44</v>
       </c>
       <c r="P515" t="n">
         <v>9900</v>
       </c>
       <c r="Q515" t="n">
-        <v>108900</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="516">
@@ -23076,7 +23076,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -23085,19 +23085,19 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N517" t="n">
         <v>6000</v>
       </c>
       <c r="O517" t="n">
-        <v>180000</v>
+        <v>240000</v>
       </c>
       <c r="P517" t="n">
         <v>7500</v>
       </c>
       <c r="Q517" t="n">
-        <v>225000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="518">
@@ -24325,28 +24325,28 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N544" t="n">
-        <v>1664.3365797101</v>
+        <v>1664.33396875</v>
       </c>
       <c r="O544" t="n">
-        <v>26629.3852753616</v>
+        <v>24965.00953125</v>
       </c>
       <c r="P544" t="n">
         <v>2900</v>
       </c>
       <c r="Q544" t="n">
-        <v>46400</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="545">
@@ -24420,13 +24420,13 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
       </c>
       <c r="L546" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M546" t="n">
         <v>5</v>
@@ -24947,10 +24947,10 @@
         <v>12</v>
       </c>
       <c r="N557" t="n">
-        <v>23521.623</v>
+        <v>23521.622708333</v>
       </c>
       <c r="O557" t="n">
-        <v>282259.476</v>
+        <v>282259.472499996</v>
       </c>
       <c r="P557" t="n">
         <v>39000</v>
@@ -25073,22 +25073,22 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="K560" t="n">
         <v>0</v>
       </c>
       <c r="L560" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M560" t="n">
         <v>28</v>
       </c>
       <c r="N560" t="n">
-        <v>1778.4728487518</v>
+        <v>1778.4728562081</v>
       </c>
       <c r="O560" t="n">
-        <v>49797.2397650504</v>
+        <v>49797.2399738268</v>
       </c>
       <c r="P560" t="n">
         <v>4900</v>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="J565" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K565" t="n">
         <v>0</v>
@@ -25312,19 +25312,19 @@
         <v>0</v>
       </c>
       <c r="M565" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N565" t="n">
         <v>22739</v>
       </c>
       <c r="O565" t="n">
-        <v>159173</v>
+        <v>204651</v>
       </c>
       <c r="P565" t="n">
         <v>36900</v>
       </c>
       <c r="Q565" t="n">
-        <v>258300</v>
+        <v>332100</v>
       </c>
     </row>
     <row r="566">
@@ -25349,7 +25349,7 @@
         </is>
       </c>
       <c r="J566" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K566" t="n">
         <v>0</v>
@@ -25358,19 +25358,19 @@
         <v>0</v>
       </c>
       <c r="M566" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N566" t="n">
         <v>18016</v>
       </c>
       <c r="O566" t="n">
-        <v>126112</v>
+        <v>198176</v>
       </c>
       <c r="P566" t="n">
         <v>29900</v>
       </c>
       <c r="Q566" t="n">
-        <v>209300</v>
+        <v>328900</v>
       </c>
     </row>
     <row r="567">
@@ -25395,7 +25395,7 @@
         </is>
       </c>
       <c r="J567" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K567" t="n">
         <v>0</v>
@@ -25404,19 +25404,19 @@
         <v>0</v>
       </c>
       <c r="M567" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N567" t="n">
         <v>16058</v>
       </c>
       <c r="O567" t="n">
-        <v>208754</v>
+        <v>305102</v>
       </c>
       <c r="P567" t="n">
         <v>25900</v>
       </c>
       <c r="Q567" t="n">
-        <v>336700</v>
+        <v>492100</v>
       </c>
     </row>
     <row r="568">
@@ -25441,7 +25441,7 @@
         </is>
       </c>
       <c r="J568" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K568" t="n">
         <v>0</v>
@@ -25450,19 +25450,19 @@
         <v>0</v>
       </c>
       <c r="M568" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N568" t="n">
         <v>25534</v>
       </c>
       <c r="O568" t="n">
-        <v>204272</v>
+        <v>459612</v>
       </c>
       <c r="P568" t="n">
         <v>40900</v>
       </c>
       <c r="Q568" t="n">
-        <v>327200</v>
+        <v>736200</v>
       </c>
     </row>
     <row r="569">
@@ -25625,7 +25625,7 @@
         </is>
       </c>
       <c r="J572" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K572" t="n">
         <v>0</v>
@@ -25634,19 +25634,19 @@
         <v>0</v>
       </c>
       <c r="M572" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N572" t="n">
         <v>6300</v>
       </c>
       <c r="O572" t="n">
-        <v>44100</v>
+        <v>37800</v>
       </c>
       <c r="P572" t="n">
         <v>10200</v>
       </c>
       <c r="Q572" t="n">
-        <v>71400</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="573">
@@ -25993,7 +25993,7 @@
         </is>
       </c>
       <c r="J580" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K580" t="n">
         <v>0</v>
@@ -26002,19 +26002,19 @@
         <v>0</v>
       </c>
       <c r="M580" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N580" t="n">
         <v>1230</v>
       </c>
       <c r="O580" t="n">
-        <v>36900</v>
+        <v>35670</v>
       </c>
       <c r="P580" t="n">
         <v>2000</v>
       </c>
       <c r="Q580" t="n">
-        <v>60000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="581">
@@ -26649,7 +26649,7 @@
         </is>
       </c>
       <c r="J594" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K594" t="n">
         <v>0</v>
@@ -26658,19 +26658,19 @@
         <v>0</v>
       </c>
       <c r="M594" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N594" t="n">
         <v>4917</v>
       </c>
       <c r="O594" t="n">
-        <v>73755</v>
+        <v>63921</v>
       </c>
       <c r="P594" t="n">
         <v>8600</v>
       </c>
       <c r="Q594" t="n">
-        <v>129000</v>
+        <v>111800</v>
       </c>
     </row>
     <row r="595">
@@ -27066,13 +27066,13 @@
         </is>
       </c>
       <c r="J603" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K603" t="n">
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M603" t="n">
         <v>44</v>
@@ -27250,28 +27250,28 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K607" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L607" t="n">
         <v>0</v>
       </c>
       <c r="M607" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N607" t="n">
         <v>3424</v>
       </c>
       <c r="O607" t="n">
-        <v>154080</v>
+        <v>150656</v>
       </c>
       <c r="P607" t="n">
         <v>5900</v>
       </c>
       <c r="Q607" t="n">
-        <v>265500</v>
+        <v>259600</v>
       </c>
     </row>
     <row r="608">
@@ -27389,13 +27389,13 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M610" t="n">
         <v>4</v>
@@ -27481,7 +27481,7 @@
         </is>
       </c>
       <c r="J612" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K612" t="n">
         <v>0</v>
@@ -27490,19 +27490,19 @@
         <v>0</v>
       </c>
       <c r="M612" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N612" t="n">
         <v>8858.16</v>
       </c>
       <c r="O612" t="n">
-        <v>203737.68</v>
+        <v>186021.36</v>
       </c>
       <c r="P612" t="n">
         <v>15500</v>
       </c>
       <c r="Q612" t="n">
-        <v>356500</v>
+        <v>325500</v>
       </c>
     </row>
     <row r="613">
@@ -27803,13 +27803,13 @@
         </is>
       </c>
       <c r="J619" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
       </c>
       <c r="L619" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M619" t="n">
         <v>155</v>
@@ -28281,10 +28281,10 @@
         <v>109</v>
       </c>
       <c r="N629" t="n">
-        <v>2328.118659892</v>
+        <v>2328.1186586141</v>
       </c>
       <c r="O629" t="n">
-        <v>253764.933928228</v>
+        <v>253764.9337889369</v>
       </c>
       <c r="P629" t="n">
         <v>4500</v>
@@ -28361,7 +28361,7 @@
         </is>
       </c>
       <c r="J631" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
@@ -28370,19 +28370,19 @@
         <v>0</v>
       </c>
       <c r="M631" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N631" t="n">
         <v>9384</v>
       </c>
       <c r="O631" t="n">
-        <v>93840</v>
+        <v>150144</v>
       </c>
       <c r="P631" t="n">
         <v>15900</v>
       </c>
       <c r="Q631" t="n">
-        <v>159000</v>
+        <v>254400</v>
       </c>
     </row>
     <row r="632">
@@ -28683,7 +28683,7 @@
         </is>
       </c>
       <c r="J638" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K638" t="n">
         <v>0</v>
@@ -28692,19 +28692,19 @@
         <v>0</v>
       </c>
       <c r="M638" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N638" t="n">
         <v>4544</v>
       </c>
       <c r="O638" t="n">
-        <v>272640</v>
+        <v>268096</v>
       </c>
       <c r="P638" t="n">
         <v>7900</v>
       </c>
       <c r="Q638" t="n">
-        <v>474000</v>
+        <v>466100</v>
       </c>
     </row>
     <row r="639">
@@ -28959,10 +28959,10 @@
         </is>
       </c>
       <c r="J644" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K644" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L644" t="n">
         <v>0</v>
@@ -29017,10 +29017,10 @@
         <v>81</v>
       </c>
       <c r="N645" t="n">
-        <v>6426.9445005045</v>
+        <v>6414</v>
       </c>
       <c r="O645" t="n">
-        <v>520582.5045408645</v>
+        <v>519534</v>
       </c>
       <c r="P645" t="n">
         <v>10900</v>
@@ -29235,28 +29235,28 @@
         </is>
       </c>
       <c r="J650" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K650" t="n">
         <v>0</v>
       </c>
       <c r="L650" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M650" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="N650" t="n">
-        <v>3903.7394652406</v>
+        <v>3903.7395348837</v>
       </c>
       <c r="O650" t="n">
-        <v>468448.735828872</v>
+        <v>456737.5255813929</v>
       </c>
       <c r="P650" t="n">
         <v>7500</v>
       </c>
       <c r="Q650" t="n">
-        <v>900000</v>
+        <v>877500</v>
       </c>
     </row>
     <row r="651">
@@ -29276,13 +29276,13 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M651" t="n">
         <v>9</v>
@@ -29690,7 +29690,7 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
@@ -29699,19 +29699,19 @@
         <v>0</v>
       </c>
       <c r="M660" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N660" t="n">
-        <v>5869.172402529</v>
+        <v>5869.1723864836</v>
       </c>
       <c r="O660" t="n">
-        <v>504748.8266174939</v>
+        <v>498879.652851106</v>
       </c>
       <c r="P660" t="n">
         <v>9500</v>
       </c>
       <c r="Q660" t="n">
-        <v>817000</v>
+        <v>807500</v>
       </c>
     </row>
     <row r="661">
@@ -29736,10 +29736,10 @@
         </is>
       </c>
       <c r="J661" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K661" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L661" t="n">
         <v>0</v>
@@ -29782,7 +29782,7 @@
         </is>
       </c>
       <c r="J662" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K662" t="n">
         <v>0</v>
@@ -29791,19 +29791,19 @@
         <v>12</v>
       </c>
       <c r="M662" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N662" t="n">
         <v>4984</v>
       </c>
       <c r="O662" t="n">
-        <v>458528</v>
+        <v>453544</v>
       </c>
       <c r="P662" t="n">
         <v>7900</v>
       </c>
       <c r="Q662" t="n">
-        <v>726800</v>
+        <v>718900</v>
       </c>
     </row>
     <row r="663">
@@ -29920,10 +29920,10 @@
         </is>
       </c>
       <c r="J665" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K665" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L665" t="n">
         <v>0</v>
@@ -29932,10 +29932,10 @@
         <v>40</v>
       </c>
       <c r="N665" t="n">
-        <v>6648.7102177554</v>
+        <v>6645</v>
       </c>
       <c r="O665" t="n">
-        <v>265948.408710216</v>
+        <v>265800</v>
       </c>
       <c r="P665" t="n">
         <v>10900</v>
@@ -30070,10 +30070,10 @@
         <v>48</v>
       </c>
       <c r="N668" t="n">
-        <v>3904.464344942</v>
+        <v>3898</v>
       </c>
       <c r="O668" t="n">
-        <v>187414.288557216</v>
+        <v>187104</v>
       </c>
       <c r="P668" t="n">
         <v>6900</v>
@@ -30334,28 +30334,28 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N674" t="n">
         <v>8806</v>
       </c>
       <c r="O674" t="n">
-        <v>140896</v>
+        <v>193732</v>
       </c>
       <c r="P674" t="n">
         <v>14900</v>
       </c>
       <c r="Q674" t="n">
-        <v>238400</v>
+        <v>327800</v>
       </c>
     </row>
     <row r="675">
@@ -30889,7 +30889,7 @@
         </is>
       </c>
       <c r="J686" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K686" t="n">
         <v>0</v>
@@ -30898,19 +30898,19 @@
         <v>0</v>
       </c>
       <c r="M686" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N686" t="n">
         <v>59834</v>
       </c>
       <c r="O686" t="n">
-        <v>7718586</v>
+        <v>7658752</v>
       </c>
       <c r="P686" t="n">
         <v>7900</v>
       </c>
       <c r="Q686" t="n">
-        <v>1019100</v>
+        <v>1011200</v>
       </c>
     </row>
     <row r="687">
@@ -31122,7 +31122,7 @@
         </is>
       </c>
       <c r="J691" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K691" t="n">
         <v>0</v>
@@ -31131,19 +31131,19 @@
         <v>0</v>
       </c>
       <c r="M691" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N691" t="n">
         <v>10755</v>
       </c>
       <c r="O691" t="n">
-        <v>290385</v>
+        <v>344160</v>
       </c>
       <c r="P691" t="n">
         <v>17900</v>
       </c>
       <c r="Q691" t="n">
-        <v>483300</v>
+        <v>572800</v>
       </c>
     </row>
     <row r="692">
@@ -31536,7 +31536,7 @@
         </is>
       </c>
       <c r="J700" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K700" t="n">
         <v>0</v>
@@ -31545,19 +31545,19 @@
         <v>0</v>
       </c>
       <c r="M700" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N700" t="n">
         <v>4303</v>
       </c>
       <c r="O700" t="n">
-        <v>228059</v>
+        <v>223756</v>
       </c>
       <c r="P700" t="n">
         <v>7900</v>
       </c>
       <c r="Q700" t="n">
-        <v>418700</v>
+        <v>410800</v>
       </c>
     </row>
     <row r="701">
@@ -31674,13 +31674,13 @@
         </is>
       </c>
       <c r="J703" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K703" t="n">
         <v>0</v>
       </c>
       <c r="L703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M703" t="n">
         <v>32</v>
@@ -31950,7 +31950,7 @@
         </is>
       </c>
       <c r="J709" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K709" t="n">
         <v>0</v>
@@ -31959,19 +31959,19 @@
         <v>0</v>
       </c>
       <c r="M709" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N709" t="n">
         <v>12489</v>
       </c>
       <c r="O709" t="n">
-        <v>187335</v>
+        <v>174846</v>
       </c>
       <c r="P709" t="n">
         <v>20900</v>
       </c>
       <c r="Q709" t="n">
-        <v>313500</v>
+        <v>292600</v>
       </c>
     </row>
     <row r="710">
@@ -32042,28 +32042,28 @@
         </is>
       </c>
       <c r="J711" t="n">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="K711" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L711" t="n">
         <v>0</v>
       </c>
       <c r="M711" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N711" t="n">
         <v>3821</v>
       </c>
       <c r="O711" t="n">
-        <v>450878</v>
+        <v>443236</v>
       </c>
       <c r="P711" t="n">
         <v>5900</v>
       </c>
       <c r="Q711" t="n">
-        <v>696200</v>
+        <v>684400</v>
       </c>
     </row>
     <row r="712">
@@ -32088,7 +32088,7 @@
         </is>
       </c>
       <c r="J712" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K712" t="n">
         <v>0</v>
@@ -32097,19 +32097,19 @@
         <v>0</v>
       </c>
       <c r="M712" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N712" t="n">
         <v>15472</v>
       </c>
       <c r="O712" t="n">
-        <v>123776</v>
+        <v>247552</v>
       </c>
       <c r="P712" t="n">
         <v>25900</v>
       </c>
       <c r="Q712" t="n">
-        <v>207200</v>
+        <v>414400</v>
       </c>
     </row>
     <row r="713">
@@ -32180,10 +32180,10 @@
         </is>
       </c>
       <c r="J714" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K714" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L714" t="n">
         <v>0</v>
@@ -32226,7 +32226,7 @@
         </is>
       </c>
       <c r="J715" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K715" t="n">
         <v>0</v>
@@ -32235,19 +32235,19 @@
         <v>0</v>
       </c>
       <c r="M715" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N715" t="n">
         <v>15223.06</v>
       </c>
       <c r="O715" t="n">
-        <v>45669.18</v>
+        <v>30446.12</v>
       </c>
       <c r="P715" t="n">
         <v>17500</v>
       </c>
       <c r="Q715" t="n">
-        <v>52500</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="716">
@@ -32364,7 +32364,7 @@
         </is>
       </c>
       <c r="J718" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K718" t="n">
         <v>0</v>
@@ -32373,19 +32373,19 @@
         <v>0</v>
       </c>
       <c r="M718" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N718" t="n">
-        <v>1516.0387386003</v>
+        <v>1516.0387367881</v>
       </c>
       <c r="O718" t="n">
-        <v>198601.0747566393</v>
+        <v>189504.8420985125</v>
       </c>
       <c r="P718" t="n">
         <v>2300</v>
       </c>
       <c r="Q718" t="n">
-        <v>301300</v>
+        <v>287500</v>
       </c>
     </row>
     <row r="719">
@@ -32500,7 +32500,7 @@
         </is>
       </c>
       <c r="J721" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K721" t="n">
         <v>0</v>
@@ -32509,19 +32509,19 @@
         <v>4</v>
       </c>
       <c r="M721" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N721" t="n">
-        <v>2458.5124201742</v>
+        <v>2458.5124119143</v>
       </c>
       <c r="O721" t="n">
-        <v>747387.7757329568</v>
+        <v>744929.260810033</v>
       </c>
       <c r="P721" t="n">
         <v>3500</v>
       </c>
       <c r="Q721" t="n">
-        <v>1064000</v>
+        <v>1060500</v>
       </c>
     </row>
     <row r="722">
@@ -32638,7 +32638,7 @@
         </is>
       </c>
       <c r="J724" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="K724" t="n">
         <v>0</v>
@@ -32647,19 +32647,19 @@
         <v>0</v>
       </c>
       <c r="M724" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="N724" t="n">
-        <v>2079.3832881866</v>
+        <v>2079.3832679245</v>
       </c>
       <c r="O724" t="n">
-        <v>623814.98645598</v>
+        <v>615497.4473056521</v>
       </c>
       <c r="P724" t="n">
         <v>2900</v>
       </c>
       <c r="Q724" t="n">
-        <v>870000</v>
+        <v>858400</v>
       </c>
     </row>
     <row r="725">
@@ -32684,7 +32684,7 @@
         </is>
       </c>
       <c r="J725" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K725" t="n">
         <v>0</v>
@@ -32693,19 +32693,19 @@
         <v>3</v>
       </c>
       <c r="M725" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N725" t="n">
-        <v>1803.0169868096</v>
+        <v>1803.0170831592</v>
       </c>
       <c r="O725" t="n">
-        <v>257831.4291137728</v>
+        <v>252422.391642288</v>
       </c>
       <c r="P725" t="n">
         <v>2500</v>
       </c>
       <c r="Q725" t="n">
-        <v>357500</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="726">
@@ -32742,10 +32742,10 @@
         <v>167</v>
       </c>
       <c r="N726" t="n">
-        <v>3306.5944099379</v>
+        <v>3306.5944012442</v>
       </c>
       <c r="O726" t="n">
-        <v>552201.2664596293</v>
+        <v>552201.2650077814</v>
       </c>
       <c r="P726" t="n">
         <v>4900</v>
@@ -32776,7 +32776,7 @@
         </is>
       </c>
       <c r="J727" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K727" t="n">
         <v>0</v>
@@ -32785,19 +32785,19 @@
         <v>0</v>
       </c>
       <c r="M727" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N727" t="n">
-        <v>2122.1634778259</v>
+        <v>2122.1634756504</v>
       </c>
       <c r="O727" t="n">
-        <v>422310.5320873541</v>
+        <v>420188.3681787792</v>
       </c>
       <c r="P727" t="n">
         <v>2900</v>
       </c>
       <c r="Q727" t="n">
-        <v>577100</v>
+        <v>574200</v>
       </c>
     </row>
     <row r="728">
@@ -32822,7 +32822,7 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
@@ -32831,19 +32831,19 @@
         <v>0</v>
       </c>
       <c r="M728" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="N728" t="n">
-        <v>2108.7971008815</v>
+        <v>2108.7972359329</v>
       </c>
       <c r="O728" t="n">
-        <v>318428.3622331065</v>
+        <v>305775.5992102705</v>
       </c>
       <c r="P728" t="n">
         <v>2900</v>
       </c>
       <c r="Q728" t="n">
-        <v>437900</v>
+        <v>420500</v>
       </c>
     </row>
     <row r="729">
@@ -32868,7 +32868,7 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
@@ -32877,19 +32877,19 @@
         <v>0</v>
       </c>
       <c r="M729" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N729" t="n">
-        <v>2056.0820030996</v>
+        <v>2056.0819782355</v>
       </c>
       <c r="O729" t="n">
-        <v>526356.9927934976</v>
+        <v>524300.9044500525</v>
       </c>
       <c r="P729" t="n">
         <v>2900</v>
       </c>
       <c r="Q729" t="n">
-        <v>742400</v>
+        <v>739500</v>
       </c>
     </row>
     <row r="730">
@@ -32926,10 +32926,10 @@
         <v>281</v>
       </c>
       <c r="N730" t="n">
-        <v>3224.5698459846</v>
+        <v>3224.5698785872</v>
       </c>
       <c r="O730" t="n">
-        <v>906104.1267216726</v>
+        <v>906104.1358830032</v>
       </c>
       <c r="P730" t="n">
         <v>4500</v>
@@ -32972,10 +32972,10 @@
         <v>255</v>
       </c>
       <c r="N731" t="n">
-        <v>1655.9292037471</v>
+        <v>1655.9291699295</v>
       </c>
       <c r="O731" t="n">
-        <v>422261.9469555105</v>
+        <v>422261.9383320225</v>
       </c>
       <c r="P731" t="n">
         <v>2500</v>
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
@@ -33156,19 +33156,19 @@
         <v>0</v>
       </c>
       <c r="M735" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N735" t="n">
         <v>2003</v>
       </c>
       <c r="O735" t="n">
-        <v>222333</v>
+        <v>220330</v>
       </c>
       <c r="P735" t="n">
         <v>3900</v>
       </c>
       <c r="Q735" t="n">
-        <v>432900</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="736">
@@ -33193,10 +33193,10 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K736" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L736" t="n">
         <v>0</v>
@@ -33239,7 +33239,7 @@
         </is>
       </c>
       <c r="J737" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K737" t="n">
         <v>0</v>
@@ -33248,19 +33248,19 @@
         <v>0</v>
       </c>
       <c r="M737" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N737" t="n">
-        <v>1592.2847324415</v>
+        <v>1592.2857321429</v>
       </c>
       <c r="O737" t="n">
-        <v>103498.5076086975</v>
+        <v>97129.42966071691</v>
       </c>
       <c r="P737" t="n">
         <v>2500</v>
       </c>
       <c r="Q737" t="n">
-        <v>162500</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="738">
@@ -33428,10 +33428,10 @@
         <v>19</v>
       </c>
       <c r="N741" t="n">
-        <v>1906.17</v>
+        <v>1906.1654098361</v>
       </c>
       <c r="O741" t="n">
-        <v>36217.23</v>
+        <v>36217.1427868859</v>
       </c>
       <c r="P741" t="n">
         <v>2900</v>
@@ -33508,7 +33508,7 @@
         </is>
       </c>
       <c r="J743" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K743" t="n">
         <v>0</v>
@@ -33517,19 +33517,19 @@
         <v>0</v>
       </c>
       <c r="M743" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N743" t="n">
-        <v>2060.1584104628</v>
+        <v>2060.158340081</v>
       </c>
       <c r="O743" t="n">
-        <v>265760.4349497012</v>
+        <v>259579.950850206</v>
       </c>
       <c r="P743" t="n">
         <v>2900</v>
       </c>
       <c r="Q743" t="n">
-        <v>374100</v>
+        <v>365400</v>
       </c>
     </row>
     <row r="744">
@@ -33612,10 +33612,10 @@
         <v>133</v>
       </c>
       <c r="N745" t="n">
-        <v>2546.979929078</v>
+        <v>2546.9798571429</v>
       </c>
       <c r="O745" t="n">
-        <v>338748.330567374</v>
+        <v>338748.3210000057</v>
       </c>
       <c r="P745" t="n">
         <v>3900</v>
@@ -33646,7 +33646,7 @@
         </is>
       </c>
       <c r="J746" t="n">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="K746" t="n">
         <v>0</v>
@@ -33655,19 +33655,19 @@
         <v>0</v>
       </c>
       <c r="M746" t="n">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="N746" t="n">
-        <v>1262.9750514202</v>
+        <v>1259.2749729064</v>
       </c>
       <c r="O746" t="n">
-        <v>694636.2782811101</v>
+        <v>678749.2103965497</v>
       </c>
       <c r="P746" t="n">
         <v>1900</v>
       </c>
       <c r="Q746" t="n">
-        <v>1045000</v>
+        <v>1024100</v>
       </c>
     </row>
     <row r="747">
@@ -33881,10 +33881,10 @@
         <v>283</v>
       </c>
       <c r="N751" t="n">
-        <v>692.15241910093</v>
+        <v>692.15242929914</v>
       </c>
       <c r="O751" t="n">
-        <v>195879.1346055632</v>
+        <v>195879.1374916566</v>
       </c>
       <c r="P751" t="n">
         <v>1200</v>
@@ -34296,28 +34296,28 @@
         </is>
       </c>
       <c r="J760" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K760" t="n">
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M760" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N760" t="n">
         <v>5215</v>
       </c>
       <c r="O760" t="n">
-        <v>130375</v>
+        <v>109515</v>
       </c>
       <c r="P760" t="n">
         <v>8900</v>
       </c>
       <c r="Q760" t="n">
-        <v>222500</v>
+        <v>186900</v>
       </c>
     </row>
     <row r="761">
@@ -35198,10 +35198,10 @@
         <v>28</v>
       </c>
       <c r="N779" t="n">
-        <v>1538.0108069164</v>
+        <v>1530.4499180664</v>
       </c>
       <c r="O779" t="n">
-        <v>43064.3025936592</v>
+        <v>42852.5977058592</v>
       </c>
       <c r="P779" t="n">
         <v>2600</v>
@@ -35511,7 +35511,7 @@
         </is>
       </c>
       <c r="J786" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K786" t="n">
         <v>0</v>
@@ -35520,19 +35520,19 @@
         <v>0</v>
       </c>
       <c r="M786" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N786" t="n">
         <v>3629.36</v>
       </c>
       <c r="O786" t="n">
-        <v>68957.84</v>
+        <v>61699.12</v>
       </c>
       <c r="P786" t="n">
         <v>3900</v>
       </c>
       <c r="Q786" t="n">
-        <v>74100</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="787">
@@ -36111,7 +36111,7 @@
         </is>
       </c>
       <c r="J799" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K799" t="n">
         <v>0</v>
@@ -36120,19 +36120,19 @@
         <v>0</v>
       </c>
       <c r="M799" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="N799" t="n">
         <v>2357.74</v>
       </c>
       <c r="O799" t="n">
-        <v>51870.28</v>
+        <v>30650.62</v>
       </c>
       <c r="P799" t="n">
         <v>3000</v>
       </c>
       <c r="Q799" t="n">
-        <v>66000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="800">
@@ -36351,10 +36351,10 @@
         <v>33</v>
       </c>
       <c r="N804" t="n">
-        <v>1690.8700094029</v>
+        <v>1690.8700094251</v>
       </c>
       <c r="O804" t="n">
-        <v>55798.7103102957</v>
+        <v>55798.71031102831</v>
       </c>
       <c r="P804" t="n">
         <v>3000</v>
@@ -36723,7 +36723,7 @@
         </is>
       </c>
       <c r="J812" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K812" t="n">
         <v>0</v>
@@ -36732,19 +36732,19 @@
         <v>0</v>
       </c>
       <c r="M812" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="N812" t="n">
         <v>1621.2</v>
       </c>
       <c r="O812" t="n">
-        <v>97272</v>
+        <v>79438.8</v>
       </c>
       <c r="P812" t="n">
         <v>2500</v>
       </c>
       <c r="Q812" t="n">
-        <v>150000</v>
+        <v>122500</v>
       </c>
     </row>
     <row r="813">
@@ -37382,10 +37382,10 @@
         <v>28</v>
       </c>
       <c r="N826" t="n">
-        <v>1283.6525514403</v>
+        <v>1283.6523305085</v>
       </c>
       <c r="O826" t="n">
-        <v>35942.2714403284</v>
+        <v>35942.265254238</v>
       </c>
       <c r="P826" t="n">
         <v>1900</v>
@@ -37958,28 +37958,28 @@
         </is>
       </c>
       <c r="J839" t="n">
-        <v>952</v>
+        <v>929</v>
       </c>
       <c r="K839" t="n">
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M839" t="n">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="N839" t="n">
-        <v>517.29511103247</v>
+        <v>517.29522417328</v>
       </c>
       <c r="O839" t="n">
-        <v>486257.4043705218</v>
+        <v>480567.2632569771</v>
       </c>
       <c r="P839" t="n">
         <v>900</v>
       </c>
       <c r="Q839" t="n">
-        <v>846000</v>
+        <v>836100</v>
       </c>
     </row>
     <row r="840">
@@ -38145,7 +38145,7 @@
         </is>
       </c>
       <c r="J843" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K843" t="n">
         <v>0</v>
@@ -38154,19 +38154,19 @@
         <v>0</v>
       </c>
       <c r="M843" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N843" t="n">
         <v>4400</v>
       </c>
       <c r="O843" t="n">
-        <v>26400</v>
+        <v>22000</v>
       </c>
       <c r="P843" t="n">
         <v>5500</v>
       </c>
       <c r="Q843" t="n">
-        <v>33000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="844">
@@ -38473,22 +38473,22 @@
         </is>
       </c>
       <c r="J850" t="n">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="K850" t="n">
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M850" t="n">
         <v>248</v>
       </c>
       <c r="N850" t="n">
-        <v>3110.8366754617</v>
+        <v>3110.8366199849</v>
       </c>
       <c r="O850" t="n">
-        <v>771487.4955145016</v>
+        <v>771487.4817562553</v>
       </c>
       <c r="P850" t="n">
         <v>4500</v>
@@ -38702,7 +38702,7 @@
         </is>
       </c>
       <c r="J855" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K855" t="n">
         <v>0</v>
@@ -38711,19 +38711,19 @@
         <v>0</v>
       </c>
       <c r="M855" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N855" t="n">
         <v>7120</v>
       </c>
       <c r="O855" t="n">
-        <v>142400</v>
+        <v>128160</v>
       </c>
       <c r="P855" t="n">
         <v>8900</v>
       </c>
       <c r="Q855" t="n">
-        <v>178000</v>
+        <v>160200</v>
       </c>
     </row>
     <row r="856">
@@ -38885,7 +38885,7 @@
         </is>
       </c>
       <c r="J859" t="n">
-        <v>1379</v>
+        <v>1352</v>
       </c>
       <c r="K859" t="n">
         <v>0</v>
@@ -38894,19 +38894,19 @@
         <v>0</v>
       </c>
       <c r="M859" t="n">
-        <v>1379</v>
+        <v>1352</v>
       </c>
       <c r="N859" t="n">
-        <v>703.79473431536</v>
+        <v>703.79472483574</v>
       </c>
       <c r="O859" t="n">
-        <v>970532.9386208814</v>
+        <v>951530.4679779204</v>
       </c>
       <c r="P859" t="n">
         <v>900</v>
       </c>
       <c r="Q859" t="n">
-        <v>1241100</v>
+        <v>1216800</v>
       </c>
     </row>
     <row r="860">
@@ -39259,7 +39259,7 @@
         </is>
       </c>
       <c r="J867" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K867" t="n">
         <v>0</v>
@@ -39268,19 +39268,19 @@
         <v>0</v>
       </c>
       <c r="M867" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N867" t="n">
         <v>2501.3844041451</v>
       </c>
       <c r="O867" t="n">
-        <v>27515.2284455961</v>
+        <v>42523.5348704667</v>
       </c>
       <c r="P867" t="n">
         <v>4100</v>
       </c>
       <c r="Q867" t="n">
-        <v>45100</v>
+        <v>69700</v>
       </c>
     </row>
     <row r="868">
@@ -39400,7 +39400,7 @@
         </is>
       </c>
       <c r="J870" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K870" t="n">
         <v>0</v>
@@ -39409,19 +39409,19 @@
         <v>0</v>
       </c>
       <c r="M870" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N870" t="n">
-        <v>3006.0209677419</v>
+        <v>3006.0209782609</v>
       </c>
       <c r="O870" t="n">
-        <v>339680.3693548347</v>
+        <v>333668.3285869599</v>
       </c>
       <c r="P870" t="n">
         <v>3900</v>
       </c>
       <c r="Q870" t="n">
-        <v>440700</v>
+        <v>432900</v>
       </c>
     </row>
     <row r="871">
@@ -39628,7 +39628,7 @@
         </is>
       </c>
       <c r="J875" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K875" t="n">
         <v>0</v>
@@ -39637,19 +39637,19 @@
         <v>0</v>
       </c>
       <c r="M875" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N875" t="n">
         <v>2400</v>
       </c>
       <c r="O875" t="n">
-        <v>24000</v>
+        <v>21600</v>
       </c>
       <c r="P875" t="n">
         <v>3000</v>
       </c>
       <c r="Q875" t="n">
-        <v>30000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="876">
@@ -39811,7 +39811,7 @@
         </is>
       </c>
       <c r="J879" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="K879" t="n">
         <v>0</v>
@@ -39820,19 +39820,19 @@
         <v>0</v>
       </c>
       <c r="M879" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="N879" t="n">
         <v>2525.02</v>
       </c>
       <c r="O879" t="n">
-        <v>196951.56</v>
+        <v>156551.24</v>
       </c>
       <c r="P879" t="n">
         <v>3000</v>
       </c>
       <c r="Q879" t="n">
-        <v>234000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="880">
@@ -39899,7 +39899,7 @@
         </is>
       </c>
       <c r="J881" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K881" t="n">
         <v>0</v>
@@ -39908,19 +39908,19 @@
         <v>0</v>
       </c>
       <c r="M881" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N881" t="n">
         <v>1755.74</v>
       </c>
       <c r="O881" t="n">
-        <v>61450.9</v>
+        <v>57939.42</v>
       </c>
       <c r="P881" t="n">
         <v>1500</v>
       </c>
       <c r="Q881" t="n">
-        <v>52500</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="882">
@@ -39960,10 +39960,10 @@
         <v>33</v>
       </c>
       <c r="N882" t="n">
-        <v>1595.4991666667</v>
+        <v>1595.4982940252</v>
       </c>
       <c r="O882" t="n">
-        <v>52651.47250000109</v>
+        <v>52651.4437028316</v>
       </c>
       <c r="P882" t="n">
         <v>2500</v>
@@ -42504,10 +42504,10 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K935" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L935" t="n">
         <v>0</v>
@@ -42553,7 +42553,7 @@
         </is>
       </c>
       <c r="J936" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K936" t="n">
         <v>0</v>
@@ -42562,19 +42562,19 @@
         <v>0</v>
       </c>
       <c r="M936" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N936" t="n">
         <v>5430.86</v>
       </c>
       <c r="O936" t="n">
-        <v>179218.38</v>
+        <v>173787.52</v>
       </c>
       <c r="P936" t="n">
         <v>13900</v>
       </c>
       <c r="Q936" t="n">
-        <v>458700</v>
+        <v>444800</v>
       </c>
     </row>
     <row r="937">
@@ -42746,7 +42746,7 @@
         </is>
       </c>
       <c r="J940" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K940" t="n">
         <v>0</v>
@@ -42755,19 +42755,19 @@
         <v>0</v>
       </c>
       <c r="M940" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N940" t="n">
         <v>4568.55</v>
       </c>
       <c r="O940" t="n">
-        <v>123350.85</v>
+        <v>141625.05</v>
       </c>
       <c r="P940" t="n">
         <v>6900</v>
       </c>
       <c r="Q940" t="n">
-        <v>186300</v>
+        <v>213900</v>
       </c>
     </row>
     <row r="941">
@@ -43085,10 +43085,10 @@
         <v>16</v>
       </c>
       <c r="N947" t="n">
-        <v>3067.0906143345</v>
+        <v>3067.0906164384</v>
       </c>
       <c r="O947" t="n">
-        <v>49073.449829352</v>
+        <v>49073.4498630144</v>
       </c>
       <c r="P947" t="n">
         <v>7200</v>
@@ -43315,10 +43315,10 @@
         </is>
       </c>
       <c r="J952" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K952" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L952" t="n">
         <v>0</v>
@@ -43364,10 +43364,10 @@
         </is>
       </c>
       <c r="J953" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K953" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L953" t="n">
         <v>0</v>
@@ -43413,10 +43413,10 @@
         </is>
       </c>
       <c r="J954" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K954" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L954" t="n">
         <v>0</v>
@@ -43462,10 +43462,10 @@
         </is>
       </c>
       <c r="J955" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K955" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L955" t="n">
         <v>0</v>
@@ -44140,7 +44140,7 @@
         </is>
       </c>
       <c r="J969" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K969" t="n">
         <v>0</v>
@@ -44149,19 +44149,19 @@
         <v>0</v>
       </c>
       <c r="M969" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N969" t="n">
-        <v>4697.3814814815</v>
+        <v>4697.3815384615</v>
       </c>
       <c r="O969" t="n">
-        <v>126829.3000000005</v>
+        <v>122131.919999999</v>
       </c>
       <c r="P969" t="n">
         <v>10900</v>
       </c>
       <c r="Q969" t="n">
-        <v>294300</v>
+        <v>283400</v>
       </c>
     </row>
     <row r="970">
@@ -44801,7 +44801,7 @@
         </is>
       </c>
       <c r="J983" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K983" t="n">
         <v>0</v>
@@ -44810,19 +44810,19 @@
         <v>0</v>
       </c>
       <c r="M983" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N983" t="n">
         <v>14751.820338983</v>
       </c>
       <c r="O983" t="n">
-        <v>88510.92203389799</v>
+        <v>147518.20338983</v>
       </c>
       <c r="P983" t="n">
         <v>37100</v>
       </c>
       <c r="Q983" t="n">
-        <v>222600</v>
+        <v>371000</v>
       </c>
     </row>
     <row r="984">
@@ -45656,7 +45656,7 @@
         </is>
       </c>
       <c r="J1001" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K1001" t="n">
         <v>0</v>
@@ -45665,19 +45665,19 @@
         <v>0</v>
       </c>
       <c r="M1001" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N1001" t="n">
-        <v>14327.785</v>
+        <v>14327.79</v>
       </c>
       <c r="O1001" t="n">
-        <v>57311.14</v>
+        <v>28655.58</v>
       </c>
       <c r="P1001" t="n">
         <v>29900</v>
       </c>
       <c r="Q1001" t="n">
-        <v>119600</v>
+        <v>59800</v>
       </c>
     </row>
     <row r="1002">
@@ -45700,7 +45700,7 @@
         </is>
       </c>
       <c r="J1002" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K1002" t="n">
         <v>0</v>
@@ -45709,19 +45709,19 @@
         <v>0</v>
       </c>
       <c r="M1002" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N1002" t="n">
-        <v>2000.7088990826</v>
+        <v>2000.711682243</v>
       </c>
       <c r="O1002" t="n">
-        <v>212075.1433027556</v>
+        <v>208074.014953272</v>
       </c>
       <c r="P1002" t="n">
         <v>2000</v>
       </c>
       <c r="Q1002" t="n">
-        <v>212000</v>
+        <v>208000</v>
       </c>
     </row>
     <row r="1003">
@@ -45792,7 +45792,7 @@
         </is>
       </c>
       <c r="J1004" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K1004" t="n">
         <v>0</v>
@@ -45801,19 +45801,19 @@
         <v>0</v>
       </c>
       <c r="M1004" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N1004" t="n">
         <v>8671.389999999999</v>
       </c>
       <c r="O1004" t="n">
-        <v>69371.12</v>
+        <v>52028.34</v>
       </c>
       <c r="P1004" t="n">
         <v>20500</v>
       </c>
       <c r="Q1004" t="n">
-        <v>164000</v>
+        <v>123000</v>
       </c>
     </row>
     <row r="1005">
@@ -45841,10 +45841,10 @@
         </is>
       </c>
       <c r="J1005" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K1005" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L1005" t="n">
         <v>0</v>
@@ -45890,10 +45890,10 @@
         </is>
       </c>
       <c r="J1006" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="K1006" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L1006" t="n">
         <v>0</v>
@@ -46081,7 +46081,7 @@
         </is>
       </c>
       <c r="J1010" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K1010" t="n">
         <v>0</v>
@@ -46090,19 +46090,19 @@
         <v>0</v>
       </c>
       <c r="M1010" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N1010" t="n">
         <v>1934.77</v>
       </c>
       <c r="O1010" t="n">
-        <v>52238.79</v>
+        <v>50304.02</v>
       </c>
       <c r="P1010" t="n">
         <v>8900</v>
       </c>
       <c r="Q1010" t="n">
-        <v>240300</v>
+        <v>231400</v>
       </c>
     </row>
     <row r="1011">
@@ -46240,10 +46240,10 @@
         <v>79</v>
       </c>
       <c r="N1013" t="n">
-        <v>7046.9398267273</v>
+        <v>7046.9398265771</v>
       </c>
       <c r="O1013" t="n">
-        <v>556708.2463114567</v>
+        <v>556708.2462995909</v>
       </c>
       <c r="P1013" t="n">
         <v>9900</v>
@@ -46274,7 +46274,7 @@
         </is>
       </c>
       <c r="J1014" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K1014" t="n">
         <v>0</v>
@@ -46283,19 +46283,19 @@
         <v>3</v>
       </c>
       <c r="M1014" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N1014" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1014" t="n">
-        <v>121692.35</v>
+        <v>267723.17</v>
       </c>
       <c r="P1014" t="n">
         <v>27900</v>
       </c>
       <c r="Q1014" t="n">
-        <v>139500</v>
+        <v>306900</v>
       </c>
     </row>
     <row r="1015">
@@ -47291,7 +47291,7 @@
         </is>
       </c>
       <c r="J1035" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="K1035" t="n">
         <v>0</v>
@@ -47300,19 +47300,19 @@
         <v>0</v>
       </c>
       <c r="M1035" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="N1035" t="n">
         <v>426.1</v>
       </c>
       <c r="O1035" t="n">
-        <v>74567.5</v>
+        <v>66045.5</v>
       </c>
       <c r="P1035" t="n">
         <v>2900</v>
       </c>
       <c r="Q1035" t="n">
-        <v>507500</v>
+        <v>449500</v>
       </c>
     </row>
     <row r="1036">
@@ -47438,7 +47438,7 @@
         </is>
       </c>
       <c r="J1038" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K1038" t="n">
         <v>0</v>
@@ -47447,19 +47447,19 @@
         <v>0</v>
       </c>
       <c r="M1038" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N1038" t="n">
-        <v>315.02741248097</v>
+        <v>315.02745788668</v>
       </c>
       <c r="O1038" t="n">
-        <v>22997.00111111081</v>
+        <v>21736.89459418092</v>
       </c>
       <c r="P1038" t="n">
         <v>2200</v>
       </c>
       <c r="Q1038" t="n">
-        <v>160600</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="1039">
@@ -47833,22 +47833,22 @@
         <v>0</v>
       </c>
       <c r="L1047" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1047" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N1047" t="n">
         <v>6761.25</v>
       </c>
       <c r="O1047" t="n">
-        <v>622035</v>
+        <v>540900</v>
       </c>
       <c r="P1047" t="n">
         <v>5200</v>
       </c>
       <c r="Q1047" t="n">
-        <v>478400</v>
+        <v>416000</v>
       </c>
     </row>
     <row r="1048">
@@ -48220,7 +48220,7 @@
         </is>
       </c>
       <c r="J1056" t="n">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="K1056" t="n">
         <v>0</v>
@@ -48229,19 +48229,19 @@
         <v>0</v>
       </c>
       <c r="M1056" t="n">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="N1056" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1056" t="n">
-        <v>617699.25</v>
+        <v>611816.4</v>
       </c>
       <c r="P1056" t="n">
         <v>1900</v>
       </c>
       <c r="Q1056" t="n">
-        <v>997500</v>
+        <v>988000</v>
       </c>
     </row>
     <row r="1057">
@@ -49975,22 +49975,22 @@
         <v>0</v>
       </c>
       <c r="L1094" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M1094" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="N1094" t="n">
-        <v>220.00066011878</v>
+        <v>220.00020804114</v>
       </c>
       <c r="O1094" t="n">
-        <v>121000.363065329</v>
+        <v>99000.09361851301</v>
       </c>
       <c r="P1094" t="n">
         <v>260</v>
       </c>
       <c r="Q1094" t="n">
-        <v>143000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="1095">
@@ -50337,7 +50337,7 @@
         </is>
       </c>
       <c r="J1102" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K1102" t="n">
         <v>0</v>
@@ -50346,19 +50346,19 @@
         <v>0</v>
       </c>
       <c r="M1102" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N1102" t="n">
         <v>3504.16</v>
       </c>
       <c r="O1102" t="n">
-        <v>238282.88</v>
+        <v>234778.72</v>
       </c>
       <c r="P1102" t="n">
         <v>3900</v>
       </c>
       <c r="Q1102" t="n">
-        <v>265200</v>
+        <v>261300</v>
       </c>
     </row>
     <row r="1103">
@@ -50383,7 +50383,7 @@
         </is>
       </c>
       <c r="J1103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1103" t="n">
         <v>0</v>
@@ -50392,19 +50392,19 @@
         <v>0</v>
       </c>
       <c r="M1103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N1103" t="n">
         <v>12000</v>
       </c>
       <c r="O1103" t="n">
-        <v>36000</v>
+        <v>12000</v>
       </c>
       <c r="P1103" t="n">
         <v>15000</v>
       </c>
       <c r="Q1103" t="n">
-        <v>45000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1104">
@@ -50659,7 +50659,7 @@
         </is>
       </c>
       <c r="J1109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K1109" t="n">
         <v>0</v>
@@ -50668,19 +50668,19 @@
         <v>0</v>
       </c>
       <c r="M1109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N1109" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O1109" t="n">
-        <v>97081.90000000001</v>
+        <v>87373.71000000001</v>
       </c>
       <c r="P1109" t="n">
         <v>10200</v>
       </c>
       <c r="Q1109" t="n">
-        <v>102000</v>
+        <v>91800</v>
       </c>
     </row>
     <row r="1110">
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="J1112" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K1112" t="n">
         <v>0</v>
@@ -50806,19 +50806,19 @@
         <v>0</v>
       </c>
       <c r="M1112" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N1112" t="n">
         <v>6270.21</v>
       </c>
       <c r="O1112" t="n">
-        <v>31351.05</v>
+        <v>12540.42</v>
       </c>
       <c r="P1112" t="n">
         <v>8900</v>
       </c>
       <c r="Q1112" t="n">
-        <v>44500</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="1113">
@@ -50935,10 +50935,10 @@
         </is>
       </c>
       <c r="J1115" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K1115" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L1115" t="n">
         <v>0</v>
@@ -51119,7 +51119,7 @@
         </is>
       </c>
       <c r="J1119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1119" t="n">
         <v>0</v>
@@ -51128,19 +51128,19 @@
         <v>0</v>
       </c>
       <c r="M1119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N1119" t="n">
         <v>17986.24</v>
       </c>
       <c r="O1119" t="n">
-        <v>125903.68</v>
+        <v>143889.92</v>
       </c>
       <c r="P1119" t="n">
         <v>18500</v>
       </c>
       <c r="Q1119" t="n">
-        <v>129500</v>
+        <v>148000</v>
       </c>
     </row>
     <row r="1120">
@@ -51315,10 +51315,10 @@
         <v>9</v>
       </c>
       <c r="N1123" t="n">
-        <v>1160.1569811321</v>
+        <v>1160.1575510204</v>
       </c>
       <c r="O1123" t="n">
-        <v>10441.4128301889</v>
+        <v>10441.4179591836</v>
       </c>
       <c r="P1123" t="n">
         <v>1600</v>
@@ -51349,7 +51349,7 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K1124" t="n">
         <v>0</v>
@@ -51358,19 +51358,19 @@
         <v>0</v>
       </c>
       <c r="M1124" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N1124" t="n">
         <v>7740</v>
       </c>
       <c r="O1124" t="n">
-        <v>325080</v>
+        <v>317340</v>
       </c>
       <c r="P1124" t="n">
         <v>9500</v>
       </c>
       <c r="Q1124" t="n">
-        <v>399000</v>
+        <v>389500</v>
       </c>
     </row>
     <row r="1125">
@@ -51395,28 +51395,28 @@
         </is>
       </c>
       <c r="J1125" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K1125" t="n">
         <v>0</v>
       </c>
       <c r="L1125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1125" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N1125" t="n">
         <v>7480</v>
       </c>
       <c r="O1125" t="n">
-        <v>149600</v>
+        <v>142120</v>
       </c>
       <c r="P1125" t="n">
         <v>9500</v>
       </c>
       <c r="Q1125" t="n">
-        <v>190000</v>
+        <v>180500</v>
       </c>
     </row>
     <row r="1126">
@@ -51441,13 +51441,13 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1126" t="n">
         <v>27</v>
@@ -51533,7 +51533,7 @@
         </is>
       </c>
       <c r="J1128" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K1128" t="n">
         <v>0</v>
@@ -51542,19 +51542,19 @@
         <v>0</v>
       </c>
       <c r="M1128" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N1128" t="n">
         <v>5280</v>
       </c>
       <c r="O1128" t="n">
-        <v>142560</v>
+        <v>137280</v>
       </c>
       <c r="P1128" t="n">
         <v>6900</v>
       </c>
       <c r="Q1128" t="n">
-        <v>186300</v>
+        <v>179400</v>
       </c>
     </row>
     <row r="1129">
@@ -51815,10 +51815,10 @@
         </is>
       </c>
       <c r="J1134" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="K1134" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L1134" t="n">
         <v>0</v>
@@ -51959,28 +51959,28 @@
         </is>
       </c>
       <c r="J1137" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K1137" t="n">
         <v>0</v>
       </c>
       <c r="L1137" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M1137" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N1137" t="n">
         <v>3520</v>
       </c>
       <c r="O1137" t="n">
-        <v>112640</v>
+        <v>105600</v>
       </c>
       <c r="P1137" t="n">
         <v>4500</v>
       </c>
       <c r="Q1137" t="n">
-        <v>144000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="1138">
@@ -52097,7 +52097,7 @@
         </is>
       </c>
       <c r="J1140" t="n">
-        <v>202</v>
+        <v>502</v>
       </c>
       <c r="K1140" t="n">
         <v>0</v>
@@ -52106,19 +52106,19 @@
         <v>0</v>
       </c>
       <c r="M1140" t="n">
-        <v>202</v>
+        <v>502</v>
       </c>
       <c r="N1140" t="n">
         <v>9240</v>
       </c>
       <c r="O1140" t="n">
-        <v>1866480</v>
+        <v>4638480</v>
       </c>
       <c r="P1140" t="n">
         <v>11500</v>
       </c>
       <c r="Q1140" t="n">
-        <v>2323000</v>
+        <v>5773000</v>
       </c>
     </row>
     <row r="1141">
@@ -52143,7 +52143,7 @@
         </is>
       </c>
       <c r="J1141" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K1141" t="n">
         <v>0</v>
@@ -52152,19 +52152,19 @@
         <v>0</v>
       </c>
       <c r="M1141" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="N1141" t="n">
         <v>2288</v>
       </c>
       <c r="O1141" t="n">
-        <v>526240</v>
+        <v>517088</v>
       </c>
       <c r="P1141" t="n">
         <v>2900</v>
       </c>
       <c r="Q1141" t="n">
-        <v>667000</v>
+        <v>655400</v>
       </c>
     </row>
     <row r="1142">
@@ -52189,7 +52189,7 @@
         </is>
       </c>
       <c r="J1142" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K1142" t="n">
         <v>0</v>
@@ -52198,19 +52198,19 @@
         <v>0</v>
       </c>
       <c r="M1142" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="N1142" t="n">
         <v>4576</v>
       </c>
       <c r="O1142" t="n">
-        <v>45760</v>
+        <v>183040</v>
       </c>
       <c r="P1142" t="n">
         <v>5900</v>
       </c>
       <c r="Q1142" t="n">
-        <v>59000</v>
+        <v>236000</v>
       </c>
     </row>
     <row r="1143">
@@ -52235,7 +52235,7 @@
         </is>
       </c>
       <c r="J1143" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="K1143" t="n">
         <v>0</v>
@@ -52244,19 +52244,19 @@
         <v>0</v>
       </c>
       <c r="M1143" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="N1143" t="n">
         <v>5280</v>
       </c>
       <c r="O1143" t="n">
-        <v>47520</v>
+        <v>190080</v>
       </c>
       <c r="P1143" t="n">
         <v>6900</v>
       </c>
       <c r="Q1143" t="n">
-        <v>62100</v>
+        <v>248400</v>
       </c>
     </row>
     <row r="1144">
@@ -54279,28 +54279,28 @@
         </is>
       </c>
       <c r="J1187" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K1187" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L1187" t="n">
         <v>0</v>
       </c>
       <c r="M1187" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N1187" t="n">
         <v>571.87</v>
       </c>
       <c r="O1187" t="n">
-        <v>48608.95</v>
+        <v>48037.08</v>
       </c>
       <c r="P1187" t="n">
         <v>2500</v>
       </c>
       <c r="Q1187" t="n">
-        <v>212500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="1188">
@@ -54330,28 +54330,28 @@
         </is>
       </c>
       <c r="J1188" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K1188" t="n">
         <v>0</v>
       </c>
       <c r="L1188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1188" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N1188" t="n">
-        <v>2432.1358227848</v>
+        <v>2432.1360526316</v>
       </c>
       <c r="O1188" t="n">
-        <v>36482.037341772</v>
+        <v>29185.6326315792</v>
       </c>
       <c r="P1188" t="n">
         <v>4500</v>
       </c>
       <c r="Q1188" t="n">
-        <v>67500</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="1189">
@@ -54388,10 +54388,10 @@
         <v>23</v>
       </c>
       <c r="N1189" t="n">
-        <v>227.41614285714</v>
+        <v>227.41615210843</v>
       </c>
       <c r="O1189" t="n">
-        <v>5230.57128571422</v>
+        <v>5230.57149849389</v>
       </c>
       <c r="P1189" t="n">
         <v>1200</v>
@@ -55091,10 +55091,10 @@
         <v>45</v>
       </c>
       <c r="N1204" t="n">
-        <v>4171.6685019206</v>
+        <v>4171.6684942085</v>
       </c>
       <c r="O1204" t="n">
-        <v>187725.082586427</v>
+        <v>187725.0822393825</v>
       </c>
       <c r="P1204" t="n">
         <v>5000</v>
@@ -56314,7 +56314,7 @@
         </is>
       </c>
       <c r="J1231" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1231" t="n">
         <v>0</v>
@@ -56323,19 +56323,19 @@
         <v>0</v>
       </c>
       <c r="M1231" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N1231" t="n">
         <v>4550</v>
       </c>
       <c r="O1231" t="n">
-        <v>195650</v>
+        <v>191100</v>
       </c>
       <c r="P1231" t="n">
         <v>5500</v>
       </c>
       <c r="Q1231" t="n">
-        <v>236500</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="1232">
@@ -56501,7 +56501,7 @@
         </is>
       </c>
       <c r="J1235" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="K1235" t="n">
         <v>0</v>
@@ -56510,19 +56510,19 @@
         <v>0</v>
       </c>
       <c r="M1235" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N1235" t="n">
         <v>2210</v>
       </c>
       <c r="O1235" t="n">
-        <v>530400</v>
+        <v>519350</v>
       </c>
       <c r="P1235" t="n">
         <v>2700</v>
       </c>
       <c r="Q1235" t="n">
-        <v>648000</v>
+        <v>634500</v>
       </c>
     </row>
     <row r="1236">
@@ -56550,13 +56550,13 @@
         </is>
       </c>
       <c r="J1236" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K1236" t="n">
         <v>0</v>
       </c>
       <c r="L1236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1236" t="n">
         <v>154</v>
@@ -56599,7 +56599,7 @@
         </is>
       </c>
       <c r="J1237" t="n">
-        <v>2771</v>
+        <v>2747</v>
       </c>
       <c r="K1237" t="n">
         <v>0</v>
@@ -56608,19 +56608,19 @@
         <v>0</v>
       </c>
       <c r="M1237" t="n">
-        <v>2771</v>
+        <v>2747</v>
       </c>
       <c r="N1237" t="n">
         <v>467</v>
       </c>
       <c r="O1237" t="n">
-        <v>1294057</v>
+        <v>1282849</v>
       </c>
       <c r="P1237" t="n">
         <v>600</v>
       </c>
       <c r="Q1237" t="n">
-        <v>1662600</v>
+        <v>1648200</v>
       </c>
     </row>
     <row r="1238">
@@ -56648,28 +56648,28 @@
         </is>
       </c>
       <c r="J1238" t="n">
-        <v>1500</v>
+        <v>2630</v>
       </c>
       <c r="K1238" t="n">
         <v>0</v>
       </c>
       <c r="L1238" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M1238" t="n">
-        <v>1488</v>
+        <v>2630</v>
       </c>
       <c r="N1238" t="n">
         <v>425</v>
       </c>
       <c r="O1238" t="n">
-        <v>632400</v>
+        <v>1117750</v>
       </c>
       <c r="P1238" t="n">
         <v>500</v>
       </c>
       <c r="Q1238" t="n">
-        <v>744000</v>
+        <v>1315000</v>
       </c>
     </row>
     <row r="1239">
@@ -56697,7 +56697,7 @@
         </is>
       </c>
       <c r="J1239" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K1239" t="n">
         <v>0</v>
@@ -56706,19 +56706,19 @@
         <v>0</v>
       </c>
       <c r="M1239" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N1239" t="n">
         <v>1700</v>
       </c>
       <c r="O1239" t="n">
-        <v>297500</v>
+        <v>295800</v>
       </c>
       <c r="P1239" t="n">
         <v>2000</v>
       </c>
       <c r="Q1239" t="n">
-        <v>350000</v>
+        <v>348000</v>
       </c>
     </row>
     <row r="1240">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -12276,10 +12276,10 @@
         <v>6</v>
       </c>
       <c r="N273" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O273" t="n">
-        <v>74534.777757498</v>
+        <v>74534.77776522</v>
       </c>
       <c r="P273" t="n">
         <v>19900</v>
@@ -15458,22 +15458,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N343" t="n">
-        <v>2403.5207171448</v>
+        <v>2403.5207309746</v>
       </c>
       <c r="O343" t="n">
-        <v>740284.3808805984</v>
+        <v>737880.8644092022</v>
       </c>
       <c r="P343" t="n">
         <v>3500</v>
       </c>
       <c r="Q343" t="n">
-        <v>1078000</v>
+        <v>1074500</v>
       </c>
     </row>
     <row r="344">
@@ -27256,22 +27256,22 @@
         <v>0</v>
       </c>
       <c r="L607" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M607" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N607" t="n">
         <v>3424</v>
       </c>
       <c r="O607" t="n">
-        <v>150656</v>
+        <v>147232</v>
       </c>
       <c r="P607" t="n">
         <v>5900</v>
       </c>
       <c r="Q607" t="n">
-        <v>259600</v>
+        <v>253700</v>
       </c>
     </row>
     <row r="608">
@@ -30202,22 +30202,22 @@
         <v>0</v>
       </c>
       <c r="L671" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M671" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N671" t="n">
         <v>5682</v>
       </c>
       <c r="O671" t="n">
-        <v>68184</v>
+        <v>62502</v>
       </c>
       <c r="P671" t="n">
         <v>9900</v>
       </c>
       <c r="Q671" t="n">
-        <v>118800</v>
+        <v>108900</v>
       </c>
     </row>
     <row r="672">
@@ -33245,22 +33245,22 @@
         <v>0</v>
       </c>
       <c r="L737" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M737" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N737" t="n">
-        <v>1592.2857321429</v>
+        <v>1592.2857602862</v>
       </c>
       <c r="O737" t="n">
-        <v>97129.42966071691</v>
+        <v>95537.14561717201</v>
       </c>
       <c r="P737" t="n">
         <v>2500</v>
       </c>
       <c r="Q737" t="n">
-        <v>152500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="738">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -2183,10 +2183,10 @@
         <v>19</v>
       </c>
       <c r="N44" t="n">
-        <v>3716.3301967213</v>
+        <v>3716.3301970443</v>
       </c>
       <c r="O44" t="n">
-        <v>70610.2737377047</v>
+        <v>70610.2737438417</v>
       </c>
       <c r="P44" t="n">
         <v>9500</v>
@@ -11290,10 +11290,10 @@
         <v>23</v>
       </c>
       <c r="N251" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O251" t="n">
-        <v>82667.8174079538</v>
+        <v>82667.81728813531</v>
       </c>
       <c r="P251" t="n">
         <v>6500</v>
@@ -12221,25 +12221,25 @@
         <v>6</v>
       </c>
       <c r="K272" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M272" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N272" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O272" t="n">
-        <v>74534.77792105199</v>
+        <v>186336.944861655</v>
       </c>
       <c r="P272" t="n">
         <v>19900</v>
       </c>
       <c r="Q272" t="n">
-        <v>119400</v>
+        <v>298500</v>
       </c>
     </row>
     <row r="273">
@@ -12736,10 +12736,10 @@
         <v>7</v>
       </c>
       <c r="N283" t="n">
-        <v>3041.6600148258</v>
+        <v>3041.6600148478</v>
       </c>
       <c r="O283" t="n">
-        <v>21291.6201037806</v>
+        <v>21291.6201039346</v>
       </c>
       <c r="P283" t="n">
         <v>5500</v>
@@ -15182,22 +15182,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M337" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="N337" t="n">
-        <v>1630.9246804626</v>
+        <v>1630.9246976176</v>
       </c>
       <c r="O337" t="n">
-        <v>169616.1667681104</v>
+        <v>150045.0721808192</v>
       </c>
       <c r="P337" t="n">
         <v>2500</v>
       </c>
       <c r="Q337" t="n">
-        <v>260000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="338">
@@ -16396,22 +16396,22 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N364" t="n">
         <v>17328</v>
       </c>
       <c r="O364" t="n">
-        <v>259920</v>
+        <v>242592</v>
       </c>
       <c r="P364" t="n">
         <v>32900</v>
       </c>
       <c r="Q364" t="n">
-        <v>493500</v>
+        <v>460600</v>
       </c>
     </row>
     <row r="365">
@@ -19575,10 +19575,10 @@
         <v>40</v>
       </c>
       <c r="N437" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="O437" t="n">
-        <v>171407.856565656</v>
+        <v>171407.857215188</v>
       </c>
       <c r="P437" t="n">
         <v>6900</v>
@@ -32283,22 +32283,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M716" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="N716" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O716" t="n">
-        <v>189504.84195255</v>
+        <v>134927.4470525742</v>
       </c>
       <c r="P716" t="n">
         <v>2300</v>
       </c>
       <c r="Q716" t="n">
-        <v>287500</v>
+        <v>204700</v>
       </c>
     </row>
     <row r="717">
@@ -47314,10 +47314,10 @@
         <v>126</v>
       </c>
       <c r="N1035" t="n">
-        <v>465.87102642276</v>
+        <v>465.87102746694</v>
       </c>
       <c r="O1035" t="n">
-        <v>58699.74932926776</v>
+        <v>58699.74946083444</v>
       </c>
       <c r="P1035" t="n">
         <v>2500</v>
@@ -54958,10 +54958,10 @@
         <v>41</v>
       </c>
       <c r="N1201" t="n">
-        <v>2539.571774676</v>
+        <v>2539.5717817818</v>
       </c>
       <c r="O1201" t="n">
-        <v>104122.442761716</v>
+        <v>104122.4430530538</v>
       </c>
       <c r="P1201" t="n">
         <v>2900</v>
@@ -55004,10 +55004,10 @@
         <v>45</v>
       </c>
       <c r="N1202" t="n">
-        <v>4171.6684503311</v>
+        <v>4171.6684420772</v>
       </c>
       <c r="O1202" t="n">
-        <v>187725.0802648995</v>
+        <v>187725.079893474</v>
       </c>
       <c r="P1202" t="n">
         <v>5000</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -944,10 +944,10 @@
         <v>26</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3106796117</v>
+        <v>1811.3107843137</v>
       </c>
       <c r="O13" t="n">
-        <v>47094.0776699042</v>
+        <v>47094.0803921562</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -8001,10 +8001,10 @@
         <v>295</v>
       </c>
       <c r="N178" t="n">
-        <v>1098.0691359493</v>
+        <v>1098.0698699716</v>
       </c>
       <c r="O178" t="n">
-        <v>323930.3951050435</v>
+        <v>323930.611641622</v>
       </c>
       <c r="P178" t="n">
         <v>1500</v>
@@ -9102,22 +9102,22 @@
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N203" t="n">
         <v>10600</v>
       </c>
       <c r="O203" t="n">
-        <v>466400</v>
+        <v>455800</v>
       </c>
       <c r="P203" t="n">
         <v>17200</v>
       </c>
       <c r="Q203" t="n">
-        <v>756800</v>
+        <v>739600</v>
       </c>
     </row>
     <row r="204">
@@ -9746,10 +9746,10 @@
         <v>66</v>
       </c>
       <c r="N217" t="n">
-        <v>3230.0661344538</v>
+        <v>3230.0661016949</v>
       </c>
       <c r="O217" t="n">
-        <v>213184.3648739508</v>
+        <v>213184.3627118634</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -10296,10 +10296,10 @@
         <v>34</v>
       </c>
       <c r="N229" t="n">
-        <v>3795.7100076321</v>
+        <v>3795.710007638</v>
       </c>
       <c r="O229" t="n">
-        <v>129054.1402594914</v>
+        <v>129054.140259692</v>
       </c>
       <c r="P229" t="n">
         <v>6200</v>
@@ -10521,10 +10521,10 @@
         <v>5</v>
       </c>
       <c r="N234" t="n">
-        <v>4890.9300537634</v>
+        <v>4890.9300539811</v>
       </c>
       <c r="O234" t="n">
-        <v>24454.650268817</v>
+        <v>24454.6502699055</v>
       </c>
       <c r="P234" t="n">
         <v>8200</v>
@@ -11515,10 +11515,10 @@
         <v>14</v>
       </c>
       <c r="N256" t="n">
-        <v>4891</v>
+        <v>4906.5393169182</v>
       </c>
       <c r="O256" t="n">
-        <v>68474</v>
+        <v>68691.5504368548</v>
       </c>
       <c r="P256" t="n">
         <v>8200</v>
@@ -11694,22 +11694,22 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M260" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N260" t="n">
         <v>2090.85</v>
       </c>
       <c r="O260" t="n">
-        <v>591710.5499999999</v>
+        <v>589619.7</v>
       </c>
       <c r="P260" t="n">
         <v>2900</v>
       </c>
       <c r="Q260" t="n">
-        <v>820700</v>
+        <v>817800</v>
       </c>
     </row>
     <row r="261">
@@ -12422,10 +12422,10 @@
         <v>282</v>
       </c>
       <c r="N276" t="n">
-        <v>3472.2762877567</v>
+        <v>3472.2762983503</v>
       </c>
       <c r="O276" t="n">
-        <v>979181.9131473894</v>
+        <v>979181.9161347846</v>
       </c>
       <c r="P276" t="n">
         <v>5900</v>
@@ -12825,10 +12825,10 @@
         <v>8</v>
       </c>
       <c r="N285" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O285" t="n">
-        <v>34969.3701071016</v>
+        <v>34969.37011124</v>
       </c>
       <c r="P285" t="n">
         <v>8900</v>
@@ -15143,22 +15143,22 @@
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M336" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="N336" t="n">
-        <v>1630.9246990529</v>
+        <v>1630.9247048027</v>
       </c>
       <c r="O336" t="n">
-        <v>177770.7921967661</v>
+        <v>171247.0940042835</v>
       </c>
       <c r="P336" t="n">
         <v>2500</v>
       </c>
       <c r="Q336" t="n">
-        <v>272500</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="337">
@@ -15373,22 +15373,22 @@
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M341" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N341" t="n">
-        <v>2403.5211979522</v>
+        <v>2403.5212124317</v>
       </c>
       <c r="O341" t="n">
-        <v>723459.8805836122</v>
+        <v>718652.8425170783</v>
       </c>
       <c r="P341" t="n">
         <v>3500</v>
       </c>
       <c r="Q341" t="n">
-        <v>1053500</v>
+        <v>1046500</v>
       </c>
     </row>
     <row r="342">
@@ -19359,10 +19359,10 @@
         <v>20</v>
       </c>
       <c r="N432" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="O432" t="n">
-        <v>124159.76446235</v>
+        <v>124263.34602336</v>
       </c>
       <c r="P432" t="n">
         <v>9900</v>
@@ -19964,10 +19964,10 @@
         <v>8</v>
       </c>
       <c r="N446" t="n">
-        <v>3591.13</v>
+        <v>3594.9639466192</v>
       </c>
       <c r="O446" t="n">
-        <v>28729.04</v>
+        <v>28759.7115729536</v>
       </c>
       <c r="P446" t="n">
         <v>6300</v>
@@ -21623,10 +21623,10 @@
         <v>32</v>
       </c>
       <c r="N484" t="n">
-        <v>9627.34</v>
+        <v>9808.987924528299</v>
       </c>
       <c r="O484" t="n">
-        <v>308074.88</v>
+        <v>313887.6135849056</v>
       </c>
       <c r="P484" t="n">
         <v>15900</v>
@@ -22019,10 +22019,10 @@
         <v>121</v>
       </c>
       <c r="N493" t="n">
-        <v>548.14706357215</v>
+        <v>548.14704568528</v>
       </c>
       <c r="O493" t="n">
-        <v>66325.79469223015</v>
+        <v>66325.79252791888</v>
       </c>
       <c r="P493" t="n">
         <v>2000</v>
@@ -27316,10 +27316,10 @@
         <v>20</v>
       </c>
       <c r="N608" t="n">
-        <v>8858.16</v>
+        <v>8873.1568848758</v>
       </c>
       <c r="O608" t="n">
-        <v>177163.2</v>
+        <v>177463.137697516</v>
       </c>
       <c r="P608" t="n">
         <v>15500</v>
@@ -29571,10 +29571,10 @@
         <v>42</v>
       </c>
       <c r="N657" t="n">
-        <v>6849.2</v>
+        <v>6862.329456869</v>
       </c>
       <c r="O657" t="n">
-        <v>287666.4</v>
+        <v>288217.837188498</v>
       </c>
       <c r="P657" t="n">
         <v>11500</v>
@@ -32101,22 +32101,22 @@
         <v>0</v>
       </c>
       <c r="L712" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M712" t="n">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="N712" t="n">
         <v>1803</v>
       </c>
       <c r="O712" t="n">
-        <v>257829</v>
+        <v>187512</v>
       </c>
       <c r="P712" t="n">
         <v>3900</v>
       </c>
       <c r="Q712" t="n">
-        <v>557700</v>
+        <v>405600</v>
       </c>
     </row>
     <row r="713">
@@ -32193,22 +32193,22 @@
         <v>0</v>
       </c>
       <c r="L714" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M714" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N714" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O714" t="n">
-        <v>103090.6334532652</v>
+        <v>100058.5559813862</v>
       </c>
       <c r="P714" t="n">
         <v>2300</v>
       </c>
       <c r="Q714" t="n">
-        <v>156400</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="715">
@@ -32427,10 +32427,10 @@
         <v>157</v>
       </c>
       <c r="N719" t="n">
-        <v>1771.0893205318</v>
+        <v>1771.0891278195</v>
       </c>
       <c r="O719" t="n">
-        <v>278061.0233234926</v>
+        <v>278060.9930676615</v>
       </c>
       <c r="P719" t="n">
         <v>2500</v>
@@ -32749,10 +32749,10 @@
         <v>275</v>
       </c>
       <c r="N726" t="n">
-        <v>3224.5699223947</v>
+        <v>3224.5699334073</v>
       </c>
       <c r="O726" t="n">
-        <v>886756.7286585425</v>
+        <v>886756.7316870076</v>
       </c>
       <c r="P726" t="n">
         <v>4500</v>
@@ -32795,10 +32795,10 @@
         <v>255</v>
       </c>
       <c r="N727" t="n">
-        <v>1655.9291188041</v>
+        <v>1655.9290150913</v>
       </c>
       <c r="O727" t="n">
-        <v>422261.9252950455</v>
+        <v>422261.8988482815</v>
       </c>
       <c r="P727" t="n">
         <v>2500</v>
@@ -38357,10 +38357,10 @@
         <v>232</v>
       </c>
       <c r="N847" t="n">
-        <v>3110.8359666534</v>
+        <v>3110.8359331476</v>
       </c>
       <c r="O847" t="n">
-        <v>721713.9442635889</v>
+        <v>721713.9364902432</v>
       </c>
       <c r="P847" t="n">
         <v>4500</v>
@@ -38763,22 +38763,22 @@
         <v>0</v>
       </c>
       <c r="L856" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M856" t="n">
-        <v>1272</v>
+        <v>1217</v>
       </c>
       <c r="N856" t="n">
-        <v>703.79469605084</v>
+        <v>703.79468467395</v>
       </c>
       <c r="O856" t="n">
-        <v>895226.8533766685</v>
+        <v>856518.1312481972</v>
       </c>
       <c r="P856" t="n">
         <v>900</v>
       </c>
       <c r="Q856" t="n">
-        <v>1144800</v>
+        <v>1095300</v>
       </c>
     </row>
     <row r="857">
@@ -40938,22 +40938,22 @@
         <v>0</v>
       </c>
       <c r="L902" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M902" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N902" t="n">
-        <v>2832.1953125</v>
+        <v>2832.1953968254</v>
       </c>
       <c r="O902" t="n">
-        <v>19825.3671875</v>
+        <v>16993.1723809524</v>
       </c>
       <c r="P902" t="n">
         <v>12900</v>
       </c>
       <c r="Q902" t="n">
-        <v>90300</v>
+        <v>77400</v>
       </c>
     </row>
     <row r="903">
@@ -46152,22 +46152,22 @@
         <v>0</v>
       </c>
       <c r="L1011" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M1011" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N1011" t="n">
         <v>24338.47</v>
       </c>
       <c r="O1011" t="n">
-        <v>243384.7</v>
+        <v>194707.76</v>
       </c>
       <c r="P1011" t="n">
         <v>27900</v>
       </c>
       <c r="Q1011" t="n">
-        <v>279000</v>
+        <v>223200</v>
       </c>
     </row>
     <row r="1012">
@@ -51975,22 +51975,22 @@
         <v>0</v>
       </c>
       <c r="L1137" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="M1137" t="n">
-        <v>516</v>
+        <v>166</v>
       </c>
       <c r="N1137" t="n">
         <v>9240</v>
       </c>
       <c r="O1137" t="n">
-        <v>4767840</v>
+        <v>1533840</v>
       </c>
       <c r="P1137" t="n">
         <v>11500</v>
       </c>
       <c r="Q1137" t="n">
-        <v>5934000</v>
+        <v>1909000</v>
       </c>
     </row>
     <row r="1138">
@@ -56526,22 +56526,22 @@
         <v>0</v>
       </c>
       <c r="L1235" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M1235" t="n">
-        <v>2587</v>
+        <v>2532</v>
       </c>
       <c r="N1235" t="n">
         <v>425</v>
       </c>
       <c r="O1235" t="n">
-        <v>1099475</v>
+        <v>1076100</v>
       </c>
       <c r="P1235" t="n">
         <v>500</v>
       </c>
       <c r="Q1235" t="n">
-        <v>1293500</v>
+        <v>1266000</v>
       </c>
     </row>
     <row r="1236">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -1743,10 +1743,10 @@
         <v>13</v>
       </c>
       <c r="N33" t="n">
-        <v>12357.960428571</v>
+        <v>12357.960431655</v>
       </c>
       <c r="O33" t="n">
-        <v>160653.485571423</v>
+        <v>160653.485611515</v>
       </c>
       <c r="P33" t="n">
         <v>15900</v>
@@ -3708,10 +3708,10 @@
         <v>7</v>
       </c>
       <c r="N79" t="n">
-        <v>15711.963831169</v>
+        <v>15711.96379085</v>
       </c>
       <c r="O79" t="n">
-        <v>109983.746818183</v>
+        <v>109983.74653595</v>
       </c>
       <c r="P79" t="n">
         <v>28500</v>
@@ -5911,10 +5911,10 @@
         <v>19</v>
       </c>
       <c r="N130" t="n">
-        <v>2584.1380683507</v>
+        <v>2572.67</v>
       </c>
       <c r="O130" t="n">
-        <v>49098.6232986633</v>
+        <v>48880.73</v>
       </c>
       <c r="P130" t="n">
         <v>4700</v>
@@ -7706,10 +7706,10 @@
         <v>108</v>
       </c>
       <c r="N171" t="n">
-        <v>4937.3101733649</v>
+        <v>4937.3101737757</v>
       </c>
       <c r="O171" t="n">
-        <v>533229.4987234093</v>
+        <v>533229.4987677756</v>
       </c>
       <c r="P171" t="n">
         <v>7500</v>
@@ -8001,10 +8001,10 @@
         <v>271</v>
       </c>
       <c r="N178" t="n">
-        <v>1108.8838530981</v>
+        <v>1098.0703134021</v>
       </c>
       <c r="O178" t="n">
-        <v>300507.5241895851</v>
+        <v>297577.0549319691</v>
       </c>
       <c r="P178" t="n">
         <v>1500</v>
@@ -8401,10 +8401,10 @@
         <v>4</v>
       </c>
       <c r="N187" t="n">
-        <v>13261.303571429</v>
+        <v>12587</v>
       </c>
       <c r="O187" t="n">
-        <v>53045.214285716</v>
+        <v>50348</v>
       </c>
       <c r="P187" t="n">
         <v>18900</v>
@@ -9016,10 +9016,10 @@
         <v>56</v>
       </c>
       <c r="N201" t="n">
-        <v>2582.2548633316</v>
+        <v>2582.2548540429</v>
       </c>
       <c r="O201" t="n">
-        <v>144606.2723465696</v>
+        <v>144606.2718264024</v>
       </c>
       <c r="P201" t="n">
         <v>4500</v>
@@ -9341,10 +9341,10 @@
         <v>1</v>
       </c>
       <c r="N208" t="n">
-        <v>3154</v>
+        <v>3359.6956521739</v>
       </c>
       <c r="O208" t="n">
-        <v>3154</v>
+        <v>3359.6956521739</v>
       </c>
       <c r="P208" t="n">
         <v>5500</v>
@@ -9792,10 +9792,10 @@
         <v>92</v>
       </c>
       <c r="N218" t="n">
-        <v>1482.2572445348</v>
+        <v>1480</v>
       </c>
       <c r="O218" t="n">
-        <v>136367.6664972016</v>
+        <v>136160</v>
       </c>
       <c r="P218" t="n">
         <v>2600</v>
@@ -10521,10 +10521,10 @@
         <v>5</v>
       </c>
       <c r="N234" t="n">
-        <v>4890.9300540176</v>
+        <v>4890.9300540541</v>
       </c>
       <c r="O234" t="n">
-        <v>24454.650270088</v>
+        <v>24454.6502702705</v>
       </c>
       <c r="P234" t="n">
         <v>8200</v>
@@ -10930,22 +10930,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M243" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N243" t="n">
-        <v>7063.376059322</v>
+        <v>7041</v>
       </c>
       <c r="O243" t="n">
-        <v>155394.273305084</v>
+        <v>133779</v>
       </c>
       <c r="P243" t="n">
         <v>11500</v>
       </c>
       <c r="Q243" t="n">
-        <v>253000</v>
+        <v>218500</v>
       </c>
     </row>
     <row r="244">
@@ -11297,10 +11297,10 @@
         <v>17</v>
       </c>
       <c r="N251" t="n">
-        <v>3594.2528730512</v>
+        <v>3594.2528624535</v>
       </c>
       <c r="O251" t="n">
-        <v>61102.2988418704</v>
+        <v>61102.29866170949</v>
       </c>
       <c r="P251" t="n">
         <v>6500</v>
@@ -11469,10 +11469,10 @@
         <v>74</v>
       </c>
       <c r="N255" t="n">
-        <v>3354.2325655977</v>
+        <v>3240.850058309</v>
       </c>
       <c r="O255" t="n">
-        <v>248213.2098542298</v>
+        <v>239822.904314866</v>
       </c>
       <c r="P255" t="n">
         <v>5200</v>
@@ -11515,10 +11515,10 @@
         <v>10</v>
       </c>
       <c r="N256" t="n">
-        <v>7767.2727272727</v>
+        <v>7120</v>
       </c>
       <c r="O256" t="n">
-        <v>77672.727272727</v>
+        <v>71200</v>
       </c>
       <c r="P256" t="n">
         <v>8900</v>
@@ -11746,10 +11746,10 @@
         <v>266</v>
       </c>
       <c r="N261" t="n">
-        <v>2093.3158067369</v>
+        <v>2090.85</v>
       </c>
       <c r="O261" t="n">
-        <v>556822.0045920154</v>
+        <v>556166.1</v>
       </c>
       <c r="P261" t="n">
         <v>2900</v>
@@ -12462,22 +12462,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M277" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="N277" t="n">
-        <v>3472.276319645</v>
+        <v>3472.276322317</v>
       </c>
       <c r="O277" t="n">
-        <v>916680.94838628</v>
+        <v>895847.291157786</v>
       </c>
       <c r="P277" t="n">
         <v>5900</v>
       </c>
       <c r="Q277" t="n">
-        <v>1557600</v>
+        <v>1522200</v>
       </c>
     </row>
     <row r="278">
@@ -13007,10 +13007,10 @@
         <v>169</v>
       </c>
       <c r="N289" t="n">
-        <v>1592.5646884576</v>
+        <v>1592.5646666667</v>
       </c>
       <c r="O289" t="n">
-        <v>269143.4323493344</v>
+        <v>269143.4286666723</v>
       </c>
       <c r="P289" t="n">
         <v>3900</v>
@@ -13807,10 +13807,10 @@
         <v>1</v>
       </c>
       <c r="N307" t="n">
-        <v>9677.770167910399</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O307" t="n">
-        <v>9677.770167910399</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="P307" t="n">
         <v>16900</v>
@@ -15149,10 +15149,10 @@
         <v>100</v>
       </c>
       <c r="N336" t="n">
-        <v>1630.9247235872</v>
+        <v>1630.9247279434</v>
       </c>
       <c r="O336" t="n">
-        <v>163092.47235872</v>
+        <v>163092.47279434</v>
       </c>
       <c r="P336" t="n">
         <v>2500</v>
@@ -15379,10 +15379,10 @@
         <v>266</v>
       </c>
       <c r="N341" t="n">
-        <v>2403.5218851304</v>
+        <v>2403.5220092133</v>
       </c>
       <c r="O341" t="n">
-        <v>639336.8214446864</v>
+        <v>639336.8544507378</v>
       </c>
       <c r="P341" t="n">
         <v>3500</v>
@@ -18288,22 +18288,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M407" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="N407" t="n">
         <v>2567</v>
       </c>
       <c r="O407" t="n">
-        <v>205360</v>
+        <v>174556</v>
       </c>
       <c r="P407" t="n">
         <v>4500</v>
       </c>
       <c r="Q407" t="n">
-        <v>360000</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="408">
@@ -19272,10 +19272,10 @@
         <v>42</v>
       </c>
       <c r="N430" t="n">
-        <v>6207.988218663</v>
+        <v>6207.9882181666</v>
       </c>
       <c r="O430" t="n">
-        <v>260735.505183846</v>
+        <v>260735.5051629972</v>
       </c>
       <c r="P430" t="n">
         <v>9900</v>
@@ -19877,10 +19877,10 @@
         <v>23</v>
       </c>
       <c r="N444" t="n">
-        <v>4814.2679247144</v>
+        <v>4814.2679243911</v>
       </c>
       <c r="O444" t="n">
-        <v>110728.1622684312</v>
+        <v>110728.1622609953</v>
       </c>
       <c r="P444" t="n">
         <v>9900</v>
@@ -20921,10 +20921,10 @@
         <v>88</v>
       </c>
       <c r="N468" t="n">
-        <v>1561.0061538462</v>
+        <v>1561.0062900506</v>
       </c>
       <c r="O468" t="n">
-        <v>137368.5415384656</v>
+        <v>137368.5535244528</v>
       </c>
       <c r="P468" t="n">
         <v>2900</v>
@@ -21626,10 +21626,10 @@
         <v>256</v>
       </c>
       <c r="N484" t="n">
-        <v>1200.9029345372</v>
+        <v>1200</v>
       </c>
       <c r="O484" t="n">
-        <v>307431.1512415232</v>
+        <v>307200</v>
       </c>
       <c r="P484" t="n">
         <v>1500</v>
@@ -25368,10 +25368,10 @@
         <v>37</v>
       </c>
       <c r="N566" t="n">
-        <v>5188.8571428571</v>
+        <v>5148</v>
       </c>
       <c r="O566" t="n">
-        <v>191987.7142857127</v>
+        <v>190476</v>
       </c>
       <c r="P566" t="n">
         <v>8600</v>
@@ -26901,10 +26901,10 @@
         <v>36</v>
       </c>
       <c r="N599" t="n">
-        <v>3957.6262600321</v>
+        <v>3938.66</v>
       </c>
       <c r="O599" t="n">
-        <v>142474.5453611556</v>
+        <v>141791.76</v>
       </c>
       <c r="P599" t="n">
         <v>4500</v>
@@ -27316,10 +27316,10 @@
         <v>23</v>
       </c>
       <c r="N608" t="n">
-        <v>10448.721014493</v>
+        <v>10411</v>
       </c>
       <c r="O608" t="n">
-        <v>240320.583333339</v>
+        <v>239453</v>
       </c>
       <c r="P608" t="n">
         <v>16900</v>
@@ -29433,10 +29433,10 @@
         <v>145</v>
       </c>
       <c r="N654" t="n">
-        <v>2636.2357798165</v>
+        <v>2629</v>
       </c>
       <c r="O654" t="n">
-        <v>382254.1880733925</v>
+        <v>381205</v>
       </c>
       <c r="P654" t="n">
         <v>4500</v>
@@ -29709,10 +29709,10 @@
         <v>37</v>
       </c>
       <c r="N660" t="n">
-        <v>6650.5777839955</v>
+        <v>6645</v>
       </c>
       <c r="O660" t="n">
-        <v>246071.3780078335</v>
+        <v>245865</v>
       </c>
       <c r="P660" t="n">
         <v>10900</v>
@@ -31555,10 +31555,10 @@
         <v>4</v>
       </c>
       <c r="N700" t="n">
-        <v>10795.831156812</v>
+        <v>10713.21</v>
       </c>
       <c r="O700" t="n">
-        <v>43183.324627248</v>
+        <v>42852.84</v>
       </c>
       <c r="P700" t="n">
         <v>20900</v>
@@ -32107,10 +32107,10 @@
         <v>29</v>
       </c>
       <c r="N712" t="n">
-        <v>1516.0387131507</v>
+        <v>1516.0387126124</v>
       </c>
       <c r="O712" t="n">
-        <v>43965.1226813703</v>
+        <v>43965.12266575961</v>
       </c>
       <c r="P712" t="n">
         <v>2300</v>
@@ -32982,10 +32982,10 @@
         <v>48</v>
       </c>
       <c r="N731" t="n">
-        <v>1592.2864981273</v>
+        <v>1592.2866856061</v>
       </c>
       <c r="O731" t="n">
-        <v>76429.75191011041</v>
+        <v>76429.7609090928</v>
       </c>
       <c r="P731" t="n">
         <v>2500</v>
@@ -33251,10 +33251,10 @@
         <v>121</v>
       </c>
       <c r="N737" t="n">
-        <v>2072.7973006135</v>
+        <v>2060.1582208589</v>
       </c>
       <c r="O737" t="n">
-        <v>250808.4733742335</v>
+        <v>249279.1447239269</v>
       </c>
       <c r="P737" t="n">
         <v>2900</v>
@@ -33297,10 +33297,10 @@
         <v>37</v>
       </c>
       <c r="N738" t="n">
-        <v>1693.5530348259</v>
+        <v>1668.6492929293</v>
       </c>
       <c r="O738" t="n">
-        <v>62661.4622885583</v>
+        <v>61740.0238383841</v>
       </c>
       <c r="P738" t="n">
         <v>2500</v>
@@ -33612,10 +33612,10 @@
         <v>247</v>
       </c>
       <c r="N745" t="n">
-        <v>692.15249234096</v>
+        <v>692.15249774246</v>
       </c>
       <c r="O745" t="n">
-        <v>170961.6656082171</v>
+        <v>170961.6669423876</v>
       </c>
       <c r="P745" t="n">
         <v>1200</v>
@@ -33705,10 +33705,10 @@
         <v>4</v>
       </c>
       <c r="N747" t="n">
-        <v>19051.333333333</v>
+        <v>18491</v>
       </c>
       <c r="O747" t="n">
-        <v>76205.333333332</v>
+        <v>73964</v>
       </c>
       <c r="P747" t="n">
         <v>13500</v>
@@ -36039,10 +36039,10 @@
         <v>145</v>
       </c>
       <c r="N797" t="n">
-        <v>631.09868421053</v>
+        <v>628</v>
       </c>
       <c r="O797" t="n">
-        <v>91509.30921052684</v>
+        <v>91060</v>
       </c>
       <c r="P797" t="n">
         <v>1400</v>
@@ -37476,10 +37476,10 @@
         <v>55</v>
       </c>
       <c r="N828" t="n">
-        <v>1333.9879518072</v>
+        <v>1326</v>
       </c>
       <c r="O828" t="n">
-        <v>73369.337349396</v>
+        <v>72930</v>
       </c>
       <c r="P828" t="n">
         <v>2900</v>
@@ -37750,10 +37750,10 @@
         <v>809</v>
       </c>
       <c r="N834" t="n">
-        <v>517.29622957051</v>
+        <v>517.29632575033</v>
       </c>
       <c r="O834" t="n">
-        <v>418492.6497225426</v>
+        <v>418492.7275320169</v>
       </c>
       <c r="P834" t="n">
         <v>900</v>
@@ -38677,10 +38677,10 @@
         <v>1191</v>
       </c>
       <c r="N854" t="n">
-        <v>703.79465893216</v>
+        <v>703.79465786602</v>
       </c>
       <c r="O854" t="n">
-        <v>838219.4387882026</v>
+        <v>838219.4375184298</v>
       </c>
       <c r="P854" t="n">
         <v>900</v>
@@ -39740,10 +39740,10 @@
         <v>33</v>
       </c>
       <c r="N877" t="n">
-        <v>1595.4982940252</v>
+        <v>1595.4982440945</v>
       </c>
       <c r="O877" t="n">
-        <v>52651.4437028316</v>
+        <v>52651.4420551185</v>
       </c>
       <c r="P877" t="n">
         <v>2500</v>
@@ -41472,10 +41472,10 @@
         <v>13</v>
       </c>
       <c r="N913" t="n">
-        <v>14670.891428571</v>
+        <v>12837.03</v>
       </c>
       <c r="O913" t="n">
-        <v>190721.588571423</v>
+        <v>166881.39</v>
       </c>
       <c r="P913" t="n">
         <v>15500</v>
@@ -42394,10 +42394,10 @@
         <v>25</v>
       </c>
       <c r="N932" t="n">
-        <v>7190.9555769231</v>
+        <v>6989.34</v>
       </c>
       <c r="O932" t="n">
-        <v>179773.8894230775</v>
+        <v>174733.5</v>
       </c>
       <c r="P932" t="n">
         <v>10900</v>
@@ -42775,10 +42775,10 @@
         <v>17</v>
       </c>
       <c r="N940" t="n">
-        <v>4592.3142857143</v>
+        <v>4286.16</v>
       </c>
       <c r="O940" t="n">
-        <v>78069.3428571431</v>
+        <v>72864.72</v>
       </c>
       <c r="P940" t="n">
         <v>8900</v>
@@ -42865,10 +42865,10 @@
         <v>12</v>
       </c>
       <c r="N942" t="n">
-        <v>3099.0394791667</v>
+        <v>3067.090625</v>
       </c>
       <c r="O942" t="n">
-        <v>37188.4737500004</v>
+        <v>36805.08749999999</v>
       </c>
       <c r="P942" t="n">
         <v>7200</v>
@@ -43107,10 +43107,10 @@
         <v>32</v>
       </c>
       <c r="N947" t="n">
-        <v>4234.8833684211</v>
+        <v>4190.77</v>
       </c>
       <c r="O947" t="n">
-        <v>135516.2677894752</v>
+        <v>134104.64</v>
       </c>
       <c r="P947" t="n">
         <v>5900</v>
@@ -45731,10 +45731,10 @@
         <v>13</v>
       </c>
       <c r="N1002" t="n">
-        <v>1517.945625</v>
+        <v>1278.27</v>
       </c>
       <c r="O1002" t="n">
-        <v>19733.293125</v>
+        <v>16617.51</v>
       </c>
       <c r="P1002" t="n">
         <v>5900</v>
@@ -46694,10 +46694,10 @@
         <v>3</v>
       </c>
       <c r="N1022" t="n">
-        <v>3822</v>
+        <v>1911</v>
       </c>
       <c r="O1022" t="n">
-        <v>11466</v>
+        <v>5733</v>
       </c>
       <c r="P1022" t="n">
         <v>4500</v>
@@ -46936,10 +46936,10 @@
         <v>65</v>
       </c>
       <c r="N1027" t="n">
-        <v>548.38743842365</v>
+        <v>540.40123152709</v>
       </c>
       <c r="O1027" t="n">
-        <v>35645.18349753725</v>
+        <v>35126.08004926085</v>
       </c>
       <c r="P1027" t="n">
         <v>2500</v>
@@ -47957,22 +47957,22 @@
         <v>0</v>
       </c>
       <c r="L1050" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1050" t="n">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="N1050" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1050" t="n">
-        <v>611816.4</v>
+        <v>583578.72</v>
       </c>
       <c r="P1050" t="n">
         <v>1900</v>
       </c>
       <c r="Q1050" t="n">
-        <v>988000</v>
+        <v>942400</v>
       </c>
     </row>
     <row r="1051">
@@ -48694,10 +48694,10 @@
         <v>49</v>
       </c>
       <c r="N1066" t="n">
-        <v>1757.3206341463</v>
+        <v>1757.3206356968</v>
       </c>
       <c r="O1066" t="n">
-        <v>86108.7110731687</v>
+        <v>86108.7111491432</v>
       </c>
       <c r="P1066" t="n">
         <v>2000</v>
@@ -51322,10 +51322,10 @@
         <v>104</v>
       </c>
       <c r="N1123" t="n">
-        <v>1949.5384615385</v>
+        <v>1584</v>
       </c>
       <c r="O1123" t="n">
-        <v>202752.000000004</v>
+        <v>164736</v>
       </c>
       <c r="P1123" t="n">
         <v>2000</v>
@@ -53879,10 +53879,10 @@
         <v>21</v>
       </c>
       <c r="N1178" t="n">
-        <v>1333.5477419355</v>
+        <v>1319.3610452962</v>
       </c>
       <c r="O1178" t="n">
-        <v>28004.5025806455</v>
+        <v>27706.5819512202</v>
       </c>
       <c r="P1178" t="n">
         <v>3500</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -11238,13 +11238,13 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M250" t="n">
         <v>17</v>
@@ -28464,13 +28464,13 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
       </c>
       <c r="L633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M633" t="n">
         <v>14</v>
@@ -30777,10 +30777,10 @@
         <v>53</v>
       </c>
       <c r="N683" t="n">
-        <v>10755</v>
+        <v>10795.738636364</v>
       </c>
       <c r="O683" t="n">
-        <v>570015</v>
+        <v>572174.147727292</v>
       </c>
       <c r="P683" t="n">
         <v>17900</v>
@@ -32327,13 +32327,13 @@
         </is>
       </c>
       <c r="J717" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K717" t="n">
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M717" t="n">
         <v>136</v>
@@ -38577,22 +38577,22 @@
         </is>
       </c>
       <c r="J852" t="n">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="K852" t="n">
         <v>0</v>
       </c>
       <c r="L852" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M852" t="n">
         <v>1164</v>
       </c>
       <c r="N852" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O852" t="n">
-        <v>819216.9578326928</v>
+        <v>819216.9558307759</v>
       </c>
       <c r="P852" t="n">
         <v>900</v>
@@ -54685,10 +54685,10 @@
         <v>27</v>
       </c>
       <c r="N1195" t="n">
-        <v>4171.6683165468</v>
+        <v>4171.668314121</v>
       </c>
       <c r="O1195" t="n">
-        <v>112635.0445467636</v>
+        <v>112635.044481267</v>
       </c>
       <c r="P1195" t="n">
         <v>5000</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9969,22 +9969,22 @@
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M222" t="n">
-        <v>1582</v>
+        <v>1522</v>
       </c>
       <c r="N222" t="n">
         <v>156.25</v>
       </c>
       <c r="O222" t="n">
-        <v>247187.5</v>
+        <v>237812.5</v>
       </c>
       <c r="P222" t="n">
         <v>250</v>
       </c>
       <c r="Q222" t="n">
-        <v>395500</v>
+        <v>380500</v>
       </c>
     </row>
     <row r="223">
@@ -20167,10 +20167,10 @@
         <v>0</v>
       </c>
       <c r="L451" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M451" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N451" t="n">
         <v>0</v>
@@ -20182,7 +20182,7 @@
         <v>29900</v>
       </c>
       <c r="Q451" t="n">
-        <v>209300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -37063,22 +37063,22 @@
         <v>0</v>
       </c>
       <c r="L819" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M819" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="N819" t="n">
         <v>1283.6512980769</v>
       </c>
       <c r="O819" t="n">
-        <v>33374.9337499994</v>
+        <v>10269.2103846152</v>
       </c>
       <c r="P819" t="n">
         <v>1900</v>
       </c>
       <c r="Q819" t="n">
-        <v>49400</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="820">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -550,22 +550,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>405000</v>
+        <v>270000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
       </c>
       <c r="Q4" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="5">
@@ -1337,10 +1337,10 @@
         <v>16</v>
       </c>
       <c r="N23" t="n">
-        <v>15238.01</v>
+        <v>15304.843377193</v>
       </c>
       <c r="O23" t="n">
-        <v>243808.16</v>
+        <v>244877.494035088</v>
       </c>
       <c r="P23" t="n">
         <v>40400</v>
@@ -2339,10 +2339,10 @@
         <v>34</v>
       </c>
       <c r="N48" t="n">
-        <v>21333.69</v>
+        <v>21425.250901288</v>
       </c>
       <c r="O48" t="n">
-        <v>725345.46</v>
+        <v>728458.530643792</v>
       </c>
       <c r="P48" t="n">
         <v>30000</v>
@@ -4698,10 +4698,10 @@
         <v>8</v>
       </c>
       <c r="N102" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="O102" t="n">
-        <v>216000</v>
+        <v>228000</v>
       </c>
       <c r="P102" t="n">
         <v>20000</v>
@@ -8400,10 +8400,10 @@
         <v>6</v>
       </c>
       <c r="N187" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="O187" t="n">
-        <v>81560.10000000001</v>
+        <v>82164.99567367201</v>
       </c>
       <c r="P187" t="n">
         <v>25500</v>
@@ -8963,22 +8963,22 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M200" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="N200" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O200" t="n">
-        <v>126530.4807490017</v>
+        <v>82632.1499252928</v>
       </c>
       <c r="P200" t="n">
         <v>4500</v>
       </c>
       <c r="Q200" t="n">
-        <v>220500</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="201">
@@ -9644,22 +9644,22 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M215" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N215" t="n">
         <v>8214</v>
       </c>
       <c r="O215" t="n">
-        <v>689976</v>
+        <v>673548</v>
       </c>
       <c r="P215" t="n">
         <v>7900</v>
       </c>
       <c r="Q215" t="n">
-        <v>663600</v>
+        <v>647800</v>
       </c>
     </row>
     <row r="216">
@@ -10474,10 +10474,10 @@
         <v>5</v>
       </c>
       <c r="N233" t="n">
-        <v>4890.9300565371</v>
+        <v>4890.9300570207</v>
       </c>
       <c r="O233" t="n">
-        <v>24454.6502826855</v>
+        <v>24454.6502851035</v>
       </c>
       <c r="P233" t="n">
         <v>8900</v>
@@ -10929,22 +10929,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M243" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N243" t="n">
         <v>5667.94</v>
       </c>
       <c r="O243" t="n">
-        <v>51011.46</v>
+        <v>45343.52</v>
       </c>
       <c r="P243" t="n">
         <v>9500</v>
       </c>
       <c r="Q243" t="n">
-        <v>85500</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="244">
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N246" t="n">
         <v>8662</v>
       </c>
       <c r="O246" t="n">
-        <v>138592</v>
+        <v>129930</v>
       </c>
       <c r="P246" t="n">
         <v>14200</v>
       </c>
       <c r="Q246" t="n">
-        <v>227200</v>
+        <v>213000</v>
       </c>
     </row>
     <row r="247">
@@ -11554,22 +11554,22 @@
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M257" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N257" t="n">
         <v>8154</v>
       </c>
       <c r="O257" t="n">
-        <v>114156</v>
+        <v>106002</v>
       </c>
       <c r="P257" t="n">
         <v>13500</v>
       </c>
       <c r="Q257" t="n">
-        <v>189000</v>
+        <v>175500</v>
       </c>
     </row>
     <row r="258">
@@ -11600,22 +11600,22 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M258" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N258" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O258" t="n">
-        <v>59289.515256332</v>
+        <v>44494.61922126</v>
       </c>
       <c r="P258" t="n">
         <v>24900</v>
       </c>
       <c r="Q258" t="n">
-        <v>99600</v>
+        <v>74700</v>
       </c>
     </row>
     <row r="259">
@@ -12190,10 +12190,10 @@
         <v>9</v>
       </c>
       <c r="N271" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O271" t="n">
-        <v>111802.16708352</v>
+        <v>111802.167119466</v>
       </c>
       <c r="P271" t="n">
         <v>19900</v>
@@ -12415,22 +12415,22 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M276" t="n">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="N276" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O276" t="n">
-        <v>437506.825581126</v>
+        <v>333338.535091056</v>
       </c>
       <c r="P276" t="n">
         <v>5900</v>
       </c>
       <c r="Q276" t="n">
-        <v>743400</v>
+        <v>566400</v>
       </c>
     </row>
     <row r="277">
@@ -12818,22 +12818,22 @@
         <v>0</v>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N285" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O285" t="n">
-        <v>74309.9405442283</v>
+        <v>69938.76757867679</v>
       </c>
       <c r="P285" t="n">
         <v>8900</v>
       </c>
       <c r="Q285" t="n">
-        <v>151300</v>
+        <v>142400</v>
       </c>
     </row>
     <row r="286">
@@ -13128,22 +13128,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M292" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N292" t="n">
         <v>4717</v>
       </c>
       <c r="O292" t="n">
-        <v>457549</v>
+        <v>400945</v>
       </c>
       <c r="P292" t="n">
         <v>7900</v>
       </c>
       <c r="Q292" t="n">
-        <v>766300</v>
+        <v>671500</v>
       </c>
     </row>
     <row r="293">
@@ -13354,22 +13354,22 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M297" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N297" t="n">
         <v>4648.6</v>
       </c>
       <c r="O297" t="n">
-        <v>1120312.6</v>
+        <v>1111015.4</v>
       </c>
       <c r="P297" t="n">
         <v>8900</v>
       </c>
       <c r="Q297" t="n">
-        <v>2144900</v>
+        <v>2127100</v>
       </c>
     </row>
     <row r="298">
@@ -13942,22 +13942,22 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M310" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N310" t="n">
-        <v>4635.49</v>
+        <v>4680.6408766234</v>
       </c>
       <c r="O310" t="n">
-        <v>162242.15</v>
+        <v>149780.5080519488</v>
       </c>
       <c r="P310" t="n">
         <v>7500</v>
       </c>
       <c r="Q310" t="n">
-        <v>262500</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="311">
@@ -15047,22 +15047,22 @@
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M334" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N334" t="n">
-        <v>1630.9251335113</v>
+        <v>1633.1055147059</v>
       </c>
       <c r="O334" t="n">
-        <v>399576.6577102685</v>
+        <v>393578.4290441219</v>
       </c>
       <c r="P334" t="n">
         <v>2500</v>
       </c>
       <c r="Q334" t="n">
-        <v>612500</v>
+        <v>602500</v>
       </c>
     </row>
     <row r="335">
@@ -15185,22 +15185,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M337" t="n">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N337" t="n">
-        <v>1550.1949625568</v>
+        <v>1550.1949638844</v>
       </c>
       <c r="O337" t="n">
-        <v>796800.2107541952</v>
+        <v>793699.8215088128</v>
       </c>
       <c r="P337" t="n">
         <v>2500</v>
       </c>
       <c r="Q337" t="n">
-        <v>1285000</v>
+        <v>1280000</v>
       </c>
     </row>
     <row r="338">
@@ -15277,22 +15277,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M339" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N339" t="n">
-        <v>2403.523063498</v>
+        <v>2404.4159026746</v>
       </c>
       <c r="O339" t="n">
-        <v>581652.581366516</v>
+        <v>579464.2325445786</v>
       </c>
       <c r="P339" t="n">
         <v>3500</v>
       </c>
       <c r="Q339" t="n">
-        <v>847000</v>
+        <v>843500</v>
       </c>
     </row>
     <row r="340">
@@ -16791,22 +16791,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N373" t="n">
-        <v>28384.62</v>
+        <v>0</v>
       </c>
       <c r="O373" t="n">
-        <v>28384.62</v>
+        <v>0</v>
       </c>
       <c r="P373" t="n">
         <v>36900</v>
       </c>
       <c r="Q373" t="n">
-        <v>36900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -16840,22 +16840,22 @@
         <v>0</v>
       </c>
       <c r="L374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N374" t="n">
         <v>19120</v>
       </c>
       <c r="O374" t="n">
-        <v>478000</v>
+        <v>458880</v>
       </c>
       <c r="P374" t="n">
         <v>23900</v>
       </c>
       <c r="Q374" t="n">
-        <v>597500</v>
+        <v>573600</v>
       </c>
     </row>
     <row r="375">
@@ -16971,22 +16971,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N377" t="n">
-        <v>18071.26</v>
+        <v>18238.586481481</v>
       </c>
       <c r="O377" t="n">
-        <v>18071.26</v>
+        <v>0</v>
       </c>
       <c r="P377" t="n">
         <v>23900</v>
       </c>
       <c r="Q377" t="n">
-        <v>23900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -19775,22 +19775,22 @@
         <v>0</v>
       </c>
       <c r="L442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M442" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N442" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O442" t="n">
-        <v>168499.217229616</v>
+        <v>158870.6904577221</v>
       </c>
       <c r="P442" t="n">
         <v>7900</v>
       </c>
       <c r="Q442" t="n">
-        <v>276500</v>
+        <v>260700</v>
       </c>
     </row>
     <row r="443">
@@ -19908,22 +19908,22 @@
         <v>0</v>
       </c>
       <c r="L445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N445" t="n">
-        <v>13513.644019608</v>
+        <v>13513.644059406</v>
       </c>
       <c r="O445" t="n">
-        <v>135136.44019608</v>
+        <v>121622.796534654</v>
       </c>
       <c r="P445" t="n">
         <v>21900</v>
       </c>
       <c r="Q445" t="n">
-        <v>219000</v>
+        <v>197100</v>
       </c>
     </row>
     <row r="446">
@@ -20118,22 +20118,22 @@
         <v>0</v>
       </c>
       <c r="L450" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M450" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N450" t="n">
-        <v>15700</v>
+        <v>0</v>
       </c>
       <c r="O450" t="n">
-        <v>109900</v>
+        <v>0</v>
       </c>
       <c r="P450" t="n">
         <v>29900</v>
       </c>
       <c r="Q450" t="n">
-        <v>209300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -20471,22 +20471,22 @@
         <v>0</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M458" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N458" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O458" t="n">
-        <v>162742.587526428</v>
+        <v>135618.822881355</v>
       </c>
       <c r="P458" t="n">
         <v>44500</v>
       </c>
       <c r="Q458" t="n">
-        <v>267000</v>
+        <v>222500</v>
       </c>
     </row>
     <row r="459">
@@ -20599,22 +20599,22 @@
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M461" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N461" t="n">
         <v>16974.69</v>
       </c>
       <c r="O461" t="n">
-        <v>254620.35</v>
+        <v>203696.28</v>
       </c>
       <c r="P461" t="n">
         <v>26900</v>
       </c>
       <c r="Q461" t="n">
-        <v>403500</v>
+        <v>322800</v>
       </c>
     </row>
     <row r="462">
@@ -20640,22 +20640,22 @@
         <v>0</v>
       </c>
       <c r="L462" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M462" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N462" t="n">
         <v>4100.45</v>
       </c>
       <c r="O462" t="n">
-        <v>49205.39999999999</v>
+        <v>41004.5</v>
       </c>
       <c r="P462" t="n">
         <v>26900</v>
       </c>
       <c r="Q462" t="n">
-        <v>322800</v>
+        <v>269000</v>
       </c>
     </row>
     <row r="463">
@@ -21347,22 +21347,22 @@
         <v>0</v>
       </c>
       <c r="L478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N478" t="n">
-        <v>8968.24</v>
+        <v>9120.244067796601</v>
       </c>
       <c r="O478" t="n">
-        <v>8968.24</v>
+        <v>0</v>
       </c>
       <c r="P478" t="n">
         <v>18600</v>
       </c>
       <c r="Q478" t="n">
-        <v>18600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479">
@@ -21475,22 +21475,22 @@
         <v>0</v>
       </c>
       <c r="L481" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M481" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N481" t="n">
         <v>9627.34</v>
       </c>
       <c r="O481" t="n">
-        <v>221428.82</v>
+        <v>211801.48</v>
       </c>
       <c r="P481" t="n">
         <v>15900</v>
       </c>
       <c r="Q481" t="n">
-        <v>365700</v>
+        <v>349800</v>
       </c>
     </row>
     <row r="482">
@@ -22007,22 +22007,22 @@
         <v>0</v>
       </c>
       <c r="L493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M493" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N493" t="n">
-        <v>12981.59</v>
+        <v>13033.935120968</v>
       </c>
       <c r="O493" t="n">
-        <v>467337.24</v>
+        <v>456187.72923388</v>
       </c>
       <c r="P493" t="n">
         <v>21900</v>
       </c>
       <c r="Q493" t="n">
-        <v>788400</v>
+        <v>766500</v>
       </c>
     </row>
     <row r="494">
@@ -24251,22 +24251,22 @@
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M542" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N542" t="n">
-        <v>9188.98</v>
+        <v>9254.3819928826</v>
       </c>
       <c r="O542" t="n">
-        <v>358370.22</v>
+        <v>342412.1337366562</v>
       </c>
       <c r="P542" t="n">
         <v>12900</v>
       </c>
       <c r="Q542" t="n">
-        <v>503100</v>
+        <v>477300</v>
       </c>
     </row>
     <row r="543">
@@ -25134,10 +25134,10 @@
         <v>23</v>
       </c>
       <c r="N561" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O561" t="n">
-        <v>587282</v>
+        <v>588287.046206496</v>
       </c>
       <c r="P561" t="n">
         <v>40900</v>
@@ -26008,22 +26008,22 @@
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M580" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N580" t="n">
-        <v>2260</v>
+        <v>2280.7339449541</v>
       </c>
       <c r="O580" t="n">
-        <v>22600</v>
+        <v>18245.8715596328</v>
       </c>
       <c r="P580" t="n">
         <v>3800</v>
       </c>
       <c r="Q580" t="n">
-        <v>38000</v>
+        <v>30400</v>
       </c>
     </row>
     <row r="581">
@@ -26618,22 +26618,22 @@
         <v>0</v>
       </c>
       <c r="L593" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M593" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N593" t="n">
-        <v>11857</v>
+        <v>12039.415384615</v>
       </c>
       <c r="O593" t="n">
-        <v>331996</v>
+        <v>325064.215384605</v>
       </c>
       <c r="P593" t="n">
         <v>19900</v>
       </c>
       <c r="Q593" t="n">
-        <v>557200</v>
+        <v>537300</v>
       </c>
     </row>
     <row r="594">
@@ -27125,22 +27125,22 @@
         <v>0</v>
       </c>
       <c r="L604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M604" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N604" t="n">
-        <v>10411</v>
+        <v>10448.858181818</v>
       </c>
       <c r="O604" t="n">
-        <v>301919</v>
+        <v>292568.029090904</v>
       </c>
       <c r="P604" t="n">
         <v>16900</v>
       </c>
       <c r="Q604" t="n">
-        <v>490100</v>
+        <v>473200</v>
       </c>
     </row>
     <row r="605">
@@ -28189,22 +28189,22 @@
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M627" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N627" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O627" t="n">
-        <v>108036</v>
+        <v>99199.7222222226</v>
       </c>
       <c r="P627" t="n">
         <v>14900</v>
       </c>
       <c r="Q627" t="n">
-        <v>178800</v>
+        <v>163900</v>
       </c>
     </row>
     <row r="628">
@@ -29472,22 +29472,22 @@
         <v>0</v>
       </c>
       <c r="L655" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M655" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N655" t="n">
         <v>6645</v>
       </c>
       <c r="O655" t="n">
-        <v>219285</v>
+        <v>205995</v>
       </c>
       <c r="P655" t="n">
         <v>10900</v>
       </c>
       <c r="Q655" t="n">
-        <v>359700</v>
+        <v>337900</v>
       </c>
     </row>
     <row r="656">
@@ -30119,22 +30119,22 @@
         <v>0</v>
       </c>
       <c r="L669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M669" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N669" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O669" t="n">
-        <v>809640</v>
+        <v>792682.833986912</v>
       </c>
       <c r="P669" t="n">
         <v>28900</v>
       </c>
       <c r="Q669" t="n">
-        <v>1300500</v>
+        <v>1271600</v>
       </c>
     </row>
     <row r="670">
@@ -31180,22 +31180,22 @@
         <v>0</v>
       </c>
       <c r="L692" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M692" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N692" t="n">
-        <v>8700</v>
+        <v>8711.0687022901</v>
       </c>
       <c r="O692" t="n">
-        <v>269700</v>
+        <v>261332.061068703</v>
       </c>
       <c r="P692" t="n">
         <v>14900</v>
       </c>
       <c r="Q692" t="n">
-        <v>461900</v>
+        <v>447000</v>
       </c>
     </row>
     <row r="693">
@@ -31640,22 +31640,22 @@
         <v>0</v>
       </c>
       <c r="L702" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M702" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N702" t="n">
-        <v>15472</v>
+        <v>15516.07977208</v>
       </c>
       <c r="O702" t="n">
-        <v>123776</v>
+        <v>108612.55840456</v>
       </c>
       <c r="P702" t="n">
         <v>25900</v>
       </c>
       <c r="Q702" t="n">
-        <v>207200</v>
+        <v>181300</v>
       </c>
     </row>
     <row r="703">
@@ -31922,10 +31922,10 @@
         <v>144</v>
       </c>
       <c r="N708" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O708" t="n">
-        <v>218309.572419048</v>
+        <v>218309.5723991904</v>
       </c>
       <c r="P708" t="n">
         <v>2300</v>
@@ -32098,22 +32098,22 @@
         <v>0</v>
       </c>
       <c r="L712" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M712" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N712" t="n">
-        <v>1907.3922142857</v>
+        <v>1909.6656257449</v>
       </c>
       <c r="O712" t="n">
-        <v>232701.8501428554</v>
+        <v>231069.5407151329</v>
       </c>
       <c r="P712" t="n">
         <v>2500</v>
       </c>
       <c r="Q712" t="n">
-        <v>305000</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="713">
@@ -32236,22 +32236,22 @@
         <v>0</v>
       </c>
       <c r="L715" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M715" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N715" t="n">
-        <v>1803.0176696833</v>
+        <v>1803.0176731553</v>
       </c>
       <c r="O715" t="n">
-        <v>200134.9613348463</v>
+        <v>198331.944047083</v>
       </c>
       <c r="P715" t="n">
         <v>2500</v>
       </c>
       <c r="Q715" t="n">
-        <v>277500</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="716">
@@ -32282,22 +32282,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M716" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N716" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942492013</v>
       </c>
       <c r="O716" t="n">
-        <v>532361.6770700599</v>
+        <v>529055.0798722079</v>
       </c>
       <c r="P716" t="n">
         <v>4900</v>
       </c>
       <c r="Q716" t="n">
-        <v>788900</v>
+        <v>784000</v>
       </c>
     </row>
     <row r="717">
@@ -32791,22 +32791,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M727" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N727" t="n">
-        <v>1592.2892358079</v>
+        <v>1595.7734573304</v>
       </c>
       <c r="O727" t="n">
-        <v>50953.2555458528</v>
+        <v>49468.97717724241</v>
       </c>
       <c r="P727" t="n">
         <v>2500</v>
       </c>
       <c r="Q727" t="n">
-        <v>80000</v>
+        <v>77500</v>
       </c>
     </row>
     <row r="728">
@@ -33204,10 +33204,10 @@
         <v>508</v>
       </c>
       <c r="N736" t="n">
-        <v>1259.2751809084</v>
+        <v>1259.2751822382</v>
       </c>
       <c r="O736" t="n">
-        <v>639711.7919014673</v>
+        <v>639711.7925770056</v>
       </c>
       <c r="P736" t="n">
         <v>1900</v>
@@ -33750,22 +33750,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M748" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N748" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O748" t="n">
-        <v>162216</v>
+        <v>148739.524155266</v>
       </c>
       <c r="P748" t="n">
         <v>21900</v>
       </c>
       <c r="Q748" t="n">
-        <v>262800</v>
+        <v>240900</v>
       </c>
     </row>
     <row r="749">
@@ -33897,22 +33897,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M751" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N751" t="n">
         <v>5215</v>
       </c>
       <c r="O751" t="n">
-        <v>172095</v>
+        <v>161665</v>
       </c>
       <c r="P751" t="n">
         <v>8900</v>
       </c>
       <c r="Q751" t="n">
-        <v>293700</v>
+        <v>275900</v>
       </c>
     </row>
     <row r="752">
@@ -34129,22 +34129,22 @@
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M756" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N756" t="n">
-        <v>15423.36</v>
+        <v>15547.741935484</v>
       </c>
       <c r="O756" t="n">
-        <v>123386.88</v>
+        <v>108834.193548388</v>
       </c>
       <c r="P756" t="n">
         <v>24900</v>
       </c>
       <c r="Q756" t="n">
-        <v>199200</v>
+        <v>174300</v>
       </c>
     </row>
     <row r="757">
@@ -38446,10 +38446,10 @@
         <v>1227</v>
       </c>
       <c r="N849" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O849" t="n">
-        <v>863555.955632717</v>
+        <v>863555.9534809516</v>
       </c>
       <c r="P849" t="n">
         <v>900</v>
@@ -39091,22 +39091,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M863" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N863" t="n">
         <v>2529.19</v>
       </c>
       <c r="O863" t="n">
-        <v>197276.82</v>
+        <v>187160.06</v>
       </c>
       <c r="P863" t="n">
         <v>5100</v>
       </c>
       <c r="Q863" t="n">
-        <v>397800</v>
+        <v>377400</v>
       </c>
     </row>
     <row r="864">
@@ -40143,10 +40143,10 @@
         <v>15</v>
       </c>
       <c r="N885" t="n">
-        <v>9694.41</v>
+        <v>12723.913125</v>
       </c>
       <c r="O885" t="n">
-        <v>145416.15</v>
+        <v>190858.696875</v>
       </c>
       <c r="P885" t="n">
         <v>32500</v>
@@ -41771,22 +41771,22 @@
         <v>0</v>
       </c>
       <c r="L919" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M919" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N919" t="n">
-        <v>7653.955</v>
+        <v>8747.3771428571</v>
       </c>
       <c r="O919" t="n">
-        <v>22961.865</v>
+        <v>17494.7542857142</v>
       </c>
       <c r="P919" t="n">
         <v>11900</v>
       </c>
       <c r="Q919" t="n">
-        <v>35700</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="920">
@@ -42350,22 +42350,22 @@
         <v>0</v>
       </c>
       <c r="L931" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M931" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N931" t="n">
-        <v>4568.55</v>
+        <v>4627.1211538462</v>
       </c>
       <c r="O931" t="n">
-        <v>114213.75</v>
+        <v>111050.9076923088</v>
       </c>
       <c r="P931" t="n">
         <v>6900</v>
       </c>
       <c r="Q931" t="n">
-        <v>172500</v>
+        <v>165600</v>
       </c>
     </row>
     <row r="932">
@@ -42489,22 +42489,22 @@
         <v>0</v>
       </c>
       <c r="L934" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M934" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N934" t="n">
-        <v>19632.66</v>
+        <v>19743.578983051</v>
       </c>
       <c r="O934" t="n">
-        <v>3043062.3</v>
+        <v>3040511.163389854</v>
       </c>
       <c r="P934" t="n">
         <v>2800</v>
       </c>
       <c r="Q934" t="n">
-        <v>434000</v>
+        <v>431200</v>
       </c>
     </row>
     <row r="935">
@@ -43646,22 +43646,22 @@
         <v>0</v>
       </c>
       <c r="L958" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M958" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N958" t="n">
-        <v>22042.26</v>
+        <v>23737.818461538</v>
       </c>
       <c r="O958" t="n">
-        <v>220422.6</v>
+        <v>213640.366153842</v>
       </c>
       <c r="P958" t="n">
         <v>56000</v>
       </c>
       <c r="Q958" t="n">
-        <v>560000</v>
+        <v>504000</v>
       </c>
     </row>
     <row r="959">
@@ -44027,22 +44027,22 @@
         <v>0</v>
       </c>
       <c r="L966" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M966" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N966" t="n">
-        <v>10737.525135135</v>
+        <v>10737.525</v>
       </c>
       <c r="O966" t="n">
-        <v>257700.60324324</v>
+        <v>246963.075</v>
       </c>
       <c r="P966" t="n">
         <v>18900</v>
       </c>
       <c r="Q966" t="n">
-        <v>453600</v>
+        <v>434700</v>
       </c>
     </row>
     <row r="967">
@@ -44264,22 +44264,22 @@
         <v>0</v>
       </c>
       <c r="L971" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M971" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N971" t="n">
-        <v>7258.5</v>
+        <v>7742.4</v>
       </c>
       <c r="O971" t="n">
-        <v>101619</v>
+        <v>100651.2</v>
       </c>
       <c r="P971" t="n">
         <v>17500</v>
       </c>
       <c r="Q971" t="n">
-        <v>245000</v>
+        <v>227500</v>
       </c>
     </row>
     <row r="972">
@@ -45209,22 +45209,22 @@
         <v>0</v>
       </c>
       <c r="L991" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M991" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N991" t="n">
-        <v>2000.7487209302</v>
+        <v>2000.7532142857</v>
       </c>
       <c r="O991" t="n">
-        <v>166062.1438372066</v>
+        <v>162061.0103571417</v>
       </c>
       <c r="P991" t="n">
         <v>2000</v>
       </c>
       <c r="Q991" t="n">
-        <v>166000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="992">
@@ -45344,13 +45344,13 @@
         <v>4</v>
       </c>
       <c r="K994" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L994" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M994" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N994" t="n">
         <v>0</v>
@@ -45359,10 +45359,10 @@
         <v>0</v>
       </c>
       <c r="P994" t="n">
-        <v>92500</v>
+        <v>25000</v>
       </c>
       <c r="Q994" t="n">
-        <v>370000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="995">
@@ -47338,22 +47338,22 @@
         <v>0</v>
       </c>
       <c r="L1036" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1036" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N1036" t="n">
         <v>110520.77</v>
       </c>
       <c r="O1036" t="n">
-        <v>1105207.7</v>
+        <v>221041.54</v>
       </c>
       <c r="P1036" t="n">
         <v>176900</v>
       </c>
       <c r="Q1036" t="n">
-        <v>1769000</v>
+        <v>353800</v>
       </c>
     </row>
     <row r="1037">
@@ -48268,22 +48268,22 @@
         <v>0</v>
       </c>
       <c r="L1057" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M1057" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N1057" t="n">
-        <v>22951.704377622</v>
+        <v>22951.704345992</v>
       </c>
       <c r="O1057" t="n">
-        <v>550840.9050629281</v>
+        <v>459034.08691984</v>
       </c>
       <c r="P1057" t="n">
         <v>37900</v>
       </c>
       <c r="Q1057" t="n">
-        <v>909600</v>
+        <v>758000</v>
       </c>
     </row>
     <row r="1058">
@@ -48404,22 +48404,22 @@
         <v>0</v>
       </c>
       <c r="L1060" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1060" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N1060" t="n">
-        <v>4985.4086330935</v>
+        <v>5058.1883211679</v>
       </c>
       <c r="O1060" t="n">
-        <v>129620.624460431</v>
+        <v>121396.5197080296</v>
       </c>
       <c r="P1060" t="n">
         <v>7900</v>
       </c>
       <c r="Q1060" t="n">
-        <v>205400</v>
+        <v>189600</v>
       </c>
     </row>
     <row r="1061">
@@ -51275,22 +51275,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1122" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N1122" t="n">
         <v>7920</v>
       </c>
       <c r="O1122" t="n">
-        <v>435600</v>
+        <v>427680</v>
       </c>
       <c r="P1122" t="n">
         <v>10500</v>
       </c>
       <c r="Q1122" t="n">
-        <v>577500</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="1123">
@@ -51324,22 +51324,22 @@
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1123" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1123" t="n">
-        <v>7920</v>
+        <v>7953.8461538462</v>
       </c>
       <c r="O1123" t="n">
-        <v>324720</v>
+        <v>318153.846153848</v>
       </c>
       <c r="P1123" t="n">
         <v>10500</v>
       </c>
       <c r="Q1123" t="n">
-        <v>430500</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="1124">
@@ -51373,22 +51373,22 @@
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1124" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1124" t="n">
-        <v>7920</v>
+        <v>7971.0967741935</v>
       </c>
       <c r="O1124" t="n">
-        <v>324720</v>
+        <v>318843.87096774</v>
       </c>
       <c r="P1124" t="n">
         <v>10500</v>
       </c>
       <c r="Q1124" t="n">
-        <v>430500</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="1125">
@@ -51557,22 +51557,22 @@
         <v>0</v>
       </c>
       <c r="L1128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1128" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N1128" t="n">
         <v>9240</v>
       </c>
       <c r="O1128" t="n">
-        <v>1386000</v>
+        <v>1349040</v>
       </c>
       <c r="P1128" t="n">
         <v>11500</v>
       </c>
       <c r="Q1128" t="n">
-        <v>1725000</v>
+        <v>1679000</v>
       </c>
     </row>
     <row r="1129">
@@ -51649,22 +51649,22 @@
         <v>0</v>
       </c>
       <c r="L1130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1130" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N1130" t="n">
-        <v>4576</v>
+        <v>4591.2533333333</v>
       </c>
       <c r="O1130" t="n">
-        <v>151008</v>
+        <v>146920.1066666656</v>
       </c>
       <c r="P1130" t="n">
         <v>5900</v>
       </c>
       <c r="Q1130" t="n">
-        <v>194700</v>
+        <v>188800</v>
       </c>
     </row>
     <row r="1131">
@@ -51695,22 +51695,22 @@
         <v>0</v>
       </c>
       <c r="L1131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1131" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N1131" t="n">
-        <v>5280</v>
+        <v>5285.1815505397</v>
       </c>
       <c r="O1131" t="n">
-        <v>253440</v>
+        <v>248403.5328753659</v>
       </c>
       <c r="P1131" t="n">
         <v>6900</v>
       </c>
       <c r="Q1131" t="n">
-        <v>331200</v>
+        <v>324300</v>
       </c>
     </row>
     <row r="1132">
@@ -52845,22 +52845,22 @@
         <v>0</v>
       </c>
       <c r="L1156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N1156" t="n">
         <v>46491.75</v>
       </c>
       <c r="O1156" t="n">
-        <v>185967</v>
+        <v>139475.25</v>
       </c>
       <c r="P1156" t="n">
         <v>52900</v>
       </c>
       <c r="Q1156" t="n">
-        <v>211600</v>
+        <v>158700</v>
       </c>
     </row>
     <row r="1157">
